--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2420" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2420" uniqueCount="500">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,7 +591,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
+    <t>http://va.gov/fhir/ValueSet/VSnull</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -609,7 +609,7 @@
     <t>FiveWs.status</t>
   </si>
   <si>
-    <t>1488: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - BACT RPT STATUS (#63.05-11.5)</t>
+    <t>1488: terminologyMaps using null on MICROBIOLOGY - BACT RPT STATUS (#63.05-11.5)</t>
   </si>
   <si>
     <t>Micro.Microbiology.BacteriologyReportStatus</t>
@@ -713,7 +713,7 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
-    <t>1525: fixed value without value? when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03) case NULL</t>
+    <t>1525: fixed value without value? when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1009,9 +1009,6 @@
     <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFPositiveNegative</t>
-  </si>
-  <si>
     <t>CodeableConcept.coding</t>
   </si>
   <si>
@@ -1021,7 +1018,7 @@
     <t>union(., ./translation)</t>
   </si>
   <si>
-    <t>1516: terminologyMaps using VF_PositiveNegative on MICROBIOLOGY - URINE SCREEN (#63.05-11.57)</t>
+    <t>1516: terminologyMaps using null on MICROBIOLOGY - URINE SCREEN (#63.05-11.57)</t>
   </si>
   <si>
     <t>Micro.Microbiology.UrineScreen</t>
@@ -1580,10 +1577,7 @@
     <t>Observation.component.interpretation</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFAntibioticSensitivityInterpretation</t>
-  </si>
-  <si>
-    <t>1524: terminologyMaps using VF_AntibioticSensitivityInterpretation on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (#63.05-12 &gt; 63.3-5.1+to+160.1)</t>
+    <t>1524: terminologyMaps using null on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (#63.05-12 &gt; 63.3-5.1+to+160.1)</t>
   </si>
   <si>
     <t>Observation.component.referenceRange</t>
@@ -1937,7 +1931,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="63.70703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.58203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="50.40625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -1953,7 +1947,7 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="226.3125" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="247.3984375" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -5450,25 +5444,25 @@
       </c>
       <c r="Y28" s="2"/>
       <c r="Z28" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF28" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="AA28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF28" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>82</v>
@@ -5489,30 +5483,30 @@
         <v>84</v>
       </c>
       <c r="AM28" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AN28" t="s" s="2">
+      <c r="AO28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP28" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AQ28" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AO28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP28" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AQ28" t="s" s="2">
+      <c r="AR28" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AR28" t="s" s="2">
-        <v>320</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5538,16 +5532,16 @@
         <v>297</v>
       </c>
       <c r="L29" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M29" t="s" s="2">
         <v>323</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" t="s" s="2">
         <v>324</v>
       </c>
-      <c r="N29" t="s" s="2">
+      <c r="O29" t="s" s="2">
         <v>325</v>
-      </c>
-      <c r="O29" t="s" s="2">
-        <v>326</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>84</v>
@@ -5596,7 +5590,7 @@
         <v>84</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>82</v>
@@ -5617,10 +5611,10 @@
         <v>84</v>
       </c>
       <c r="AM29" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AN29" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>84</v>
@@ -5637,13 +5631,13 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B30" t="s" s="2">
         <v>280</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D30" t="s" s="2">
         <v>84</v>
@@ -5759,18 +5753,18 @@
         <v>292</v>
       </c>
       <c r="AQ30" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="AR30" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="AR30" t="s" s="2">
-        <v>333</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5796,16 +5790,16 @@
         <v>193</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M31" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="N31" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>84</v>
@@ -5834,7 +5828,7 @@
       </c>
       <c r="Y31" s="2"/>
       <c r="Z31" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>84</v>
@@ -5852,7 +5846,7 @@
         <v>84</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>82</v>
@@ -5861,7 +5855,7 @@
         <v>94</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>106</v>
@@ -5876,7 +5870,7 @@
         <v>137</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>84</v>
@@ -5893,14 +5887,14 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5922,16 +5916,16 @@
         <v>193</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>84</v>
@@ -5959,11 +5953,11 @@
         <v>213</v>
       </c>
       <c r="Y32" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="Z32" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="Z32" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="AA32" t="s" s="2">
         <v>84</v>
       </c>
@@ -5980,7 +5974,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -5998,19 +5992,19 @@
         <v>84</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AM32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP32" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="AO32" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP32" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6021,10 +6015,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6047,19 +6041,19 @@
         <v>84</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>358</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6108,7 +6102,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6129,10 +6123,10 @@
         <v>84</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>84</v>
@@ -6149,10 +6143,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6178,13 +6172,13 @@
         <v>193</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6210,14 +6204,14 @@
         <v>84</v>
       </c>
       <c r="X34" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="Y34" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="Y34" t="s" s="2">
+      <c r="Z34" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="Z34" t="s" s="2">
-        <v>368</v>
-      </c>
       <c r="AA34" t="s" s="2">
         <v>84</v>
       </c>
@@ -6234,7 +6228,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6252,19 +6246,19 @@
         <v>84</v>
       </c>
       <c r="AL34" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>369</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP34" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6275,10 +6269,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6304,16 +6298,16 @@
         <v>193</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>374</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="N35" t="s" s="2">
+      <c r="O35" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6338,14 +6332,14 @@
         <v>84</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Y35" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Z35" t="s" s="2">
         <v>378</v>
       </c>
-      <c r="Z35" t="s" s="2">
-        <v>379</v>
-      </c>
       <c r="AA35" t="s" s="2">
         <v>84</v>
       </c>
@@ -6362,7 +6356,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6383,10 +6377,10 @@
         <v>84</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>381</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>84</v>
@@ -6403,10 +6397,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6429,16 +6423,16 @@
         <v>84</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="L36" t="s" s="2">
+      <c r="M36" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="M36" t="s" s="2">
+      <c r="N36" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -6488,7 +6482,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6506,19 +6500,19 @@
         <v>84</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AM36" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="AM36" t="s" s="2">
+      <c r="AN36" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="AN36" t="s" s="2">
+      <c r="AO36" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP36" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AO36" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP36" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6529,10 +6523,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6555,16 +6549,16 @@
         <v>84</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>395</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6614,7 +6608,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -6632,19 +6626,19 @@
         <v>84</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>396</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP37" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP37" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="AQ37" t="s" s="2">
         <v>84</v>
@@ -6655,10 +6649,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6681,19 +6675,19 @@
         <v>84</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>401</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>84</v>
@@ -6742,7 +6736,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -6754,19 +6748,19 @@
         <v>84</v>
       </c>
       <c r="AJ38" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AK38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>84</v>
@@ -6783,10 +6777,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6907,10 +6901,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7033,14 +7027,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7062,10 +7056,10 @@
         <v>140</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>143</v>
@@ -7120,7 +7114,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7161,10 +7155,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7187,13 +7181,13 @@
         <v>84</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7244,7 +7238,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7253,7 +7247,7 @@
         <v>94</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>106</v>
@@ -7265,10 +7259,10 @@
         <v>84</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>84</v>
@@ -7285,10 +7279,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7311,13 +7305,13 @@
         <v>84</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7368,7 +7362,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7377,7 +7371,7 @@
         <v>94</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>106</v>
@@ -7389,10 +7383,10 @@
         <v>84</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>84</v>
@@ -7409,10 +7403,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7438,16 +7432,16 @@
         <v>193</v>
       </c>
       <c r="L44" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="M44" t="s" s="2">
         <v>428</v>
       </c>
-      <c r="M44" t="s" s="2">
+      <c r="N44" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="N44" t="s" s="2">
+      <c r="O44" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7475,11 +7469,11 @@
         <v>118</v>
       </c>
       <c r="Y44" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="Z44" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="Z44" t="s" s="2">
-        <v>433</v>
-      </c>
       <c r="AA44" t="s" s="2">
         <v>84</v>
       </c>
@@ -7496,7 +7490,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7514,13 +7508,13 @@
         <v>84</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AM44" t="s" s="2">
-        <v>435</v>
-      </c>
       <c r="AN44" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>84</v>
@@ -7537,10 +7531,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7566,16 +7560,16 @@
         <v>193</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M45" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M45" t="s" s="2">
+      <c r="N45" t="s" s="2">
         <v>438</v>
       </c>
-      <c r="N45" t="s" s="2">
+      <c r="O45" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="O45" t="s" s="2">
-        <v>440</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -7600,14 +7594,14 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Y45" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="Z45" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="Z45" t="s" s="2">
-        <v>442</v>
-      </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
       </c>
@@ -7624,7 +7618,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -7642,13 +7636,13 @@
         <v>84</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>435</v>
-      </c>
       <c r="AN45" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>84</v>
@@ -7665,10 +7659,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7691,17 +7685,17 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="L46" t="s" s="2">
+      <c r="M46" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -7750,7 +7744,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -7774,7 +7768,7 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>84</v>
@@ -7791,10 +7785,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7820,10 +7814,10 @@
         <v>297</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7874,7 +7868,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -7895,10 +7889,10 @@
         <v>84</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>84</v>
@@ -7915,10 +7909,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7941,16 +7935,16 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="M48" t="s" s="2">
+      <c r="N48" t="s" s="2">
         <v>456</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>457</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8000,7 +7994,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8021,10 +8015,10 @@
         <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>84</v>
@@ -8041,10 +8035,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8067,16 +8061,16 @@
         <v>95</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>462</v>
       </c>
-      <c r="M49" t="s" s="2">
+      <c r="N49" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -8126,7 +8120,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8147,10 +8141,10 @@
         <v>84</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>84</v>
@@ -8167,10 +8161,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8193,19 +8187,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>469</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>470</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>84</v>
@@ -8254,7 +8248,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8275,10 +8269,10 @@
         <v>84</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>84</v>
@@ -8295,10 +8289,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8419,10 +8413,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8545,14 +8539,14 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
@@ -8574,10 +8568,10 @@
         <v>140</v>
       </c>
       <c r="L53" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="M53" t="s" s="2">
         <v>413</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>414</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>143</v>
@@ -8632,7 +8626,7 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
@@ -8673,10 +8667,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8702,13 +8696,13 @@
         <v>193</v>
       </c>
       <c r="L54" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>477</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="O54" t="s" s="2">
         <v>212</v>
@@ -8736,10 +8730,10 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="Z54" t="s" s="2">
         <v>215</v>
@@ -8760,7 +8754,7 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>94</v>
@@ -8778,7 +8772,7 @@
         <v>84</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>218</v>
@@ -8793,7 +8787,7 @@
         <v>84</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>84</v>
@@ -8801,10 +8795,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8830,13 +8824,13 @@
         <v>281</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M55" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>285</v>
@@ -8886,7 +8880,7 @@
         <v>201</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -8904,7 +8898,7 @@
         <v>84</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>290</v>
@@ -8927,13 +8921,13 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>84</v>
@@ -8958,13 +8952,13 @@
         <v>297</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>484</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>485</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>486</v>
       </c>
       <c r="O56" t="s" s="2">
         <v>285</v>
@@ -9016,7 +9010,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9034,7 +9028,7 @@
         <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>290</v>
@@ -9049,7 +9043,7 @@
         <v>292</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>84</v>
@@ -9057,10 +9051,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9086,16 +9080,16 @@
         <v>193</v>
       </c>
       <c r="L57" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="M57" t="s" s="2">
         <v>491</v>
       </c>
-      <c r="M57" t="s" s="2">
+      <c r="N57" t="s" s="2">
         <v>492</v>
       </c>
-      <c r="N57" t="s" s="2">
-        <v>493</v>
-      </c>
       <c r="O57" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9123,10 +9117,10 @@
         <v>213</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>84</v>
@@ -9144,7 +9138,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9153,7 +9147,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9168,7 +9162,7 @@
         <v>137</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>84</v>
@@ -9185,14 +9179,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -9214,16 +9208,16 @@
         <v>193</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M58" t="s" s="2">
+      <c r="N58" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9252,7 +9246,7 @@
       </c>
       <c r="Y58" s="2"/>
       <c r="Z58" t="s" s="2">
-        <v>497</v>
+        <v>184</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9270,7 +9264,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9288,22 +9282,22 @@
         <v>84</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AO58" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AP58" t="s" s="2">
-        <v>353</v>
-      </c>
       <c r="AQ58" t="s" s="2">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>84</v>
@@ -9311,10 +9305,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9340,16 +9334,16 @@
         <v>85</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="N59" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="O59" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9398,7 +9392,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9419,10 +9413,10 @@
         <v>84</v>
       </c>
       <c r="AM59" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>407</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>408</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,7 +591,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSnull</t>
+    <t>http://va.gov/fhir/ValueSet/VSundefined</t>
   </si>
   <si>
     <t>Event.status</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2420" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2422" uniqueCount="500">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -591,7 +591,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSundefined</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-status</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -5440,11 +5440,13 @@
         <v>84</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>184</v>
+        <v>84</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>84</v>
@@ -9242,11 +9244,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>213</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>347</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>184</v>
+        <v>348</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -713,7 +713,7 @@
     <t>116680003 |Is a|</t>
   </si>
   <si>
-    <t>1525: fixed value without value? when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
+    <t>1525: fixed value = http://loinc.org#42803-7 Bacteria identified in Isolate when MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (#63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.03 &gt; 95.03-) case NULL</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1947,7 +1947,7 @@
     <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
-    <col min="43" max="43" width="247.3984375" customWidth="true" bestFit="true"/>
+    <col min="43" max="43" width="255.0" customWidth="true" bestFit="true"/>
     <col min="44" max="44" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AR$93</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4032" uniqueCount="656">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3789" uniqueCount="640">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1359,57 +1359,6 @@
   </si>
   <si>
     <t>363714003 |Interprets|</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.id</t>
-  </si>
-  <si>
-    <t>Observation.value[x].id</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x].extension</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>Observation.value[x].coding</t>
-  </si>
-  <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFMicrobiologyUrineScreenResult</t>
-  </si>
-  <si>
-    <t>1516: terminologyMaps using VF_MicrobiologyUrineScreenResult on MICROBIOLOGY - URINE SCREEN (63.05-11.57)</t>
-  </si>
-  <si>
-    <t>Micro.Microbiology.UrineScreen</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept.text</t>
-  </si>
-  <si>
-    <t>Observation.value[x].text</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
-  </si>
-  <si>
-    <t>1517: source value from MICROBIOLOGY - SPUTUM SCREEN (63.05-11.58)</t>
-  </si>
-  <si>
-    <t>Micro.Microbiology.SputumScreen</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -2042,6 +1991,9 @@
   </si>
   <si>
     <t>Observation.component:va-component.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
   </si>
   <si>
     <t>1523: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (63.05-12 &gt; 63.3-5+to+160)</t>
@@ -2376,12 +2328,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AR99"/>
+  <dimension ref="A1:AR93"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="47.40625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -7947,14 +7899,16 @@
         <v>84</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AC44" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="AD44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>419</v>
@@ -8001,11 +7955,9 @@
         <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="C45" t="s" s="2">
-        <v>432</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>84</v>
       </c>
@@ -8023,22 +7975,22 @@
         <v>84</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K45" t="s" s="2">
         <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8063,13 +8015,11 @@
         <v>84</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -8087,7 +8037,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8096,10 +8046,10 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>426</v>
+        <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>84</v>
@@ -8111,38 +8061,38 @@
         <v>84</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>427</v>
+        <v>84</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>428</v>
+        <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>430</v>
+        <v>84</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>84</v>
+        <v>440</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>84</v>
@@ -8154,16 +8104,20 @@
         <v>84</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>162</v>
+        <v>441</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
       </c>
@@ -8187,13 +8141,13 @@
         <v>84</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>84</v>
+        <v>446</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8211,19 +8165,19 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>164</v>
+        <v>439</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>84</v>
@@ -8235,31 +8189,31 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>84</v>
+        <v>447</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>84</v>
+        <v>448</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>165</v>
+        <v>449</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>84</v>
+        <v>450</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -8269,7 +8223,7 @@
         <v>83</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>84</v>
@@ -8278,18 +8232,20 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>140</v>
+        <v>452</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>141</v>
+        <v>453</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>167</v>
+        <v>454</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>456</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
       </c>
@@ -8325,19 +8281,19 @@
         <v>84</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>171</v>
+        <v>451</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8349,13 +8305,13 @@
         <v>84</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>84</v>
+        <v>457</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>84</v>
+        <v>458</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>84</v>
@@ -8364,10 +8320,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>84</v>
+        <v>459</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>165</v>
+        <v>460</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8378,10 +8334,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>437</v>
+        <v>461</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>438</v>
+        <v>461</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8392,32 +8348,30 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>290</v>
+        <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>291</v>
+        <v>462</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>292</v>
+        <v>463</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>84</v>
       </c>
@@ -8441,11 +8395,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y48" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="Z48" t="s" s="2">
-        <v>439</v>
+        <v>467</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8463,13 +8419,13 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>295</v>
+        <v>461</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>84</v>
@@ -8478,36 +8434,36 @@
         <v>106</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>440</v>
+        <v>84</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>441</v>
+        <v>84</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>84</v>
+        <v>468</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>297</v>
+        <v>469</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>298</v>
+        <v>470</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>84</v>
+        <v>471</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>442</v>
+        <v>472</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>443</v>
+        <v>472</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8527,22 +8483,22 @@
         <v>84</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>343</v>
+        <v>473</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>344</v>
+        <v>474</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>345</v>
+        <v>475</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>346</v>
+        <v>476</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8567,13 +8523,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>84</v>
+        <v>465</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>84</v>
+        <v>477</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>84</v>
+        <v>478</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8591,7 +8547,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>347</v>
+        <v>472</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8618,10 +8574,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>348</v>
+        <v>479</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>349</v>
+        <v>480</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8632,14 +8588,12 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>444</v>
+        <v>481</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="C50" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>481</v>
+      </c>
+      <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8657,23 +8611,21 @@
         <v>84</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>161</v>
+        <v>482</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>421</v>
+        <v>483</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>422</v>
+        <v>484</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>84</v>
       </c>
@@ -8721,7 +8673,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>419</v>
+        <v>481</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8730,42 +8682,42 @@
         <v>94</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>425</v>
+        <v>84</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>426</v>
+        <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>446</v>
+        <v>486</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>447</v>
+        <v>487</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>427</v>
+        <v>488</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>428</v>
+        <v>489</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>429</v>
+        <v>490</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>430</v>
+        <v>491</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>448</v>
+        <v>492</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>448</v>
+        <v>492</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8779,7 +8731,7 @@
         <v>94</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>84</v>
@@ -8788,20 +8740,18 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>183</v>
+        <v>493</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>449</v>
+        <v>494</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>450</v>
+        <v>495</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>84</v>
       </c>
@@ -8825,11 +8775,13 @@
         <v>84</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y51" s="2"/>
+        <v>84</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="Z51" t="s" s="2">
-        <v>453</v>
+        <v>84</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>84</v>
@@ -8847,7 +8799,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>448</v>
+        <v>492</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8856,7 +8808,7 @@
         <v>94</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>454</v>
+        <v>84</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>106</v>
@@ -8871,31 +8823,31 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>84</v>
+        <v>497</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>137</v>
+        <v>498</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>455</v>
+        <v>499</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>84</v>
+        <v>500</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>457</v>
+        <v>84</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -8914,19 +8866,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>183</v>
+        <v>502</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>458</v>
+        <v>503</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>459</v>
+        <v>504</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>460</v>
+        <v>505</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>461</v>
+        <v>506</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8951,13 +8903,13 @@
         <v>84</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>462</v>
+        <v>84</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>463</v>
+        <v>84</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>84</v>
@@ -8975,7 +8927,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>456</v>
+        <v>501</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8987,7 +8939,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>106</v>
+        <v>507</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8999,27 +8951,27 @@
         <v>84</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>464</v>
+        <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>465</v>
+        <v>508</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>466</v>
+        <v>509</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR52" t="s" s="2">
-        <v>467</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>468</v>
+        <v>510</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>468</v>
+        <v>510</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9030,10 +8982,10 @@
         <v>82</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>84</v>
@@ -9042,20 +8994,16 @@
         <v>84</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>469</v>
+        <v>161</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>470</v>
+        <v>162</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>473</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>84</v>
       </c>
@@ -9103,25 +9051,25 @@
         <v>84</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>468</v>
+        <v>164</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>474</v>
+        <v>84</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>475</v>
+        <v>84</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>84</v>
@@ -9130,10 +9078,10 @@
         <v>84</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>476</v>
+        <v>84</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>477</v>
+        <v>165</v>
       </c>
       <c r="AQ53" t="s" s="2">
         <v>84</v>
@@ -9144,21 +9092,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>478</v>
+        <v>511</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>478</v>
+        <v>511</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>84</v>
@@ -9170,16 +9118,16 @@
         <v>84</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>479</v>
+        <v>141</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>480</v>
+        <v>167</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>481</v>
+        <v>143</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -9205,13 +9153,13 @@
         <v>84</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>482</v>
+        <v>84</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>483</v>
+        <v>84</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>484</v>
+        <v>84</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>84</v>
@@ -9229,19 +9177,19 @@
         <v>84</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>478</v>
+        <v>171</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>84</v>
@@ -9253,62 +9201,62 @@
         <v>84</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>485</v>
+        <v>84</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>486</v>
+        <v>84</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>487</v>
+        <v>165</v>
       </c>
       <c r="AQ54" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR54" t="s" s="2">
-        <v>488</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>489</v>
+        <v>512</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>489</v>
+        <v>512</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>84</v>
+        <v>513</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>490</v>
+        <v>514</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>491</v>
+        <v>515</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>492</v>
+        <v>143</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>493</v>
+        <v>149</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>84</v>
@@ -9333,13 +9281,13 @@
         <v>84</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>482</v>
+        <v>84</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>494</v>
+        <v>84</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>495</v>
+        <v>84</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>84</v>
@@ -9357,19 +9305,19 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>84</v>
@@ -9384,10 +9332,10 @@
         <v>84</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>496</v>
+        <v>84</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>497</v>
+        <v>137</v>
       </c>
       <c r="AQ55" t="s" s="2">
         <v>84</v>
@@ -9398,10 +9346,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9415,7 +9363,7 @@
         <v>94</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>84</v>
@@ -9424,17 +9372,15 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>499</v>
+        <v>518</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>500</v>
+        <v>519</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>520</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>84</v>
@@ -9483,7 +9429,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>498</v>
+        <v>517</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9492,42 +9438,42 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>84</v>
+        <v>521</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>503</v>
+        <v>84</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>504</v>
+        <v>84</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>505</v>
+        <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>506</v>
+        <v>522</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>507</v>
+        <v>523</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR56" t="s" s="2">
-        <v>508</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9550,17 +9496,15 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>513</v>
-      </c>
+        <v>526</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>84</v>
@@ -9609,7 +9553,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>509</v>
+        <v>524</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9618,7 +9562,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>84</v>
+        <v>521</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9633,27 +9577,27 @@
         <v>84</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>514</v>
+        <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR57" t="s" s="2">
-        <v>517</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9664,7 +9608,7 @@
         <v>82</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>84</v>
@@ -9676,19 +9620,19 @@
         <v>84</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>519</v>
+        <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9713,13 +9657,13 @@
         <v>84</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>84</v>
+        <v>118</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>84</v>
+        <v>533</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>84</v>
+        <v>534</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9737,19 +9681,19 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>518</v>
+        <v>528</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>524</v>
+        <v>106</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>84</v>
@@ -9761,13 +9705,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>84</v>
+        <v>535</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>525</v>
+        <v>536</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>526</v>
+        <v>449</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9778,10 +9722,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>527</v>
+        <v>537</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9792,7 +9736,7 @@
         <v>82</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>84</v>
@@ -9804,16 +9748,20 @@
         <v>84</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>162</v>
+        <v>538</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N59" s="2"/>
-      <c r="O59" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>541</v>
+      </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
       </c>
@@ -9837,13 +9785,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>84</v>
+        <v>465</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>84</v>
+        <v>542</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>84</v>
+        <v>543</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9861,19 +9809,19 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>164</v>
+        <v>537</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>84</v>
@@ -9885,13 +9833,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>84</v>
+        <v>535</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>84</v>
+        <v>536</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>165</v>
+        <v>449</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9902,21 +9850,21 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>528</v>
+        <v>544</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>84</v>
@@ -9928,18 +9876,18 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>140</v>
+        <v>545</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>141</v>
+        <v>546</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
       </c>
@@ -9987,19 +9935,19 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>171</v>
+        <v>544</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>84</v>
@@ -10017,7 +9965,7 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>165</v>
+        <v>549</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -10028,46 +9976,42 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>529</v>
+        <v>550</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>530</v>
+        <v>84</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>531</v>
+        <v>551</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>84</v>
       </c>
@@ -10115,19 +10059,19 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>533</v>
+        <v>550</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>84</v>
@@ -10142,10 +10086,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>84</v>
+        <v>522</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>137</v>
+        <v>553</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10156,10 +10100,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10170,7 +10114,7 @@
         <v>82</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>84</v>
@@ -10179,18 +10123,20 @@
         <v>84</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>535</v>
+        <v>555</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>536</v>
+        <v>556</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="N62" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>84</v>
@@ -10239,16 +10185,16 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>538</v>
+        <v>84</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>106</v>
@@ -10266,10 +10212,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>540</v>
+        <v>560</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10280,10 +10226,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10294,7 +10240,7 @@
         <v>82</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>84</v>
@@ -10303,18 +10249,20 @@
         <v>84</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>535</v>
+        <v>562</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>542</v>
+        <v>563</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>564</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>565</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>84</v>
@@ -10363,16 +10311,16 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>538</v>
+        <v>84</v>
       </c>
       <c r="AJ63" t="s" s="2">
         <v>106</v>
@@ -10390,10 +10338,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>539</v>
+        <v>559</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>544</v>
+        <v>566</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10404,10 +10352,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>545</v>
+        <v>567</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>545</v>
+        <v>567</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10418,7 +10366,7 @@
         <v>82</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>84</v>
@@ -10427,22 +10375,22 @@
         <v>84</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>183</v>
+        <v>502</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>546</v>
+        <v>568</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>547</v>
+        <v>569</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>548</v>
+        <v>570</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>549</v>
+        <v>571</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10467,37 +10415,35 @@
         <v>84</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>550</v>
+        <v>84</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>551</v>
+        <v>84</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>545</v>
+        <v>567</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>84</v>
@@ -10515,13 +10461,13 @@
         <v>84</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>552</v>
+        <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>553</v>
+        <v>573</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>466</v>
+        <v>574</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10532,10 +10478,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>554</v>
+        <v>575</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10546,7 +10492,7 @@
         <v>82</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>84</v>
@@ -10558,20 +10504,16 @@
         <v>84</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>555</v>
+        <v>162</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>84</v>
       </c>
@@ -10595,13 +10537,13 @@
         <v>84</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>482</v>
+        <v>84</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>559</v>
+        <v>84</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>560</v>
+        <v>84</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>84</v>
@@ -10619,19 +10561,19 @@
         <v>84</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>554</v>
+        <v>164</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>84</v>
@@ -10643,13 +10585,13 @@
         <v>84</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>552</v>
+        <v>84</v>
       </c>
       <c r="AO65" t="s" s="2">
-        <v>553</v>
+        <v>84</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>466</v>
+        <v>165</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>84</v>
@@ -10660,21 +10602,21 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>84</v>
@@ -10686,18 +10628,18 @@
         <v>84</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>562</v>
+        <v>140</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>563</v>
+        <v>141</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" t="s" s="2">
-        <v>565</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>84</v>
       </c>
@@ -10745,19 +10687,19 @@
         <v>84</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>561</v>
+        <v>171</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>84</v>
@@ -10775,7 +10717,7 @@
         <v>84</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>566</v>
+        <v>165</v>
       </c>
       <c r="AQ66" t="s" s="2">
         <v>84</v>
@@ -10786,42 +10728,46 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>567</v>
+        <v>577</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>84</v>
+        <v>513</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>568</v>
+        <v>514</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N67" s="2"/>
-      <c r="O67" s="2"/>
+        <v>515</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="O67" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P67" t="s" s="2">
         <v>84</v>
       </c>
@@ -10869,19 +10815,19 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>567</v>
+        <v>516</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>84</v>
@@ -10896,10 +10842,10 @@
         <v>84</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>539</v>
+        <v>84</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>570</v>
+        <v>137</v>
       </c>
       <c r="AQ67" t="s" s="2">
         <v>84</v>
@@ -10910,10 +10856,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10921,10 +10867,10 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>84</v>
@@ -10936,18 +10882,20 @@
         <v>95</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>572</v>
+        <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O68" s="2"/>
+        <v>581</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>278</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>84</v>
       </c>
@@ -10971,13 +10919,13 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>84</v>
+        <v>465</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>84</v>
+        <v>582</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>84</v>
+        <v>280</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>84</v>
@@ -10995,13 +10943,13 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>84</v>
@@ -11019,16 +10967,16 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>84</v>
+        <v>583</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>576</v>
+        <v>283</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>577</v>
+        <v>284</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>84</v>
+        <v>285</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>84</v>
@@ -11036,10 +10984,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11050,7 +10998,7 @@
         <v>82</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>84</v>
@@ -11062,18 +11010,20 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>579</v>
+        <v>420</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>580</v>
+        <v>585</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>581</v>
+        <v>586</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
       </c>
@@ -11121,13 +11071,13 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>578</v>
+        <v>584</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>84</v>
@@ -11145,27 +11095,27 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>84</v>
+        <v>588</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>576</v>
+        <v>428</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>583</v>
+        <v>429</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>84</v>
+        <v>430</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>584</v>
+        <v>589</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11176,7 +11126,7 @@
         <v>82</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>84</v>
@@ -11185,22 +11135,22 @@
         <v>84</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>519</v>
+        <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>586</v>
+        <v>591</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>587</v>
+        <v>592</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>588</v>
+        <v>435</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11225,38 +11175,40 @@
         <v>84</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>84</v>
+        <v>593</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AB70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="AC70" s="2"/>
-      <c r="AD70" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>584</v>
-      </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>84</v>
+        <v>594</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11274,10 +11226,10 @@
         <v>84</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>590</v>
+        <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>591</v>
+        <v>438</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11288,21 +11240,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>84</v>
+        <v>440</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>84</v>
@@ -11314,16 +11266,20 @@
         <v>84</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>162</v>
+        <v>441</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
       </c>
@@ -11347,13 +11303,13 @@
         <v>84</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>84</v>
+        <v>445</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>84</v>
+        <v>446</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11371,19 +11327,19 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>164</v>
+        <v>595</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>84</v>
@@ -11395,31 +11351,31 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>84</v>
+        <v>447</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>84</v>
+        <v>448</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>165</v>
+        <v>449</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>84</v>
+        <v>450</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11438,18 +11394,20 @@
         <v>84</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>141</v>
+        <v>597</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>167</v>
+        <v>598</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O72" s="2"/>
+        <v>505</v>
+      </c>
+      <c r="O72" t="s" s="2">
+        <v>506</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
       </c>
@@ -11497,7 +11455,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>171</v>
+        <v>596</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11509,7 +11467,7 @@
         <v>84</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>84</v>
@@ -11524,10 +11482,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>84</v>
+        <v>508</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>165</v>
+        <v>509</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11538,45 +11496,47 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>567</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>600</v>
+      </c>
       <c r="D73" t="s" s="2">
-        <v>530</v>
+        <v>84</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>95</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>140</v>
+        <v>502</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>531</v>
+        <v>568</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>532</v>
+        <v>569</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>143</v>
+        <v>570</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>149</v>
+        <v>571</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
@@ -11625,7 +11585,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>533</v>
+        <v>567</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11637,7 +11597,7 @@
         <v>84</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>84</v>
@@ -11652,10 +11612,10 @@
         <v>84</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>84</v>
+        <v>573</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>137</v>
+        <v>574</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11666,10 +11626,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>595</v>
+        <v>575</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11677,7 +11637,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>94</v>
@@ -11689,23 +11649,19 @@
         <v>84</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>596</v>
+        <v>162</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>278</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>84</v>
       </c>
@@ -11729,13 +11685,13 @@
         <v>84</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>482</v>
+        <v>84</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>599</v>
+        <v>84</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>280</v>
+        <v>84</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>84</v>
@@ -11753,10 +11709,10 @@
         <v>84</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>595</v>
+        <v>164</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>94</v>
@@ -11765,7 +11721,7 @@
         <v>84</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>84</v>
@@ -11777,16 +11733,16 @@
         <v>84</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>600</v>
+        <v>84</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>283</v>
+        <v>84</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>284</v>
+        <v>165</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>285</v>
+        <v>84</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>84</v>
@@ -11794,21 +11750,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>601</v>
+        <v>576</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>84</v>
@@ -11817,23 +11773,21 @@
         <v>84</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>420</v>
+        <v>140</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>602</v>
+        <v>141</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>603</v>
+        <v>167</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="O75" t="s" s="2">
-        <v>424</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>84</v>
       </c>
@@ -11881,19 +11835,19 @@
         <v>84</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>601</v>
+        <v>171</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>84</v>
@@ -11905,62 +11859,62 @@
         <v>84</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>605</v>
+        <v>84</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>428</v>
+        <v>84</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>429</v>
+        <v>165</v>
       </c>
       <c r="AQ75" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR75" t="s" s="2">
-        <v>430</v>
+        <v>84</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>606</v>
+        <v>577</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>84</v>
+        <v>513</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>183</v>
+        <v>140</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>607</v>
+        <v>514</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>608</v>
+        <v>515</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>609</v>
+        <v>143</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>452</v>
+        <v>149</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>84</v>
@@ -11985,13 +11939,13 @@
         <v>84</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>188</v>
+        <v>84</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>610</v>
+        <v>84</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>453</v>
+        <v>84</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>84</v>
@@ -12009,19 +11963,19 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>606</v>
+        <v>516</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>611</v>
+        <v>84</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>84</v>
@@ -12036,10 +11990,10 @@
         <v>84</v>
       </c>
       <c r="AO76" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AP76" t="s" s="2">
         <v>137</v>
-      </c>
-      <c r="AP76" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AQ76" t="s" s="2">
         <v>84</v>
@@ -12050,45 +12004,45 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>612</v>
+        <v>578</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>457</v>
+        <v>84</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K77" t="s" s="2">
         <v>183</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>458</v>
+        <v>579</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>459</v>
+        <v>580</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>460</v>
+        <v>581</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>461</v>
+        <v>278</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>84</v>
@@ -12113,13 +12067,13 @@
         <v>84</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>188</v>
+        <v>465</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>462</v>
+        <v>582</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>463</v>
+        <v>280</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>84</v>
@@ -12137,13 +12091,13 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>612</v>
+        <v>578</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>84</v>
@@ -12152,7 +12106,7 @@
         <v>106</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>84</v>
+        <v>605</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>84</v>
@@ -12161,27 +12115,27 @@
         <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>464</v>
+        <v>583</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>465</v>
+        <v>283</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>466</v>
+        <v>284</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>84</v>
+        <v>285</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>467</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>613</v>
+        <v>606</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12192,7 +12146,7 @@
         <v>82</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>84</v>
@@ -12204,20 +12158,16 @@
         <v>84</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>85</v>
+        <v>161</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>614</v>
+        <v>162</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O78" t="s" s="2">
-        <v>523</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>84</v>
       </c>
@@ -12265,19 +12215,19 @@
         <v>84</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>613</v>
+        <v>164</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>106</v>
+        <v>84</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>84</v>
@@ -12292,10 +12242,10 @@
         <v>84</v>
       </c>
       <c r="AO78" t="s" s="2">
-        <v>525</v>
+        <v>84</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>526</v>
+        <v>165</v>
       </c>
       <c r="AQ78" t="s" s="2">
         <v>84</v>
@@ -12306,23 +12256,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>617</v>
-      </c>
+        <v>609</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>84</v>
@@ -12331,23 +12279,21 @@
         <v>84</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>519</v>
+        <v>140</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>585</v>
+        <v>141</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>586</v>
+        <v>167</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>588</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>84</v>
       </c>
@@ -12383,19 +12329,19 @@
         <v>84</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>584</v>
+        <v>171</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>82</v>
@@ -12407,7 +12353,7 @@
         <v>84</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>84</v>
@@ -12422,10 +12368,10 @@
         <v>84</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>590</v>
+        <v>84</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>591</v>
+        <v>165</v>
       </c>
       <c r="AQ79" t="s" s="2">
         <v>84</v>
@@ -12436,10 +12382,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>592</v>
+        <v>611</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12450,7 +12396,7 @@
         <v>82</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>84</v>
@@ -12459,19 +12405,23 @@
         <v>84</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>161</v>
+        <v>290</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>162</v>
+        <v>291</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="O80" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="P80" t="s" s="2">
         <v>84</v>
       </c>
@@ -12519,19 +12469,19 @@
         <v>84</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>164</v>
+        <v>295</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>84</v>
@@ -12546,10 +12496,10 @@
         <v>84</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>84</v>
+        <v>297</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>165</v>
+        <v>298</v>
       </c>
       <c r="AQ80" t="s" s="2">
         <v>84</v>
@@ -12560,21 +12510,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>619</v>
+        <v>612</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>593</v>
+        <v>613</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>84</v>
@@ -12586,17 +12536,15 @@
         <v>84</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N81" t="s" s="2">
-        <v>143</v>
-      </c>
+        <v>163</v>
+      </c>
+      <c r="N81" s="2"/>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>84</v>
@@ -12645,19 +12593,19 @@
         <v>84</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>84</v>
@@ -12686,14 +12634,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>594</v>
+        <v>615</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>530</v>
+        <v>139</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12706,26 +12654,24 @@
         <v>84</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>140</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>531</v>
+        <v>141</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>532</v>
+        <v>167</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="O82" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>84</v>
       </c>
@@ -12761,19 +12707,19 @@
         <v>84</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>84</v>
+        <v>168</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>84</v>
+        <v>169</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>533</v>
+        <v>171</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>82</v>
@@ -12803,7 +12749,7 @@
         <v>84</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="AQ82" t="s" s="2">
         <v>84</v>
@@ -12814,10 +12760,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>621</v>
+        <v>616</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>595</v>
+        <v>617</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12825,7 +12771,7 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>94</v>
@@ -12840,19 +12786,19 @@
         <v>95</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>183</v>
+        <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>596</v>
+        <v>302</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>597</v>
+        <v>303</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>598</v>
+        <v>304</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>84</v>
@@ -12862,7 +12808,7 @@
         <v>84</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>84</v>
+        <v>618</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>84</v>
@@ -12877,13 +12823,13 @@
         <v>84</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>482</v>
+        <v>84</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>599</v>
+        <v>84</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>280</v>
+        <v>84</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>84</v>
@@ -12901,10 +12847,10 @@
         <v>84</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>595</v>
+        <v>306</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>94</v>
@@ -12916,7 +12862,7 @@
         <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>84</v>
@@ -12925,16 +12871,16 @@
         <v>84</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>600</v>
+        <v>84</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>284</v>
+        <v>309</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>285</v>
+        <v>84</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>84</v>
@@ -12942,10 +12888,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>623</v>
+        <v>620</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>624</v>
+        <v>621</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12965,18 +12911,20 @@
         <v>84</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>161</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>162</v>
+        <v>311</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>312</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>84</v>
@@ -13025,7 +12973,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>164</v>
+        <v>314</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13037,7 +12985,7 @@
         <v>84</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>84</v>
@@ -13052,10 +13000,10 @@
         <v>84</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>84</v>
+        <v>315</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>165</v>
+        <v>316</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13066,44 +13014,44 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>625</v>
+        <v>622</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>626</v>
+        <v>623</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>141</v>
+        <v>318</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>320</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
       </c>
@@ -13139,34 +13087,34 @@
         <v>84</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>171</v>
+        <v>321</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>84</v>
+        <v>624</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>84</v>
@@ -13178,10 +13126,10 @@
         <v>84</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>84</v>
+        <v>323</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>165</v>
+        <v>324</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13192,10 +13140,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13206,7 +13154,7 @@
         <v>82</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>84</v>
@@ -13218,19 +13166,17 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>290</v>
+        <v>161</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>291</v>
+        <v>326</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>327</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>294</v>
+        <v>328</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>84</v>
@@ -13279,13 +13225,13 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>295</v>
+        <v>329</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>84</v>
@@ -13306,10 +13252,10 @@
         <v>84</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>297</v>
+        <v>331</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>298</v>
+        <v>332</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13320,10 +13266,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13343,19 +13289,23 @@
         <v>84</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>161</v>
+        <v>334</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>162</v>
+        <v>335</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>336</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>338</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
       </c>
@@ -13403,7 +13353,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>164</v>
+        <v>339</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13415,7 +13365,7 @@
         <v>84</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>84</v>
@@ -13430,10 +13380,10 @@
         <v>84</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>84</v>
+        <v>340</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>165</v>
+        <v>341</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13444,21 +13394,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>139</v>
+        <v>84</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>84</v>
@@ -13467,21 +13417,23 @@
         <v>84</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>141</v>
+        <v>343</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>167</v>
+        <v>344</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>345</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>346</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
       </c>
@@ -13517,31 +13469,31 @@
         <v>84</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>168</v>
+        <v>84</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>170</v>
+        <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>171</v>
+        <v>347</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>145</v>
+        <v>106</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>84</v>
@@ -13556,10 +13508,10 @@
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>84</v>
+        <v>348</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>165</v>
+        <v>349</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13570,10 +13522,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>634</v>
+        <v>584</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13587,7 +13539,7 @@
         <v>94</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>84</v>
@@ -13596,19 +13548,19 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>108</v>
+        <v>420</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>302</v>
+        <v>585</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>303</v>
+        <v>586</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>304</v>
+        <v>587</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>305</v>
+        <v>424</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -13618,7 +13570,7 @@
         <v>84</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>635</v>
+        <v>84</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>84</v>
@@ -13645,19 +13597,17 @@
         <v>84</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC89" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>386</v>
+      </c>
+      <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>84</v>
+        <v>170</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>306</v>
+        <v>584</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13672,7 +13622,7 @@
         <v>106</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>636</v>
+        <v>84</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>84</v>
@@ -13681,29 +13631,31 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>84</v>
+        <v>588</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>308</v>
+        <v>428</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>309</v>
+        <v>429</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>84</v>
+        <v>430</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>638</v>
-      </c>
-      <c r="C90" s="2"/>
+        <v>584</v>
+      </c>
+      <c r="C90" t="s" s="2">
+        <v>633</v>
+      </c>
       <c r="D90" t="s" s="2">
         <v>84</v>
       </c>
@@ -13715,7 +13667,7 @@
         <v>94</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>84</v>
@@ -13727,15 +13679,17 @@
         <v>161</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>311</v>
+        <v>585</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>312</v>
+        <v>586</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>587</v>
+      </c>
+      <c r="O90" t="s" s="2">
+        <v>424</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
       </c>
@@ -13783,7 +13737,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>314</v>
+        <v>584</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13798,7 +13752,7 @@
         <v>106</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>84</v>
+        <v>634</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>84</v>
@@ -13807,27 +13761,27 @@
         <v>84</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>84</v>
+        <v>588</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>315</v>
+        <v>428</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>316</v>
+        <v>429</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>84</v>
+        <v>430</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>640</v>
+        <v>589</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13841,26 +13795,28 @@
         <v>94</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>114</v>
+        <v>183</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>318</v>
+        <v>590</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>591</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>592</v>
+      </c>
       <c r="O91" t="s" s="2">
-        <v>320</v>
+        <v>435</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -13885,13 +13841,13 @@
         <v>84</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>84</v>
+        <v>593</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>84</v>
+        <v>436</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>84</v>
@@ -13909,7 +13865,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>321</v>
+        <v>589</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -13918,13 +13874,13 @@
         <v>94</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>84</v>
+        <v>594</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>641</v>
+        <v>84</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>84</v>
@@ -13936,10 +13892,10 @@
         <v>84</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>323</v>
+        <v>137</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>324</v>
+        <v>438</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -13950,43 +13906,45 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>643</v>
+        <v>595</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>84</v>
+        <v>440</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>84</v>
       </c>
       <c r="J92" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>161</v>
+        <v>183</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>326</v>
+        <v>441</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="O92" t="s" s="2">
-        <v>328</v>
+        <v>444</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -14011,13 +13969,11 @@
         <v>84</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>84</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>84</v>
+        <v>637</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>84</v>
@@ -14035,13 +13991,13 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>329</v>
+        <v>595</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>84</v>
@@ -14050,7 +14006,7 @@
         <v>106</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>84</v>
+        <v>638</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>84</v>
@@ -14059,27 +14015,27 @@
         <v>84</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>84</v>
+        <v>447</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>331</v>
+        <v>448</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>332</v>
+        <v>449</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>84</v>
+        <v>450</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>644</v>
+        <v>639</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>645</v>
+        <v>596</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14090,7 +14046,7 @@
         <v>82</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>84</v>
@@ -14099,22 +14055,22 @@
         <v>84</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>334</v>
+        <v>85</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>335</v>
+        <v>597</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>336</v>
+        <v>598</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>337</v>
+        <v>505</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>338</v>
+        <v>506</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14163,13 +14119,13 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>339</v>
+        <v>596</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>84</v>
@@ -14190,786 +14146,20 @@
         <v>84</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>340</v>
+        <v>508</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>341</v>
+        <v>509</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR93" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="94" hidden="true">
-      <c r="A94" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="B94" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="C94" s="2"/>
-      <c r="D94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E94" s="2"/>
-      <c r="F94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G94" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J94" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K94" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L94" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="M94" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="P94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q94" s="2"/>
-      <c r="R94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF94" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="AG94" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH94" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ94" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AP94" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AQ94" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR94" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="95" hidden="true">
-      <c r="A95" t="s" s="2">
-        <v>648</v>
-      </c>
-      <c r="B95" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C95" s="2"/>
-      <c r="D95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E95" s="2"/>
-      <c r="F95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G95" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J95" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K95" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="L95" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="M95" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="O95" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="P95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q95" s="2"/>
-      <c r="R95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB95" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AC95" s="2"/>
-      <c r="AD95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE95" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="AF95" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="AG95" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH95" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ95" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="AO95" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AP95" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AQ95" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR95" t="s" s="2">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>649</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="D96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="P96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>650</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR96" t="s" s="2">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>651</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR97" t="s" s="2">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>652</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y98" s="2"/>
-      <c r="Z98" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>654</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AQ98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR98" t="s" s="2">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>655</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AQ99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AR99" t="s" s="2">
         <v>84</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AR99">
+  <autoFilter ref="A1:AR93">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14979,7 +14169,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI98">
+  <conditionalFormatting sqref="A2:AI92">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1106,7 +1106,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
 </t>
   </si>
   <si>
@@ -1291,7 +1291,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization|http://va.gov/fhir/StructureDefinition/Practitioner)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1519,7 +1519,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologySpecimen)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1106,7 +1106,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Patient)
+    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/core/StructureDefinition/us-core-patient)
 </t>
   </si>
   <si>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3789" uniqueCount="640">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3789" uniqueCount="641">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1382,6 +1382,9 @@
   <si>
     <t>obs-6
 us-core-2</t>
+  </si>
+  <si>
+    <t>null: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>
@@ -8052,7 +8055,7 @@
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>84</v>
+        <v>438</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>84</v>
@@ -8067,7 +8070,7 @@
         <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8078,14 +8081,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -8107,16 +8110,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8144,10 +8147,10 @@
         <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8165,7 +8168,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8189,27 +8192,27 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8232,19 +8235,19 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8293,7 +8296,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8308,10 +8311,10 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>84</v>
@@ -8320,10 +8323,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8334,10 +8337,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8363,13 +8366,13 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8395,13 +8398,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8419,7 +8422,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8443,27 +8446,27 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8489,16 +8492,16 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8523,13 +8526,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8547,7 +8550,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8574,10 +8577,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8588,10 +8591,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8614,16 +8617,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8673,7 +8676,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8688,36 +8691,36 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8740,16 +8743,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8799,7 +8802,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8823,27 +8826,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8866,19 +8869,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8927,7 +8930,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8939,7 +8942,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8954,10 +8957,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8968,10 +8971,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9092,10 +9095,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9218,14 +9221,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9247,10 +9250,10 @@
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
@@ -9305,7 +9308,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9346,10 +9349,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9372,13 +9375,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9429,7 +9432,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9438,7 +9441,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9456,10 +9459,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9470,10 +9473,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9496,13 +9499,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9553,7 +9556,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9562,7 +9565,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9580,10 +9583,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9594,10 +9597,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9623,16 +9626,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9660,10 +9663,10 @@
         <v>118</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9681,7 +9684,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9705,13 +9708,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9722,10 +9725,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9751,16 +9754,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9785,13 +9788,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9809,7 +9812,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9833,13 +9836,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9850,10 +9853,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9876,17 +9879,17 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9935,7 +9938,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9965,7 +9968,7 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9976,10 +9979,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10005,10 +10008,10 @@
         <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10059,7 +10062,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10086,10 +10089,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10100,10 +10103,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10126,16 +10129,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10185,7 +10188,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10212,10 +10215,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10226,10 +10229,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10252,16 +10255,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10311,7 +10314,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10338,10 +10341,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10352,10 +10355,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10378,19 +10381,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10427,7 +10430,7 @@
         <v>84</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
@@ -10437,7 +10440,7 @@
         <v>170</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10464,10 +10467,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10478,10 +10481,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10602,10 +10605,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10728,14 +10731,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10757,10 +10760,10 @@
         <v>140</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>143</v>
@@ -10815,7 +10818,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10856,10 +10859,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10885,13 +10888,13 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>278</v>
@@ -10919,10 +10922,10 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>280</v>
@@ -10943,7 +10946,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>94</v>
@@ -10967,7 +10970,7 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>283</v>
@@ -10984,10 +10987,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11013,13 +11016,13 @@
         <v>420</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O69" t="s" s="2">
         <v>424</v>
@@ -11071,7 +11074,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11095,7 +11098,7 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>428</v>
@@ -11112,10 +11115,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11141,13 +11144,13 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O70" t="s" s="2">
         <v>435</v>
@@ -11178,7 +11181,7 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="Z70" t="s" s="2">
         <v>436</v>
@@ -11199,7 +11202,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11208,7 +11211,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11229,7 +11232,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11240,14 +11243,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11269,16 +11272,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11306,10 +11309,10 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11327,7 +11330,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11351,27 +11354,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11397,16 +11400,16 @@
         <v>85</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11455,7 +11458,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11482,10 +11485,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11496,13 +11499,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>84</v>
@@ -11524,19 +11527,19 @@
         <v>95</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
@@ -11585,7 +11588,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11612,10 +11615,10 @@
         <v>84</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11626,10 +11629,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11750,10 +11753,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11876,14 +11879,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11905,10 +11908,10 @@
         <v>140</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>143</v>
@@ -11963,7 +11966,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12004,10 +12007,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12033,13 +12036,13 @@
         <v>183</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="O77" t="s" s="2">
         <v>278</v>
@@ -12067,10 +12070,10 @@
         <v>84</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="Z77" t="s" s="2">
         <v>280</v>
@@ -12091,7 +12094,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>94</v>
@@ -12106,7 +12109,7 @@
         <v>106</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>84</v>
@@ -12115,7 +12118,7 @@
         <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>283</v>
@@ -12132,10 +12135,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12256,10 +12259,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12382,10 +12385,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12510,10 +12513,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12634,10 +12637,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12760,10 +12763,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12808,7 +12811,7 @@
         <v>84</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>84</v>
@@ -12862,7 +12865,7 @@
         <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>84</v>
@@ -12888,10 +12891,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13014,10 +13017,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13114,7 +13117,7 @@
         <v>106</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>84</v>
@@ -13140,10 +13143,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13266,10 +13269,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13394,10 +13397,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13522,10 +13525,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13551,13 +13554,13 @@
         <v>420</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O89" t="s" s="2">
         <v>424</v>
@@ -13607,7 +13610,7 @@
         <v>170</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13631,7 +13634,7 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>428</v>
@@ -13648,13 +13651,13 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>84</v>
@@ -13679,13 +13682,13 @@
         <v>161</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O90" t="s" s="2">
         <v>424</v>
@@ -13737,7 +13740,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13752,7 +13755,7 @@
         <v>106</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>84</v>
@@ -13761,7 +13764,7 @@
         <v>84</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>428</v>
@@ -13778,10 +13781,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13807,13 +13810,13 @@
         <v>183</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O91" t="s" s="2">
         <v>435</v>
@@ -13844,7 +13847,7 @@
         <v>188</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="Z91" t="s" s="2">
         <v>436</v>
@@ -13865,7 +13868,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -13874,7 +13877,7 @@
         <v>94</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>106</v>
@@ -13895,7 +13898,7 @@
         <v>137</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -13906,14 +13909,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13935,16 +13938,16 @@
         <v>183</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -13973,7 +13976,7 @@
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>84</v>
@@ -13991,7 +13994,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14006,7 +14009,7 @@
         <v>106</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>84</v>
@@ -14015,27 +14018,27 @@
         <v>84</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14061,16 +14064,16 @@
         <v>85</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14119,7 +14122,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14146,10 +14149,10 @@
         <v>84</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1384,7 +1384,7 @@
 us-core-2</t>
   </si>
   <si>
-    <t>null: target not supported</t>
+    <t>2031: target not supported</t>
   </si>
   <si>
     <t>value.nullFlavor</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -797,7 +797,7 @@
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFLabObservationStatus</t>
+    <t>http://va.gov/fhir/ValueSet/LabObservationStatus</t>
   </si>
   <si>
     <t>1488: terminologyMaps using VF_LabObservationStatus on MICROBIOLOGY - BACT RPT STATUS (63.05-11.5)</t>
@@ -2008,7 +2008,7 @@
     <t>Observation.component:va-component.interpretation</t>
   </si>
   <si>
-    <t>http://va.gov/fhir/ValueSet/VSVFAntibioticSensitivityInterpretation</t>
+    <t>http://va.gov/fhir/ValueSet/AntibioticSensitivityInterpretation</t>
   </si>
   <si>
     <t>1524: terminologyMaps using VF_AntibioticSensitivityInterpretation on MICROBIOLOGY - ORGANISM &gt; ORGANISM - * INTERPR (63.05-12 &gt; 63.3-5.1+to+160.1)</t>
@@ -2359,7 +2359,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="61.58203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="56.85546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3789" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3789" uniqueCount="642">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -971,6 +971,10 @@
   </si>
   <si>
     <t>Coding.system</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+LabObservationMicrobiologyBacteriologyObservation-1480-1:if Not NULL then fixed value http://loinc.org {null}</t>
   </si>
   <si>
     <t>1480-1: fixed value = http://loinc.org case Not NULL</t>
@@ -6274,10 +6278,10 @@
         <v>84</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>106</v>
+        <v>307</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>84</v>
@@ -6289,10 +6293,10 @@
         <v>84</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AQ31" t="s" s="2">
         <v>84</v>
@@ -6303,10 +6307,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6332,13 +6336,13 @@
         <v>161</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6388,7 +6392,7 @@
         <v>84</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>82</v>
@@ -6415,10 +6419,10 @@
         <v>84</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AQ32" t="s" s="2">
         <v>84</v>
@@ -6429,10 +6433,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6458,14 +6462,14 @@
         <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>84</v>
@@ -6514,7 +6518,7 @@
         <v>84</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>82</v>
@@ -6529,7 +6533,7 @@
         <v>106</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>84</v>
@@ -6541,10 +6545,10 @@
         <v>84</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AQ33" t="s" s="2">
         <v>84</v>
@@ -6555,10 +6559,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6584,14 +6588,14 @@
         <v>161</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>84</v>
@@ -6640,7 +6644,7 @@
         <v>84</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>82</v>
@@ -6655,7 +6659,7 @@
         <v>106</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>84</v>
@@ -6667,10 +6671,10 @@
         <v>84</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AQ34" t="s" s="2">
         <v>84</v>
@@ -6681,10 +6685,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6707,19 +6711,19 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>84</v>
@@ -6768,7 +6772,7 @@
         <v>84</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>82</v>
@@ -6795,10 +6799,10 @@
         <v>84</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AQ35" t="s" s="2">
         <v>84</v>
@@ -6809,10 +6813,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6838,16 +6842,16 @@
         <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>84</v>
@@ -6896,7 +6900,7 @@
         <v>84</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>82</v>
@@ -6923,10 +6927,10 @@
         <v>84</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AQ36" t="s" s="2">
         <v>84</v>
@@ -6937,10 +6941,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6963,19 +6967,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>84</v>
@@ -7024,7 +7028,7 @@
         <v>84</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>82</v>
@@ -7039,25 +7043,25 @@
         <v>106</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AR37" t="s" s="2">
         <v>84</v>
@@ -7065,10 +7069,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7091,16 +7095,16 @@
         <v>95</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7150,7 +7154,7 @@
         <v>84</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>82</v>
@@ -7180,10 +7184,10 @@
         <v>283</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AR38" t="s" s="2">
         <v>84</v>
@@ -7191,14 +7195,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7217,19 +7221,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>84</v>
@@ -7278,7 +7282,7 @@
         <v>84</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>82</v>
@@ -7299,19 +7303,19 @@
         <v>84</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AR39" t="s" s="2">
         <v>84</v>
@@ -7319,14 +7323,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7345,19 +7349,19 @@
         <v>95</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>84</v>
@@ -7394,7 +7398,7 @@
         <v>84</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7404,7 +7408,7 @@
         <v>170</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>82</v>
@@ -7413,10 +7417,10 @@
         <v>94</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>84</v>
@@ -7425,19 +7429,19 @@
         <v>84</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AR40" t="s" s="2">
         <v>84</v>
@@ -7445,16 +7449,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7473,19 +7477,19 @@
         <v>95</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>84</v>
@@ -7534,7 +7538,7 @@
         <v>84</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>82</v>
@@ -7543,31 +7547,31 @@
         <v>94</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AR41" t="s" s="2">
         <v>84</v>
@@ -7575,10 +7579,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7601,16 +7605,16 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7660,7 +7664,7 @@
         <v>84</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>82</v>
@@ -7675,10 +7679,10 @@
         <v>106</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>84</v>
@@ -7687,13 +7691,13 @@
         <v>84</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AR42" t="s" s="2">
         <v>84</v>
@@ -7701,10 +7705,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7727,17 +7731,17 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>84</v>
@@ -7786,7 +7790,7 @@
         <v>84</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>82</v>
@@ -7801,25 +7805,25 @@
         <v>106</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AR43" t="s" s="2">
         <v>84</v>
@@ -7827,10 +7831,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7853,19 +7857,19 @@
         <v>95</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>84</v>
@@ -7914,7 +7918,7 @@
         <v>84</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>82</v>
@@ -7923,10 +7927,10 @@
         <v>94</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>84</v>
@@ -7938,27 +7942,27 @@
         <v>84</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AQ44" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7984,16 +7988,16 @@
         <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>84</v>
@@ -8022,7 +8026,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>84</v>
@@ -8040,7 +8044,7 @@
         <v>84</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>82</v>
@@ -8049,13 +8053,13 @@
         <v>94</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>106</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>84</v>
@@ -8070,7 +8074,7 @@
         <v>137</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AQ45" t="s" s="2">
         <v>84</v>
@@ -8081,14 +8085,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -8110,16 +8114,16 @@
         <v>183</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>84</v>
@@ -8147,10 +8151,10 @@
         <v>188</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>84</v>
@@ -8168,7 +8172,7 @@
         <v>84</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>82</v>
@@ -8192,27 +8196,27 @@
         <v>84</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AQ46" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR46" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8235,19 +8239,19 @@
         <v>84</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>84</v>
@@ -8296,7 +8300,7 @@
         <v>84</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>82</v>
@@ -8311,10 +8315,10 @@
         <v>106</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>84</v>
@@ -8323,10 +8327,10 @@
         <v>84</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AQ47" t="s" s="2">
         <v>84</v>
@@ -8337,10 +8341,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8366,13 +8370,13 @@
         <v>183</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8398,13 +8402,13 @@
         <v>84</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>84</v>
@@ -8422,7 +8426,7 @@
         <v>84</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>82</v>
@@ -8446,27 +8450,27 @@
         <v>84</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AQ48" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR48" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8492,16 +8496,16 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>84</v>
@@ -8526,13 +8530,13 @@
         <v>84</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>84</v>
@@ -8550,7 +8554,7 @@
         <v>84</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>82</v>
@@ -8577,10 +8581,10 @@
         <v>84</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AQ49" t="s" s="2">
         <v>84</v>
@@ -8591,10 +8595,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8617,16 +8621,16 @@
         <v>84</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8676,7 +8680,7 @@
         <v>84</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>82</v>
@@ -8691,36 +8695,36 @@
         <v>106</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AQ50" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR50" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8743,16 +8747,16 @@
         <v>84</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8802,7 +8806,7 @@
         <v>84</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>82</v>
@@ -8826,27 +8830,27 @@
         <v>84</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AQ51" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR51" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8869,19 +8873,19 @@
         <v>84</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>84</v>
@@ -8930,7 +8934,7 @@
         <v>84</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>82</v>
@@ -8942,7 +8946,7 @@
         <v>84</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>84</v>
@@ -8957,10 +8961,10 @@
         <v>84</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ52" t="s" s="2">
         <v>84</v>
@@ -8971,10 +8975,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9095,10 +9099,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9221,14 +9225,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9250,10 +9254,10 @@
         <v>140</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>143</v>
@@ -9308,7 +9312,7 @@
         <v>84</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>82</v>
@@ -9349,10 +9353,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9375,13 +9379,13 @@
         <v>84</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9432,7 +9436,7 @@
         <v>84</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>82</v>
@@ -9441,7 +9445,7 @@
         <v>94</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>106</v>
@@ -9459,10 +9463,10 @@
         <v>84</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AQ56" t="s" s="2">
         <v>84</v>
@@ -9473,10 +9477,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9499,13 +9503,13 @@
         <v>84</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9556,7 +9560,7 @@
         <v>84</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>82</v>
@@ -9565,7 +9569,7 @@
         <v>94</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>106</v>
@@ -9583,10 +9587,10 @@
         <v>84</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AQ57" t="s" s="2">
         <v>84</v>
@@ -9597,10 +9601,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9626,16 +9630,16 @@
         <v>183</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>84</v>
@@ -9663,10 +9667,10 @@
         <v>118</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>84</v>
@@ -9684,7 +9688,7 @@
         <v>84</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>82</v>
@@ -9708,13 +9712,13 @@
         <v>84</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AQ58" t="s" s="2">
         <v>84</v>
@@ -9725,10 +9729,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9754,16 +9758,16 @@
         <v>183</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>84</v>
@@ -9788,13 +9792,13 @@
         <v>84</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>84</v>
@@ -9812,7 +9816,7 @@
         <v>84</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>82</v>
@@ -9836,13 +9840,13 @@
         <v>84</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AQ59" t="s" s="2">
         <v>84</v>
@@ -9853,10 +9857,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9879,17 +9883,17 @@
         <v>84</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>84</v>
@@ -9938,7 +9942,7 @@
         <v>84</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>82</v>
@@ -9968,7 +9972,7 @@
         <v>84</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="AQ60" t="s" s="2">
         <v>84</v>
@@ -9979,10 +9983,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10008,10 +10012,10 @@
         <v>161</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10062,7 +10066,7 @@
         <v>84</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>82</v>
@@ -10089,10 +10093,10 @@
         <v>84</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AQ61" t="s" s="2">
         <v>84</v>
@@ -10103,10 +10107,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10129,16 +10133,16 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10188,7 +10192,7 @@
         <v>84</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>82</v>
@@ -10215,10 +10219,10 @@
         <v>84</v>
       </c>
       <c r="AO62" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AQ62" t="s" s="2">
         <v>84</v>
@@ -10229,10 +10233,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10255,16 +10259,16 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10314,7 +10318,7 @@
         <v>84</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>82</v>
@@ -10341,10 +10345,10 @@
         <v>84</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AQ63" t="s" s="2">
         <v>84</v>
@@ -10355,10 +10359,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10381,19 +10385,19 @@
         <v>95</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>84</v>
@@ -10430,7 +10434,7 @@
         <v>84</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
@@ -10440,7 +10444,7 @@
         <v>170</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>82</v>
@@ -10467,10 +10471,10 @@
         <v>84</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AQ64" t="s" s="2">
         <v>84</v>
@@ -10481,10 +10485,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10605,10 +10609,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10731,14 +10735,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10760,10 +10764,10 @@
         <v>140</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>143</v>
@@ -10818,7 +10822,7 @@
         <v>84</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>82</v>
@@ -10859,10 +10863,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10888,13 +10892,13 @@
         <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O68" t="s" s="2">
         <v>278</v>
@@ -10922,10 +10926,10 @@
         <v>84</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z68" t="s" s="2">
         <v>280</v>
@@ -10946,7 +10950,7 @@
         <v>84</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>94</v>
@@ -10970,7 +10974,7 @@
         <v>84</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>283</v>
@@ -10987,10 +10991,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11013,19 +11017,19 @@
         <v>95</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>84</v>
@@ -11074,7 +11078,7 @@
         <v>84</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>82</v>
@@ -11098,27 +11102,27 @@
         <v>84</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AQ69" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR69" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11144,16 +11148,16 @@
         <v>183</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>84</v>
@@ -11181,10 +11185,10 @@
         <v>188</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>84</v>
@@ -11202,7 +11206,7 @@
         <v>84</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>82</v>
@@ -11211,7 +11215,7 @@
         <v>94</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>106</v>
@@ -11232,7 +11236,7 @@
         <v>137</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AQ70" t="s" s="2">
         <v>84</v>
@@ -11243,14 +11247,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11272,16 +11276,16 @@
         <v>183</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>84</v>
@@ -11309,10 +11313,10 @@
         <v>188</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>84</v>
@@ -11330,7 +11334,7 @@
         <v>84</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>82</v>
@@ -11354,27 +11358,27 @@
         <v>84</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AQ71" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR71" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11400,16 +11404,16 @@
         <v>85</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>84</v>
@@ -11458,7 +11462,7 @@
         <v>84</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>82</v>
@@ -11485,10 +11489,10 @@
         <v>84</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ72" t="s" s="2">
         <v>84</v>
@@ -11499,13 +11503,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>84</v>
@@ -11527,19 +11531,19 @@
         <v>95</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>84</v>
@@ -11588,7 +11592,7 @@
         <v>84</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>82</v>
@@ -11615,10 +11619,10 @@
         <v>84</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AQ73" t="s" s="2">
         <v>84</v>
@@ -11629,10 +11633,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11753,10 +11757,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11879,14 +11883,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -11908,10 +11912,10 @@
         <v>140</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>143</v>
@@ -11966,7 +11970,7 @@
         <v>84</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>82</v>
@@ -12007,10 +12011,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12036,13 +12040,13 @@
         <v>183</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O77" t="s" s="2">
         <v>278</v>
@@ -12070,10 +12074,10 @@
         <v>84</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="Z77" t="s" s="2">
         <v>280</v>
@@ -12094,7 +12098,7 @@
         <v>84</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>94</v>
@@ -12109,7 +12113,7 @@
         <v>106</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>84</v>
@@ -12118,7 +12122,7 @@
         <v>84</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>283</v>
@@ -12135,10 +12139,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12259,10 +12263,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12385,10 +12389,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12513,10 +12517,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12637,10 +12641,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12763,10 +12767,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12811,7 +12815,7 @@
         <v>84</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>84</v>
@@ -12865,7 +12869,7 @@
         <v>106</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>84</v>
@@ -12877,10 +12881,10 @@
         <v>84</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AQ83" t="s" s="2">
         <v>84</v>
@@ -12891,10 +12895,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12920,13 +12924,13 @@
         <v>161</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12976,7 +12980,7 @@
         <v>84</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>82</v>
@@ -13003,10 +13007,10 @@
         <v>84</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AQ84" t="s" s="2">
         <v>84</v>
@@ -13017,10 +13021,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13046,14 +13050,14 @@
         <v>114</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>84</v>
@@ -13102,7 +13106,7 @@
         <v>84</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>82</v>
@@ -13117,7 +13121,7 @@
         <v>106</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>84</v>
@@ -13129,10 +13133,10 @@
         <v>84</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AQ85" t="s" s="2">
         <v>84</v>
@@ -13143,10 +13147,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13172,14 +13176,14 @@
         <v>161</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>84</v>
@@ -13228,7 +13232,7 @@
         <v>84</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>82</v>
@@ -13255,10 +13259,10 @@
         <v>84</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AQ86" t="s" s="2">
         <v>84</v>
@@ -13269,10 +13273,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13295,19 +13299,19 @@
         <v>95</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>84</v>
@@ -13356,7 +13360,7 @@
         <v>84</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>82</v>
@@ -13383,10 +13387,10 @@
         <v>84</v>
       </c>
       <c r="AO87" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AQ87" t="s" s="2">
         <v>84</v>
@@ -13397,10 +13401,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13426,16 +13430,16 @@
         <v>161</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>84</v>
@@ -13484,7 +13488,7 @@
         <v>84</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>82</v>
@@ -13511,10 +13515,10 @@
         <v>84</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AQ88" t="s" s="2">
         <v>84</v>
@@ -13525,10 +13529,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13551,19 +13555,19 @@
         <v>95</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>84</v>
@@ -13600,7 +13604,7 @@
         <v>84</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
@@ -13610,7 +13614,7 @@
         <v>170</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>82</v>
@@ -13634,30 +13638,30 @@
         <v>84</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AQ89" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR89" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>84</v>
@@ -13682,16 +13686,16 @@
         <v>161</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>84</v>
@@ -13740,7 +13744,7 @@
         <v>84</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>82</v>
@@ -13755,7 +13759,7 @@
         <v>106</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>84</v>
@@ -13764,27 +13768,27 @@
         <v>84</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AQ90" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR90" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13810,16 +13814,16 @@
         <v>183</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>84</v>
@@ -13847,10 +13851,10 @@
         <v>188</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>84</v>
@@ -13868,7 +13872,7 @@
         <v>84</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>82</v>
@@ -13877,7 +13881,7 @@
         <v>94</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>106</v>
@@ -13898,7 +13902,7 @@
         <v>137</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AQ91" t="s" s="2">
         <v>84</v>
@@ -13909,14 +13913,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13938,16 +13942,16 @@
         <v>183</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>84</v>
@@ -13976,7 +13980,7 @@
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>84</v>
@@ -13994,7 +13998,7 @@
         <v>84</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>82</v>
@@ -14009,7 +14013,7 @@
         <v>106</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>84</v>
@@ -14018,27 +14022,27 @@
         <v>84</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AQ92" t="s" s="2">
         <v>84</v>
       </c>
       <c r="AR92" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14064,16 +14068,16 @@
         <v>85</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>84</v>
@@ -14122,7 +14126,7 @@
         <v>84</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>82</v>
@@ -14149,10 +14153,10 @@
         <v>84</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AQ93" t="s" s="2">
         <v>84</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -974,7 +974,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-LabObservationMicrobiologyBacteriologyObservation-1480-1:if Not NULL then fixed value http://loinc.org {null}</t>
+lombo-49-1480-1:undefined: if Not NULL then http://loinc.org {null}</t>
   </si>
   <si>
     <t>1480-1: fixed value = http://loinc.org case Not NULL</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1135,7 +1135,8 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn</t>
+    <t>demographics.lrdfn
+accession.collected</t>
   </si>
   <si>
     <t>Event.subject</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,7 +243,7 @@
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
-    <t>Mapping: Virtual Patient Record (VPR)</t>
+    <t>Mapping: Summary Document Architecure (SDA)</t>
   </si>
   <si>
     <t>Mapping: Workflow Pattern</t>
@@ -2382,7 +2382,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="40.984375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3882" uniqueCount="644">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3882" uniqueCount="648">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -807,6 +807,9 @@
   </si>
   <si>
     <t>Micro.Microbiology.BacteriologyReportStatus</t>
+  </si>
+  <si>
+    <t>Documents.DocumentCompletionStatus,LabOrder.Result.ResultStatus</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -1135,8 +1138,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>demographics.lrdfn
-accession.collected</t>
+    <t>Patient.PatientExtension.VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1290,6 +1292,9 @@
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
   </si>
   <si>
+    <t>Documents.ToTime,LabOrder.Result.ResultTime</t>
+  </si>
+  <si>
     <t>OBR.22 (or MSH.7), or perhaps OBX-19 (depends on who observation made)</t>
   </si>
   <si>
@@ -1321,6 +1326,9 @@
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
+    <t>Documents.Clinician,Documents.DocumentExtension.CareProviders,LabOrder.Result.VerifiedBy</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1550,6 +1558,9 @@
   </si>
   <si>
     <t>Micro.Microbiology.MicrobiologyAccession</t>
+  </si>
+  <si>
+    <t>LabOrder.ResultExtension.GroupName</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -2382,7 +2393,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="51.63671875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="88.89453125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>
@@ -5218,22 +5229,22 @@
         <v>254</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>85</v>
+        <v>255</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AS22" t="s" s="2">
         <v>85</v>
@@ -5241,10 +5252,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5270,16 +5281,16 @@
         <v>184</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>85</v>
@@ -5289,7 +5300,7 @@
         <v>85</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>85</v>
@@ -5307,16 +5318,16 @@
         <v>119</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5326,7 +5337,7 @@
         <v>171</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -5341,7 +5352,7 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>85</v>
@@ -5359,10 +5370,10 @@
         <v>85</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -5370,13 +5381,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>85</v>
@@ -5401,16 +5412,16 @@
         <v>184</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>85</v>
@@ -5420,7 +5431,7 @@
         <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>85</v>
@@ -5438,10 +5449,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5459,7 +5470,7 @@
         <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5492,10 +5503,10 @@
         <v>85</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>85</v>
@@ -5503,14 +5514,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5532,16 +5543,16 @@
         <v>184</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>85</v>
@@ -5569,10 +5580,10 @@
         <v>189</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>85</v>
@@ -5590,7 +5601,7 @@
         <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>95</v>
@@ -5614,30 +5625,30 @@
         <v>85</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5761,10 +5772,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5890,10 +5901,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5916,19 +5927,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>85</v>
@@ -5977,7 +5988,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -5992,7 +6003,7 @@
         <v>107</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>85</v>
@@ -6007,10 +6018,10 @@
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -6021,10 +6032,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6148,10 +6159,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6277,10 +6288,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6306,16 +6317,16 @@
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>85</v>
@@ -6364,7 +6375,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6376,10 +6387,10 @@
         <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>85</v>
@@ -6394,10 +6405,10 @@
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -6408,10 +6419,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6437,13 +6448,13 @@
         <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6493,7 +6504,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6523,10 +6534,10 @@
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>85</v>
@@ -6537,10 +6548,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6566,14 +6577,14 @@
         <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6622,7 +6633,7 @@
         <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6637,7 +6648,7 @@
         <v>107</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>85</v>
@@ -6652,10 +6663,10 @@
         <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
@@ -6666,10 +6677,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6695,14 +6706,14 @@
         <v>162</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6751,7 +6762,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6766,7 +6777,7 @@
         <v>107</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>85</v>
@@ -6781,10 +6792,10 @@
         <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
@@ -6795,10 +6806,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6821,19 +6832,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6882,7 +6893,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6912,10 +6923,10 @@
         <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
@@ -6926,10 +6937,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6955,16 +6966,16 @@
         <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -7013,7 +7024,7 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -7043,10 +7054,10 @@
         <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
@@ -7057,10 +7068,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7083,19 +7094,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -7144,7 +7155,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7159,28 +7170,28 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AS37" t="s" s="2">
         <v>85</v>
@@ -7188,10 +7199,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7214,16 +7225,16 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7273,7 +7284,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7303,13 +7314,13 @@
         <v>85</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>85</v>
@@ -7317,14 +7328,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7343,19 +7354,19 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7404,7 +7415,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7428,19 +7439,19 @@
         <v>85</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>85</v>
@@ -7448,14 +7459,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7474,19 +7485,19 @@
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7523,7 +7534,7 @@
         <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7533,7 +7544,7 @@
         <v>171</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7542,10 +7553,10 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>85</v>
@@ -7557,19 +7568,19 @@
         <v>85</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>85</v>
@@ -7577,16 +7588,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7605,19 +7616,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7666,7 +7677,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7675,34 +7686,34 @@
         <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>85</v>
@@ -7710,10 +7721,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7736,16 +7747,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7795,7 +7806,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7810,13 +7821,13 @@
         <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>85</v>
+        <v>409</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>85</v>
@@ -7825,13 +7836,13 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>85</v>
@@ -7839,10 +7850,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7865,17 +7876,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -7924,7 +7935,7 @@
         <v>85</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -7939,28 +7950,28 @@
         <v>107</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>85</v>
+        <v>420</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7968,10 +7979,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7994,19 +8005,19 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -8055,7 +8066,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -8064,10 +8075,10 @@
         <v>95</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>85</v>
@@ -8082,27 +8093,27 @@
         <v>85</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AR44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS44" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -8128,16 +8139,16 @@
         <v>184</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8166,7 +8177,7 @@
       </c>
       <c r="Y45" s="2"/>
       <c r="Z45" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>85</v>
@@ -8184,7 +8195,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8193,13 +8204,13 @@
         <v>95</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>85</v>
@@ -8217,7 +8228,7 @@
         <v>138</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AR45" t="s" s="2">
         <v>85</v>
@@ -8228,14 +8239,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -8257,16 +8268,16 @@
         <v>184</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8294,10 +8305,10 @@
         <v>189</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>85</v>
@@ -8315,7 +8326,7 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8342,27 +8353,27 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8385,19 +8396,19 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8446,7 +8457,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8461,10 +8472,10 @@
         <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>85</v>
@@ -8476,10 +8487,10 @@
         <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
@@ -8490,10 +8501,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8519,13 +8530,13 @@
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -8551,13 +8562,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8575,7 +8586,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8602,27 +8613,27 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8648,16 +8659,16 @@
         <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8682,13 +8693,13 @@
         <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8706,7 +8717,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8736,10 +8747,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -8750,10 +8761,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8776,16 +8787,16 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8835,7 +8846,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8850,39 +8861,39 @@
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>85</v>
+        <v>495</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8905,16 +8916,16 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8964,7 +8975,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -8991,27 +9002,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9034,19 +9045,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -9095,7 +9106,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9107,7 +9118,7 @@
         <v>85</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>85</v>
@@ -9125,10 +9136,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9139,10 +9150,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9266,10 +9277,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9395,14 +9406,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -9424,10 +9435,10 @@
         <v>141</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>144</v>
@@ -9482,7 +9493,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9526,10 +9537,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9552,13 +9563,13 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9609,7 +9620,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9618,7 +9629,7 @@
         <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>107</v>
@@ -9639,10 +9650,10 @@
         <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
@@ -9653,10 +9664,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9679,13 +9690,13 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9736,7 +9747,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9745,7 +9756,7 @@
         <v>95</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>107</v>
@@ -9766,10 +9777,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9780,10 +9791,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9809,16 +9820,16 @@
         <v>184</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>85</v>
@@ -9846,10 +9857,10 @@
         <v>119</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>85</v>
@@ -9867,7 +9878,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9894,13 +9905,13 @@
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9911,10 +9922,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9940,16 +9951,16 @@
         <v>184</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -9974,13 +9985,13 @@
         <v>85</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>85</v>
@@ -9998,7 +10009,7 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
@@ -10025,13 +10036,13 @@
         <v>85</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -10042,10 +10053,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10068,17 +10079,17 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -10127,7 +10138,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10160,7 +10171,7 @@
         <v>85</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10171,10 +10182,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10200,10 +10211,10 @@
         <v>162</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10254,7 +10265,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10284,10 +10295,10 @@
         <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10298,10 +10309,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10324,16 +10335,16 @@
         <v>96</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -10383,7 +10394,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10413,10 +10424,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10427,10 +10438,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10453,16 +10464,16 @@
         <v>96</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -10512,7 +10523,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10542,10 +10553,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10556,10 +10567,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10582,19 +10593,19 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
@@ -10631,7 +10642,7 @@
         <v>85</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
@@ -10641,7 +10652,7 @@
         <v>171</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10671,10 +10682,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10685,10 +10696,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10812,10 +10823,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10941,14 +10952,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10970,10 +10981,10 @@
         <v>141</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N67" t="s" s="2">
         <v>144</v>
@@ -11028,7 +11039,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11072,10 +11083,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11101,16 +11112,16 @@
         <v>184</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>85</v>
@@ -11135,31 +11146,31 @@
         <v>85</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF68" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="Z68" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AA68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE68" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF68" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>95</v>
@@ -11186,16 +11197,16 @@
         <v>85</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AS68" t="s" s="2">
         <v>85</v>
@@ -11203,10 +11214,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11229,19 +11240,19 @@
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11290,7 +11301,7 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11317,27 +11328,27 @@
         <v>85</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS69" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11363,16 +11374,16 @@
         <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11400,28 +11411,28 @@
         <v>189</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
@@ -11430,7 +11441,7 @@
         <v>95</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>107</v>
@@ -11454,7 +11465,7 @@
         <v>138</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
@@ -11465,14 +11476,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -11494,16 +11505,16 @@
         <v>184</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11531,10 +11542,10 @@
         <v>189</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11552,7 +11563,7 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
@@ -11579,27 +11590,27 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11625,16 +11636,16 @@
         <v>86</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11683,7 +11694,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11713,10 +11724,10 @@
         <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
@@ -11727,13 +11738,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>85</v>
@@ -11755,19 +11766,19 @@
         <v>96</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11816,7 +11827,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
@@ -11846,10 +11857,10 @@
         <v>85</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>85</v>
@@ -11860,10 +11871,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11987,10 +11998,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12116,14 +12127,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -12145,10 +12156,10 @@
         <v>141</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>144</v>
@@ -12203,7 +12214,7 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12247,10 +12258,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12276,16 +12287,16 @@
         <v>184</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>85</v>
@@ -12310,31 +12321,31 @@
         <v>85</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="Y77" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="Z77" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>95</v>
@@ -12349,7 +12360,7 @@
         <v>107</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>85</v>
@@ -12361,16 +12372,16 @@
         <v>85</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AS77" t="s" s="2">
         <v>85</v>
@@ -12378,10 +12389,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12505,10 +12516,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12634,10 +12645,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12660,19 +12671,19 @@
         <v>96</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>85</v>
@@ -12721,7 +12732,7 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
@@ -12751,10 +12762,10 @@
         <v>85</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>85</v>
@@ -12765,10 +12776,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12892,10 +12903,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13021,10 +13032,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13050,16 +13061,16 @@
         <v>109</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>85</v>
@@ -13069,7 +13080,7 @@
         <v>85</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>85</v>
@@ -13108,7 +13119,7 @@
         <v>85</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>83</v>
@@ -13123,7 +13134,7 @@
         <v>107</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>85</v>
@@ -13138,10 +13149,10 @@
         <v>85</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AR83" t="s" s="2">
         <v>85</v>
@@ -13152,10 +13163,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13181,13 +13192,13 @@
         <v>162</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -13237,7 +13248,7 @@
         <v>85</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -13267,10 +13278,10 @@
         <v>85</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>85</v>
@@ -13281,10 +13292,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13310,14 +13321,14 @@
         <v>115</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>85</v>
@@ -13366,7 +13377,7 @@
         <v>85</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
@@ -13381,7 +13392,7 @@
         <v>107</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>85</v>
@@ -13396,10 +13407,10 @@
         <v>85</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AR85" t="s" s="2">
         <v>85</v>
@@ -13410,10 +13421,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13439,14 +13450,14 @@
         <v>162</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>85</v>
@@ -13495,7 +13506,7 @@
         <v>85</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
@@ -13525,10 +13536,10 @@
         <v>85</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AR86" t="s" s="2">
         <v>85</v>
@@ -13539,10 +13550,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13565,19 +13576,19 @@
         <v>96</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>85</v>
@@ -13626,7 +13637,7 @@
         <v>85</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -13656,10 +13667,10 @@
         <v>85</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="AR87" t="s" s="2">
         <v>85</v>
@@ -13670,10 +13681,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13699,16 +13710,16 @@
         <v>162</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>85</v>
@@ -13757,7 +13768,7 @@
         <v>85</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -13787,10 +13798,10 @@
         <v>85</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>85</v>
@@ -13801,10 +13812,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13827,19 +13838,19 @@
         <v>96</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>85</v>
@@ -13876,7 +13887,7 @@
         <v>85</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AC89" s="2"/>
       <c r="AD89" t="s" s="2">
@@ -13886,7 +13897,7 @@
         <v>171</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -13913,30 +13924,30 @@
         <v>85</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS89" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C90" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="D90" t="s" s="2">
         <v>85</v>
@@ -13961,16 +13972,16 @@
         <v>162</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>85</v>
@@ -14019,7 +14030,7 @@
         <v>85</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
@@ -14034,7 +14045,7 @@
         <v>107</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>85</v>
@@ -14046,27 +14057,27 @@
         <v>85</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AR90" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS90" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14092,16 +14103,16 @@
         <v>184</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>85</v>
@@ -14129,28 +14140,28 @@
         <v>189</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF91" t="s" s="2">
         <v>597</v>
-      </c>
-      <c r="Z91" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="AA91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF91" t="s" s="2">
-        <v>593</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14159,7 +14170,7 @@
         <v>95</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>107</v>
@@ -14183,7 +14194,7 @@
         <v>138</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>85</v>
@@ -14194,14 +14205,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -14223,16 +14234,16 @@
         <v>184</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>85</v>
@@ -14261,7 +14272,7 @@
       </c>
       <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>85</v>
@@ -14279,7 +14290,7 @@
         <v>85</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -14294,7 +14305,7 @@
         <v>107</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>85</v>
@@ -14306,27 +14317,27 @@
         <v>85</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS92" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14352,16 +14363,16 @@
         <v>86</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>85</v>
@@ -14410,7 +14421,7 @@
         <v>85</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
@@ -14440,10 +14451,10 @@
         <v>85</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1138,7 +1138,7 @@
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
   </si>
   <si>
-    <t>Patient.PatientExtension.VeteranLrdfn</t>
+    <t>Patient.Extension[PatientExtension].VeteranLrdfn</t>
   </si>
   <si>
     <t>Event.subject</t>
@@ -1326,7 +1326,7 @@
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
   </si>
   <si>
-    <t>Documents.Clinician,Documents.DocumentExtension.CareProviders,LabOrder.Result.VerifiedBy</t>
+    <t>Documents.Clinician,Documents.Extension[DocumentExtension].CareProviders,LabOrder.Result.VerifiedBy</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1560,7 +1560,7 @@
     <t>Micro.Microbiology.MicrobiologyAccession</t>
   </si>
   <si>
-    <t>LabOrder.ResultExtension.GroupName</t>
+    <t>LabOrder.Extension[ResultExtension].GroupName</t>
   </si>
   <si>
     <t>&lt; 123038009 |Specimen|</t>
@@ -2393,7 +2393,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="88.89453125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="99.32421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="247.40625" customWidth="true" bestFit="true"/>
     <col min="42" max="42" width="255.0" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$99</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3882" uniqueCount="648">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4132" uniqueCount="670">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab</t>
+    <t>This StructureDefinition contains the maps for VistA file MICROBIOLOGY (63.05) to us-core-observation-lab.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1307,7 +1307,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization|http://va.gov/fhir/StructureDefinition/Practitioner)
+    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
 </t>
   </si>
   <si>
@@ -1320,6 +1320,47 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t>Event.performer.actor</t>
+  </si>
+  <si>
+    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
+  </si>
+  <si>
+    <t>participation[typeCode=PRF]</t>
+  </si>
+  <si>
+    <t>FiveWs.actor</t>
+  </si>
+  <si>
+    <t>Observation.performer:va-at</t>
+  </si>
+  <si>
+    <t>va-at</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Organization)
+</t>
+  </si>
+  <si>
+    <t>1464: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
+  </si>
+  <si>
+    <t>Micro.Microbiology.AccessioningInstitutionIEN</t>
+  </si>
+  <si>
+    <t>Documents.EnteredAt,LabOrder.Result.EnteredAt</t>
+  </si>
+  <si>
+    <t>Observation.performer:va-by</t>
+  </si>
+  <si>
+    <t>va-by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/Practitioner)
+</t>
+  </si>
+  <si>
     <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
   </si>
   <si>
@@ -1327,18 +1368,6 @@
   </si>
   <si>
     <t>Documents.Clinician,Documents.Extension[DocumentExtension].CareProviders,LabOrder.Result.VerifiedBy</t>
-  </si>
-  <si>
-    <t>Event.performer.actor</t>
-  </si>
-  <si>
-    <t>OBX.15 / (Practitioner)  OBX-16,  PRT-5:PRT-4='RO' /  (Device)  OBX-18 , PRT-10:PRT-4='EQUIP' / (Organization)  OBX-23,  PRT-8:PRT-4='PO'</t>
-  </si>
-  <si>
-    <t>participation[typeCode=PRF]</t>
-  </si>
-  <si>
-    <t>FiveWs.actor</t>
   </si>
   <si>
     <t>Observation.value[x]</t>
@@ -1795,6 +1824,49 @@
   </si>
   <si>
     <t>outBoundRelationship</t>
+  </si>
+  <si>
+    <t>Observation.hasMember:va-bacteria</t>
+  </si>
+  <si>
+    <t>va-bacteria</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologyBacteriologyObservationbacteria)
+</t>
+  </si>
+  <si>
+    <t>null: reference</t>
+  </si>
+  <si>
+    <t>Observation.hasMember:va-urine</t>
+  </si>
+  <si>
+    <t>va-urine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologyBacteriologyObservationurine)
+</t>
+  </si>
+  <si>
+    <t>Observation.hasMember:va-sputum</t>
+  </si>
+  <si>
+    <t>va-sputum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologyBacteriologyObservationsputum)
+</t>
+  </si>
+  <si>
+    <t>Observation.hasMember:va-gramstain</t>
+  </si>
+  <si>
+    <t>va-gramstain</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologyBacteriologyObservationgramstain)
+</t>
   </si>
   <si>
     <t>Observation.derivedFrom</t>
@@ -2353,7 +2425,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS93"/>
+  <dimension ref="A1:AS99"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.265625" customWidth="true" bestFit="true"/>
@@ -7867,7 +7939,7 @@
         <v>84</v>
       </c>
       <c r="H43" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I43" t="s" s="2">
         <v>85</v>
@@ -7923,16 +7995,14 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>413</v>
@@ -7950,28 +8020,28 @@
         <v>107</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP43" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AQ43" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="AN43" t="s" s="2">
+      <c r="AR43" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP43" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="AQ43" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="AR43" t="s" s="2">
-        <v>424</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -7979,12 +8049,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="C44" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C44" t="s" s="2">
+        <v>423</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
       </c>
@@ -8005,19 +8077,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>429</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -8066,56 +8136,58 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK44" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AG44" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="AL44" t="s" s="2">
-        <v>85</v>
+        <v>426</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>85</v>
+        <v>427</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>85</v>
+        <v>418</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>433</v>
+        <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>434</v>
+        <v>419</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>85</v>
+        <v>421</v>
       </c>
       <c r="AS44" t="s" s="2">
-        <v>436</v>
+        <v>85</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>437</v>
+        <v>428</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C45" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="C45" t="s" s="2">
+        <v>429</v>
+      </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
       </c>
@@ -8133,22 +8205,20 @@
         <v>85</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>184</v>
+        <v>430</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>438</v>
+        <v>415</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>440</v>
-      </c>
+        <v>416</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>441</v>
+        <v>417</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8173,11 +8243,13 @@
         <v>85</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>442</v>
+        <v>85</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>85</v>
@@ -8195,43 +8267,43 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>437</v>
+        <v>413</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>443</v>
+        <v>85</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>85</v>
+        <v>432</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>85</v>
+        <v>433</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>85</v>
+        <v>418</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>138</v>
+        <v>419</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>445</v>
+        <v>420</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>85</v>
+        <v>421</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8239,45 +8311,45 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>447</v>
+        <v>85</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>184</v>
+        <v>435</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>450</v>
+        <v>438</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>451</v>
+        <v>439</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8302,13 +8374,13 @@
         <v>85</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>452</v>
+        <v>85</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>453</v>
+        <v>85</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>85</v>
@@ -8326,19 +8398,19 @@
         <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>85</v>
+        <v>440</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>107</v>
+        <v>441</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8353,27 +8425,27 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>457</v>
+        <v>445</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8384,7 +8456,7 @@
         <v>83</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>96</v>
@@ -8396,19 +8468,19 @@
         <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>459</v>
+        <v>184</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>460</v>
+        <v>447</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>461</v>
+        <v>448</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>462</v>
+        <v>449</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>463</v>
+        <v>450</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8433,13 +8505,11 @@
         <v>85</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>85</v>
+        <v>451</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>85</v>
@@ -8457,25 +8527,25 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>458</v>
+        <v>446</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>85</v>
+        <v>452</v>
       </c>
       <c r="AJ47" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>465</v>
+        <v>85</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>85</v>
@@ -8487,10 +8557,10 @@
         <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>466</v>
+        <v>138</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
@@ -8501,21 +8571,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>85</v>
+        <v>456</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>85</v>
@@ -8530,15 +8600,17 @@
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>469</v>
+        <v>457</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>470</v>
+        <v>458</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>459</v>
+      </c>
+      <c r="O48" t="s" s="2">
+        <v>460</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
       </c>
@@ -8562,13 +8634,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>472</v>
+        <v>189</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>473</v>
+        <v>461</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8586,13 +8658,13 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>468</v>
+        <v>455</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>85</v>
@@ -8613,27 +8685,27 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>475</v>
+        <v>463</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>476</v>
+        <v>464</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>477</v>
+        <v>465</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>478</v>
+        <v>466</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8644,10 +8716,10 @@
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I49" t="s" s="2">
         <v>85</v>
@@ -8656,19 +8728,19 @@
         <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>184</v>
+        <v>468</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>482</v>
+        <v>471</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>483</v>
+        <v>472</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8693,13 +8765,13 @@
         <v>85</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>472</v>
+        <v>85</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>484</v>
+        <v>85</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>485</v>
+        <v>85</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>85</v>
@@ -8717,13 +8789,13 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>479</v>
+        <v>467</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>85</v>
@@ -8732,10 +8804,10 @@
         <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>85</v>
+        <v>473</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>85</v>
+        <v>474</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>85</v>
@@ -8747,10 +8819,10 @@
         <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>486</v>
+        <v>475</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>487</v>
+        <v>476</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
@@ -8761,10 +8833,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8778,7 +8850,7 @@
         <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>85</v>
@@ -8787,16 +8859,16 @@
         <v>85</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>489</v>
+        <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -8822,13 +8894,13 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>85</v>
+        <v>481</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>85</v>
+        <v>482</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>85</v>
+        <v>483</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8846,7 +8918,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>488</v>
+        <v>477</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8861,39 +8933,39 @@
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>493</v>
+        <v>85</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>494</v>
+        <v>85</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>495</v>
+        <v>85</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>499</v>
+        <v>487</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8916,18 +8988,20 @@
         <v>85</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>501</v>
+        <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>502</v>
+        <v>489</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>503</v>
+        <v>490</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>491</v>
+      </c>
+      <c r="O51" t="s" s="2">
+        <v>492</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
       </c>
@@ -8951,13 +9025,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>85</v>
+        <v>481</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>85</v>
+        <v>493</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>85</v>
+        <v>494</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -8975,7 +9049,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9002,27 +9076,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>505</v>
+        <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>506</v>
+        <v>495</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>507</v>
+        <v>496</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>508</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9033,10 +9107,10 @@
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>85</v>
@@ -9045,20 +9119,18 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>514</v>
-      </c>
+        <v>501</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>85</v>
       </c>
@@ -9106,54 +9178,54 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>515</v>
+        <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>85</v>
+        <v>502</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>85</v>
+        <v>503</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>85</v>
+        <v>504</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>85</v>
+        <v>505</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>516</v>
+        <v>506</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>517</v>
+        <v>507</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>85</v>
+        <v>508</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9176,15 +9248,17 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>162</v>
+        <v>510</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>163</v>
+        <v>511</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>512</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>513</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>85</v>
@@ -9233,7 +9307,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>165</v>
+        <v>509</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9245,7 +9319,7 @@
         <v>85</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>85</v>
@@ -9260,31 +9334,31 @@
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>85</v>
+        <v>514</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>85</v>
+        <v>515</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>166</v>
+        <v>516</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>85</v>
+        <v>517</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -9303,18 +9377,20 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>141</v>
+        <v>519</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>142</v>
+        <v>520</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>168</v>
+        <v>521</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>522</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
       </c>
@@ -9362,7 +9438,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>172</v>
+        <v>518</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9374,7 +9450,7 @@
         <v>85</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>146</v>
+        <v>524</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>85</v>
@@ -9392,10 +9468,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>85</v>
+        <v>525</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>166</v>
+        <v>526</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9406,46 +9482,42 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>521</v>
+        <v>85</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I55" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>522</v>
+        <v>163</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>85</v>
       </c>
@@ -9493,19 +9565,19 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>524</v>
+        <v>165</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>85</v>
@@ -9526,7 +9598,7 @@
         <v>85</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
@@ -9537,21 +9609,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>85</v>
@@ -9563,15 +9635,17 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>526</v>
+        <v>141</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>527</v>
+        <v>142</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N56" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>85</v>
@@ -9620,19 +9694,19 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>525</v>
+        <v>172</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>529</v>
+        <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -9650,10 +9724,10 @@
         <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>530</v>
+        <v>85</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>531</v>
+        <v>166</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
@@ -9664,42 +9738,46 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>85</v>
+        <v>530</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>526</v>
+        <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" s="2"/>
+        <v>532</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
       </c>
@@ -9747,19 +9825,19 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>529</v>
+        <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9777,10 +9855,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>530</v>
+        <v>85</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>535</v>
+        <v>138</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9791,10 +9869,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9817,20 +9895,16 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>184</v>
+        <v>535</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="M58" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>540</v>
-      </c>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>85</v>
       </c>
@@ -9854,13 +9928,13 @@
         <v>85</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>541</v>
+        <v>85</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>542</v>
+        <v>85</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>85</v>
@@ -9878,7 +9952,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9887,7 +9961,7 @@
         <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>85</v>
+        <v>538</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>107</v>
@@ -9905,13 +9979,13 @@
         <v>85</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>543</v>
+        <v>85</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>456</v>
+        <v>540</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9922,10 +9996,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9936,7 +10010,7 @@
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>85</v>
@@ -9948,20 +10022,16 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>184</v>
+        <v>535</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>549</v>
-      </c>
+        <v>543</v>
+      </c>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>85</v>
       </c>
@@ -9985,13 +10055,13 @@
         <v>85</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>472</v>
+        <v>85</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>550</v>
+        <v>85</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>551</v>
+        <v>85</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>85</v>
@@ -10009,16 +10079,16 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>85</v>
+        <v>538</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>107</v>
@@ -10036,13 +10106,13 @@
         <v>85</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>543</v>
+        <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="AQ59" t="s" s="2">
         <v>544</v>
-      </c>
-      <c r="AQ59" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -10053,10 +10123,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -10079,17 +10149,19 @@
         <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>553</v>
+        <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>547</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>548</v>
+      </c>
       <c r="O60" t="s" s="2">
-        <v>556</v>
+        <v>549</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -10114,13 +10186,13 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>85</v>
+        <v>550</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>85</v>
+        <v>551</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -10138,7 +10210,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>552</v>
+        <v>545</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10165,13 +10237,13 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>85</v>
+        <v>552</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>85</v>
+        <v>553</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>557</v>
+        <v>465</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10182,10 +10254,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10196,7 +10268,7 @@
         <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>85</v>
@@ -10208,16 +10280,20 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>556</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>558</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
       </c>
@@ -10241,13 +10317,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>85</v>
+        <v>481</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>85</v>
+        <v>559</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>85</v>
+        <v>560</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10265,13 +10341,13 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>85</v>
@@ -10292,13 +10368,13 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>85</v>
+        <v>552</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>530</v>
+        <v>553</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>561</v>
+        <v>465</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10309,10 +10385,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10323,7 +10399,7 @@
         <v>83</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>85</v>
@@ -10332,21 +10408,21 @@
         <v>85</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>564</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" s="2"/>
+      <c r="O62" t="s" s="2">
         <v>565</v>
       </c>
-      <c r="N62" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10394,13 +10470,13 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>85</v>
@@ -10424,10 +10500,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>567</v>
+        <v>85</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10438,10 +10514,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10452,7 +10528,7 @@
         <v>83</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>85</v>
@@ -10461,20 +10537,18 @@
         <v>85</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>570</v>
+        <v>162</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>571</v>
+        <v>568</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>569</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10523,13 +10597,13 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>85</v>
@@ -10553,10 +10627,10 @@
         <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>567</v>
+        <v>539</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10567,10 +10641,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10593,20 +10667,18 @@
         <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>510</v>
+        <v>572</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>85</v>
       </c>
@@ -10642,7 +10714,7 @@
         <v>85</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>580</v>
+        <v>269</v>
       </c>
       <c r="AC64" s="2"/>
       <c r="AD64" t="s" s="2">
@@ -10652,7 +10724,7 @@
         <v>171</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10682,10 +10754,10 @@
         <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10696,12 +10768,14 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="C65" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="C65" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="D65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10713,24 +10787,26 @@
         <v>95</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>162</v>
+        <v>580</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>163</v>
+        <v>573</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>574</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>575</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>85</v>
@@ -10779,22 +10855,22 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>165</v>
+        <v>571</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>85</v>
+        <v>581</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>85</v>
@@ -10809,10 +10885,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>85</v>
+        <v>576</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>166</v>
+        <v>577</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10823,42 +10899,44 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="C66" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="C66" t="s" s="2">
+        <v>583</v>
+      </c>
       <c r="D66" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>141</v>
+        <v>584</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>142</v>
+        <v>573</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>168</v>
+        <v>574</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>144</v>
+        <v>575</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10908,7 +10986,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>172</v>
+        <v>571</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -10920,10 +10998,10 @@
         <v>85</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>85</v>
+        <v>581</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>85</v>
@@ -10938,10 +11016,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>85</v>
+        <v>576</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>166</v>
+        <v>577</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -10955,43 +11033,43 @@
         <v>585</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="C67" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="C67" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="D67" t="s" s="2">
-        <v>521</v>
+        <v>85</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I67" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J67" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>141</v>
+        <v>587</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>522</v>
+        <v>573</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>523</v>
+        <v>574</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>85</v>
       </c>
@@ -11039,7 +11117,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>524</v>
+        <v>571</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11051,10 +11129,10 @@
         <v>85</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>85</v>
+        <v>581</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>85</v>
@@ -11069,10 +11147,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>85</v>
+        <v>576</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>138</v>
+        <v>577</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11083,24 +11161,26 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="C68" s="2"/>
+        <v>571</v>
+      </c>
+      <c r="C68" t="s" s="2">
+        <v>589</v>
+      </c>
       <c r="D68" t="s" s="2">
         <v>85</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>85</v>
@@ -11109,20 +11189,18 @@
         <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>184</v>
+        <v>590</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>587</v>
+        <v>573</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>588</v>
+        <v>574</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>575</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>85</v>
       </c>
@@ -11146,13 +11224,13 @@
         <v>85</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>472</v>
+        <v>85</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>590</v>
+        <v>85</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>85</v>
@@ -11170,13 +11248,13 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>586</v>
+        <v>571</v>
       </c>
       <c r="AG68" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>85</v>
@@ -11185,7 +11263,7 @@
         <v>107</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>85</v>
+        <v>581</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>85</v>
@@ -11197,16 +11275,16 @@
         <v>85</v>
       </c>
       <c r="AO68" t="s" s="2">
-        <v>591</v>
+        <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>285</v>
+        <v>576</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>286</v>
+        <v>577</v>
       </c>
       <c r="AR68" t="s" s="2">
-        <v>287</v>
+        <v>85</v>
       </c>
       <c r="AS68" t="s" s="2">
         <v>85</v>
@@ -11214,10 +11292,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11228,7 +11306,7 @@
         <v>83</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>85</v>
@@ -11240,7 +11318,7 @@
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>426</v>
+        <v>592</v>
       </c>
       <c r="L69" t="s" s="2">
         <v>593</v>
@@ -11251,9 +11329,7 @@
       <c r="N69" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="O69" t="s" s="2">
-        <v>430</v>
-      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>85</v>
       </c>
@@ -11301,13 +11377,13 @@
         <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>85</v>
@@ -11328,19 +11404,19 @@
         <v>85</v>
       </c>
       <c r="AO69" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AQ69" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="AP69" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AQ69" t="s" s="2">
-        <v>435</v>
-      </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS69" t="s" s="2">
-        <v>436</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70" hidden="true">
@@ -11359,7 +11435,7 @@
         <v>83</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>85</v>
@@ -11368,10 +11444,10 @@
         <v>85</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>184</v>
+        <v>519</v>
       </c>
       <c r="L70" t="s" s="2">
         <v>598</v>
@@ -11383,7 +11459,7 @@
         <v>600</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>441</v>
+        <v>601</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
@@ -11408,28 +11484,26 @@
         <v>85</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>601</v>
+        <v>85</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>442</v>
+        <v>85</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>602</v>
+      </c>
+      <c r="AC70" s="2"/>
       <c r="AD70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF70" t="s" s="2">
         <v>597</v>
@@ -11438,10 +11512,10 @@
         <v>83</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>602</v>
+        <v>85</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>107</v>
@@ -11462,10 +11536,10 @@
         <v>85</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>138</v>
+        <v>603</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>445</v>
+        <v>604</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
@@ -11476,21 +11550,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>447</v>
+        <v>85</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>85</v>
@@ -11502,20 +11576,16 @@
         <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>448</v>
+        <v>163</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>451</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>85</v>
       </c>
@@ -11539,13 +11609,13 @@
         <v>85</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y71" t="s" s="2">
-        <v>452</v>
+        <v>85</v>
       </c>
       <c r="Z71" t="s" s="2">
-        <v>453</v>
+        <v>85</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>85</v>
@@ -11563,19 +11633,19 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>603</v>
+        <v>165</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>85</v>
@@ -11590,31 +11660,31 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>454</v>
+        <v>85</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>455</v>
+        <v>85</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>456</v>
+        <v>166</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>457</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11633,20 +11703,18 @@
         <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>605</v>
+        <v>142</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>606</v>
+        <v>168</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="O72" t="s" s="2">
-        <v>514</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>85</v>
       </c>
@@ -11694,7 +11762,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>604</v>
+        <v>172</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11706,7 +11774,7 @@
         <v>85</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>85</v>
@@ -11724,10 +11792,10 @@
         <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>516</v>
+        <v>85</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>517</v>
+        <v>166</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
@@ -11741,44 +11809,42 @@
         <v>607</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>608</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>85</v>
+        <v>530</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>510</v>
+        <v>141</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>576</v>
+        <v>531</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>577</v>
+        <v>532</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>578</v>
+        <v>144</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>579</v>
+        <v>150</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11827,7 +11893,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>575</v>
+        <v>533</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>83</v>
@@ -11839,7 +11905,7 @@
         <v>85</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>85</v>
@@ -11857,10 +11923,10 @@
         <v>85</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>581</v>
+        <v>85</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>582</v>
+        <v>138</v>
       </c>
       <c r="AR73" t="s" s="2">
         <v>85</v>
@@ -11871,10 +11937,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>583</v>
+        <v>608</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11882,7 +11948,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>95</v>
@@ -11894,19 +11960,23 @@
         <v>85</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>163</v>
+        <v>609</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>610</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>280</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
       </c>
@@ -11930,13 +12000,13 @@
         <v>85</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>85</v>
+        <v>481</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>85</v>
+        <v>612</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>85</v>
+        <v>282</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>85</v>
@@ -11954,10 +12024,10 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>165</v>
+        <v>608</v>
       </c>
       <c r="AG74" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>95</v>
@@ -11966,7 +12036,7 @@
         <v>85</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>85</v>
@@ -11981,16 +12051,16 @@
         <v>85</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>85</v>
+        <v>613</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>85</v>
+        <v>285</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>166</v>
+        <v>286</v>
       </c>
       <c r="AR74" t="s" s="2">
-        <v>85</v>
+        <v>287</v>
       </c>
       <c r="AS74" t="s" s="2">
         <v>85</v>
@@ -11998,21 +12068,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>584</v>
+        <v>614</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>85</v>
@@ -12021,21 +12091,23 @@
         <v>85</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>141</v>
+        <v>435</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>142</v>
+        <v>615</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>168</v>
+        <v>616</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>617</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>85</v>
       </c>
@@ -12083,19 +12155,19 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>172</v>
+        <v>614</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>85</v>
@@ -12110,62 +12182,62 @@
         <v>85</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>85</v>
+        <v>618</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>85</v>
+        <v>443</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>166</v>
+        <v>444</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS75" t="s" s="2">
-        <v>85</v>
+        <v>445</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>585</v>
+        <v>619</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>521</v>
+        <v>85</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>522</v>
+        <v>620</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>523</v>
+        <v>621</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>144</v>
+        <v>622</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>85</v>
@@ -12190,13 +12262,13 @@
         <v>85</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>85</v>
+        <v>623</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>85</v>
+        <v>451</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>85</v>
@@ -12214,19 +12286,19 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>524</v>
+        <v>619</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>85</v>
+        <v>624</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>85</v>
@@ -12244,10 +12316,10 @@
         <v>85</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>138</v>
+        <v>454</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>85</v>
@@ -12258,45 +12330,45 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>612</v>
+        <v>625</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>586</v>
+        <v>625</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>85</v>
+        <v>456</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K77" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>587</v>
+        <v>457</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>588</v>
+        <v>458</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>589</v>
+        <v>459</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>280</v>
+        <v>460</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>85</v>
@@ -12321,13 +12393,13 @@
         <v>85</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>472</v>
+        <v>189</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>590</v>
+        <v>461</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>282</v>
+        <v>462</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>85</v>
@@ -12345,13 +12417,13 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>586</v>
+        <v>625</v>
       </c>
       <c r="AG77" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>85</v>
@@ -12360,7 +12432,7 @@
         <v>107</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>613</v>
+        <v>85</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>85</v>
@@ -12372,27 +12444,27 @@
         <v>85</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>591</v>
+        <v>463</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>285</v>
+        <v>464</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>286</v>
+        <v>465</v>
       </c>
       <c r="AR77" t="s" s="2">
-        <v>287</v>
+        <v>85</v>
       </c>
       <c r="AS77" t="s" s="2">
-        <v>85</v>
+        <v>466</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>615</v>
+        <v>626</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -12403,7 +12475,7 @@
         <v>83</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>85</v>
@@ -12415,16 +12487,20 @@
         <v>85</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>163</v>
+        <v>627</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
+        <v>628</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O78" t="s" s="2">
+        <v>523</v>
+      </c>
       <c r="P78" t="s" s="2">
         <v>85</v>
       </c>
@@ -12472,19 +12548,19 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>165</v>
+        <v>626</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>85</v>
@@ -12502,10 +12578,10 @@
         <v>85</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>85</v>
+        <v>525</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>166</v>
+        <v>526</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>85</v>
@@ -12516,21 +12592,23 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>616</v>
+        <v>629</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="C79" s="2"/>
+        <v>597</v>
+      </c>
+      <c r="C79" t="s" s="2">
+        <v>630</v>
+      </c>
       <c r="D79" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>85</v>
@@ -12539,21 +12617,23 @@
         <v>85</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>141</v>
+        <v>519</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>142</v>
+        <v>598</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>168</v>
+        <v>599</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O79" s="2"/>
+        <v>600</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>601</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>85</v>
       </c>
@@ -12589,19 +12669,19 @@
         <v>85</v>
       </c>
       <c r="AB79" t="s" s="2">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="AC79" t="s" s="2">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AD79" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE79" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>172</v>
+        <v>597</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
@@ -12613,7 +12693,7 @@
         <v>85</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>85</v>
@@ -12631,10 +12711,10 @@
         <v>85</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>85</v>
+        <v>603</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>166</v>
+        <v>604</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>85</v>
@@ -12645,10 +12725,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>618</v>
+        <v>631</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>619</v>
+        <v>605</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12659,7 +12739,7 @@
         <v>83</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>85</v>
@@ -12668,23 +12748,19 @@
         <v>85</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>292</v>
+        <v>162</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>293</v>
+        <v>163</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>85</v>
       </c>
@@ -12732,19 +12808,19 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>297</v>
+        <v>165</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>85</v>
@@ -12762,10 +12838,10 @@
         <v>85</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>299</v>
+        <v>85</v>
       </c>
       <c r="AQ80" t="s" s="2">
-        <v>300</v>
+        <v>166</v>
       </c>
       <c r="AR80" t="s" s="2">
         <v>85</v>
@@ -12776,21 +12852,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>621</v>
+        <v>606</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>85</v>
@@ -12802,15 +12878,17 @@
         <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>85</v>
@@ -12859,19 +12937,19 @@
         <v>85</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>85</v>
@@ -12903,14 +12981,14 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>140</v>
+        <v>530</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12923,24 +13001,26 @@
         <v>85</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K82" t="s" s="2">
         <v>141</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>142</v>
+        <v>531</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>168</v>
+        <v>532</v>
       </c>
       <c r="N82" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="O82" s="2"/>
+      <c r="O82" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>85</v>
       </c>
@@ -12976,19 +13056,19 @@
         <v>85</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>172</v>
+        <v>533</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>83</v>
@@ -13021,7 +13101,7 @@
         <v>85</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="AR82" t="s" s="2">
         <v>85</v>
@@ -13032,10 +13112,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>624</v>
+        <v>634</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>625</v>
+        <v>608</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13043,7 +13123,7 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>95</v>
@@ -13058,19 +13138,19 @@
         <v>96</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>109</v>
+        <v>184</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>304</v>
+        <v>609</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>305</v>
+        <v>610</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>306</v>
+        <v>611</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>307</v>
+        <v>280</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>85</v>
@@ -13080,7 +13160,7 @@
         <v>85</v>
       </c>
       <c r="S83" t="s" s="2">
-        <v>626</v>
+        <v>85</v>
       </c>
       <c r="T83" t="s" s="2">
         <v>85</v>
@@ -13095,13 +13175,13 @@
         <v>85</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>85</v>
+        <v>481</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>85</v>
+        <v>612</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>85</v>
+        <v>282</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>85</v>
@@ -13119,10 +13199,10 @@
         <v>85</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>308</v>
+        <v>608</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>95</v>
@@ -13134,7 +13214,7 @@
         <v>107</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>85</v>
@@ -13146,16 +13226,16 @@
         <v>85</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>85</v>
+        <v>613</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>311</v>
+        <v>285</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>312</v>
+        <v>286</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>85</v>
+        <v>287</v>
       </c>
       <c r="AS83" t="s" s="2">
         <v>85</v>
@@ -13163,10 +13243,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13186,20 +13266,18 @@
         <v>85</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K84" t="s" s="2">
         <v>162</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>314</v>
+        <v>163</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>316</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>85</v>
@@ -13248,7 +13326,7 @@
         <v>85</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>317</v>
+        <v>165</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
@@ -13260,7 +13338,7 @@
         <v>85</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>85</v>
@@ -13278,10 +13356,10 @@
         <v>85</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>318</v>
+        <v>85</v>
       </c>
       <c r="AQ84" t="s" s="2">
-        <v>319</v>
+        <v>166</v>
       </c>
       <c r="AR84" t="s" s="2">
         <v>85</v>
@@ -13292,44 +13370,44 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>631</v>
+        <v>639</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>115</v>
+        <v>141</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>321</v>
+        <v>142</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>323</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>85</v>
       </c>
@@ -13365,34 +13443,34 @@
         <v>85</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>324</v>
+        <v>172</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>632</v>
+        <v>85</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>85</v>
@@ -13407,10 +13485,10 @@
         <v>85</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>327</v>
+        <v>166</v>
       </c>
       <c r="AR85" t="s" s="2">
         <v>85</v>
@@ -13421,10 +13499,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13435,7 +13513,7 @@
         <v>83</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>85</v>
@@ -13447,17 +13525,19 @@
         <v>96</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>162</v>
+        <v>292</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>329</v>
+        <v>293</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="O86" t="s" s="2">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>85</v>
@@ -13506,13 +13586,13 @@
         <v>85</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>332</v>
+        <v>297</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>85</v>
@@ -13536,10 +13616,10 @@
         <v>85</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>334</v>
+        <v>299</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>335</v>
+        <v>300</v>
       </c>
       <c r="AR86" t="s" s="2">
         <v>85</v>
@@ -13550,10 +13630,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13573,23 +13653,19 @@
         <v>85</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>337</v>
+        <v>162</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>338</v>
+        <v>163</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="O87" t="s" s="2">
-        <v>341</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>85</v>
       </c>
@@ -13637,7 +13713,7 @@
         <v>85</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>342</v>
+        <v>165</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
@@ -13649,7 +13725,7 @@
         <v>85</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>85</v>
@@ -13667,10 +13743,10 @@
         <v>85</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>343</v>
+        <v>85</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>344</v>
+        <v>166</v>
       </c>
       <c r="AR87" t="s" s="2">
         <v>85</v>
@@ -13681,21 +13757,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>85</v>
@@ -13704,23 +13780,21 @@
         <v>85</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>346</v>
+        <v>142</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>347</v>
+        <v>168</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O88" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>85</v>
       </c>
@@ -13756,31 +13830,31 @@
         <v>85</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>350</v>
+        <v>172</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK88" t="s" s="2">
         <v>85</v>
@@ -13798,10 +13872,10 @@
         <v>85</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>351</v>
+        <v>85</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>352</v>
+        <v>166</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>85</v>
@@ -13812,10 +13886,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>592</v>
+        <v>647</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13829,7 +13903,7 @@
         <v>95</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>85</v>
@@ -13838,19 +13912,19 @@
         <v>96</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>426</v>
+        <v>109</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>593</v>
+        <v>304</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>594</v>
+        <v>305</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>595</v>
+        <v>306</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>430</v>
+        <v>307</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>85</v>
@@ -13860,7 +13934,7 @@
         <v>85</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>85</v>
+        <v>648</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>85</v>
@@ -13887,17 +13961,19 @@
         <v>85</v>
       </c>
       <c r="AB89" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AC89" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD89" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>592</v>
+        <v>308</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -13912,7 +13988,7 @@
         <v>107</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>85</v>
+        <v>649</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>85</v>
@@ -13924,31 +14000,29 @@
         <v>85</v>
       </c>
       <c r="AO89" t="s" s="2">
-        <v>596</v>
+        <v>85</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>434</v>
+        <v>311</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>435</v>
+        <v>312</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS89" t="s" s="2">
-        <v>436</v>
+        <v>85</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>640</v>
+        <v>650</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="C90" t="s" s="2">
-        <v>641</v>
-      </c>
+        <v>651</v>
+      </c>
+      <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
         <v>85</v>
       </c>
@@ -13960,7 +14034,7 @@
         <v>95</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>85</v>
@@ -13972,17 +14046,15 @@
         <v>162</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>593</v>
+        <v>314</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>594</v>
+        <v>315</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>430</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>85</v>
       </c>
@@ -14030,7 +14102,7 @@
         <v>85</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>592</v>
+        <v>317</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
@@ -14045,7 +14117,7 @@
         <v>107</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>642</v>
+        <v>85</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>85</v>
@@ -14057,27 +14129,27 @@
         <v>85</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>596</v>
+        <v>85</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>434</v>
+        <v>318</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>435</v>
+        <v>319</v>
       </c>
       <c r="AR90" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS90" t="s" s="2">
-        <v>436</v>
+        <v>85</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>643</v>
+        <v>652</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>597</v>
+        <v>653</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14091,28 +14163,26 @@
         <v>95</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>184</v>
+        <v>115</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>598</v>
+        <v>321</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>600</v>
-      </c>
+        <v>322</v>
+      </c>
+      <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>441</v>
+        <v>323</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>85</v>
@@ -14137,13 +14207,13 @@
         <v>85</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>601</v>
+        <v>85</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>442</v>
+        <v>85</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>85</v>
@@ -14161,7 +14231,7 @@
         <v>85</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>597</v>
+        <v>324</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14170,13 +14240,13 @@
         <v>95</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>602</v>
+        <v>85</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>85</v>
+        <v>654</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>85</v>
@@ -14191,10 +14261,10 @@
         <v>85</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>138</v>
+        <v>326</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>445</v>
+        <v>327</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>85</v>
@@ -14205,45 +14275,43 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>603</v>
+        <v>656</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>447</v>
+        <v>85</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H92" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J92" t="s" s="2">
         <v>96</v>
       </c>
-      <c r="I92" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J92" t="s" s="2">
-        <v>85</v>
-      </c>
       <c r="K92" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>448</v>
+        <v>329</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>450</v>
-      </c>
+        <v>330</v>
+      </c>
+      <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>451</v>
+        <v>331</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>85</v>
@@ -14268,11 +14336,13 @@
         <v>85</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y92" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z92" t="s" s="2">
-        <v>645</v>
+        <v>85</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>85</v>
@@ -14290,13 +14360,13 @@
         <v>85</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>603</v>
+        <v>332</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>85</v>
@@ -14305,7 +14375,7 @@
         <v>107</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>646</v>
+        <v>85</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>85</v>
@@ -14317,27 +14387,27 @@
         <v>85</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>454</v>
+        <v>85</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>455</v>
+        <v>334</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>456</v>
+        <v>335</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS92" t="s" s="2">
-        <v>457</v>
+        <v>85</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>647</v>
+        <v>657</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>604</v>
+        <v>658</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14348,7 +14418,7 @@
         <v>83</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>85</v>
@@ -14357,22 +14427,22 @@
         <v>85</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>86</v>
+        <v>337</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>605</v>
+        <v>338</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>606</v>
+        <v>339</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>513</v>
+        <v>340</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>514</v>
+        <v>341</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>85</v>
@@ -14421,13 +14491,13 @@
         <v>85</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>604</v>
+        <v>342</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>85</v>
@@ -14451,20 +14521,804 @@
         <v>85</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>516</v>
+        <v>343</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>517</v>
+        <v>344</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS93" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>659</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>660</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AQ94" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AR94" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS94" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="O95" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="P95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AC95" s="2"/>
+      <c r="AD95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AQ95" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AR95" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS95" t="s" s="2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="C96" t="s" s="2">
+        <v>663</v>
+      </c>
+      <c r="D96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="N96" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="O96" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="P96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AQ96" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AR96" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS96" t="s" s="2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="O97" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AQ97" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AR97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS97" t="s" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>666</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y98" s="2"/>
+      <c r="Z98" t="s" s="2">
+        <v>667</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>463</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="AQ98" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AR98" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS98" t="s" s="2">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="O99" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="AQ99" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AR99" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AS99" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS93">
+  <autoFilter ref="A1:AS99">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14474,7 +15328,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI92">
+  <conditionalFormatting sqref="A2:AI98">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$99</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$98</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4132" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4093" uniqueCount="667">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1320,6 +1320,10 @@
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:$this}
+</t>
+  </si>
+  <si>
     <t>Event.performer.actor</t>
   </si>
   <si>
@@ -1407,6 +1411,37 @@
   </si>
   <si>
     <t>363714003 |Interprets|</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueQuantity</t>
+  </si>
+  <si>
+    <t>valueQuantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>2062: target not supported</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>valueCodeableConcept</t>
+  </si>
+  <si>
+    <t>2063: target not supported</t>
+  </si>
+  <si>
+    <t>Observation.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
+  </si>
+  <si>
+    <t>2064: target not supported</t>
   </si>
   <si>
     <t>Observation.dataAbsentReason</t>
@@ -1826,49 +1861,6 @@
     <t>outBoundRelationship</t>
   </si>
   <si>
-    <t>Observation.hasMember:va-bacteria</t>
-  </si>
-  <si>
-    <t>va-bacteria</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologyBacteriologyObservationbacteria)
-</t>
-  </si>
-  <si>
-    <t>null: reference</t>
-  </si>
-  <si>
-    <t>Observation.hasMember:va-urine</t>
-  </si>
-  <si>
-    <t>va-urine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologyBacteriologyObservationurine)
-</t>
-  </si>
-  <si>
-    <t>Observation.hasMember:va-sputum</t>
-  </si>
-  <si>
-    <t>va-sputum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologyBacteriologyObservationsputum)
-</t>
-  </si>
-  <si>
-    <t>Observation.hasMember:va-gramstain</t>
-  </si>
-  <si>
-    <t>va-gramstain</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologyBacteriologyObservationgramstain)
-</t>
-  </si>
-  <si>
     <t>Observation.derivedFrom</t>
   </si>
   <si>
@@ -2088,9 +2080,6 @@
   </si>
   <si>
     <t>Observation.component:va-component.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
   </si>
   <si>
     <t>1523: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (63.05-12 &gt; 63.3-5+to+160)</t>
@@ -2425,12 +2414,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS99"/>
+  <dimension ref="A1:AS98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="47.40625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -7995,7 +7984,7 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>269</v>
+        <v>418</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -8029,19 +8018,19 @@
         <v>85</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -8049,13 +8038,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
@@ -8077,7 +8066,7 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L44" t="s" s="2">
         <v>415</v>
@@ -8151,28 +8140,28 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>85</v>
@@ -8180,13 +8169,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>413</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8208,7 +8197,7 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L45" t="s" s="2">
         <v>415</v>
@@ -8282,28 +8271,28 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8311,10 +8300,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8337,19 +8326,19 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8386,19 +8375,17 @@
         <v>85</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8407,10 +8394,10 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8425,29 +8412,31 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>448</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>85</v>
       </c>
@@ -8465,22 +8454,22 @@
         <v>85</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>184</v>
+        <v>449</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8505,11 +8494,13 @@
         <v>85</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y47" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z47" t="s" s="2">
-        <v>451</v>
+        <v>85</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>85</v>
@@ -8527,7 +8518,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>446</v>
+        <v>435</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8536,13 +8527,13 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>107</v>
+        <v>442</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>85</v>
@@ -8554,62 +8545,64 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>85</v>
+        <v>443</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>138</v>
+        <v>444</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>85</v>
+        <v>446</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="C48" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="C48" t="s" s="2">
+        <v>452</v>
+      </c>
       <c r="D48" t="s" s="2">
-        <v>456</v>
+        <v>85</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>457</v>
+        <v>437</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>458</v>
+        <v>438</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>459</v>
+        <v>439</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>460</v>
+        <v>440</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8634,13 +8627,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>461</v>
+        <v>85</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>462</v>
+        <v>85</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8658,22 +8651,22 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>455</v>
+        <v>435</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>85</v>
+        <v>441</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>107</v>
+        <v>442</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>85</v>
+        <v>453</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>85</v>
@@ -8685,29 +8678,31 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>463</v>
+        <v>443</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>464</v>
+        <v>444</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>465</v>
+        <v>445</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>466</v>
+        <v>446</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="C49" s="2"/>
+        <v>435</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="D49" t="s" s="2">
         <v>85</v>
       </c>
@@ -8716,7 +8711,7 @@
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>96</v>
@@ -8725,22 +8720,22 @@
         <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>468</v>
+        <v>162</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>469</v>
+        <v>437</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>470</v>
+        <v>438</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>471</v>
+        <v>439</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>472</v>
+        <v>440</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8789,25 +8784,25 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>467</v>
+        <v>435</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>85</v>
+        <v>441</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>107</v>
+        <v>442</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>473</v>
+        <v>456</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>474</v>
+        <v>85</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>85</v>
@@ -8816,27 +8811,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>85</v>
+        <v>443</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>475</v>
+        <v>444</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>476</v>
+        <v>445</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>85</v>
+        <v>446</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8850,7 +8845,7 @@
         <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>85</v>
@@ -8862,15 +8857,17 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>478</v>
+        <v>458</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>479</v>
+        <v>459</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>460</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>461</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
       </c>
@@ -8894,13 +8891,11 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>481</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>482</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>483</v>
+        <v>462</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8918,7 +8913,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>477</v>
+        <v>457</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8927,13 +8922,13 @@
         <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>85</v>
+        <v>463</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>85</v>
+        <v>464</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>85</v>
@@ -8945,38 +8940,38 @@
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>484</v>
+        <v>85</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>485</v>
+        <v>138</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>486</v>
+        <v>465</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>487</v>
+        <v>85</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>85</v>
+        <v>467</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>85</v>
@@ -8991,16 +8986,16 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>489</v>
+        <v>468</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>490</v>
+        <v>469</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>491</v>
+        <v>470</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>492</v>
+        <v>471</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -9025,13 +9020,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>481</v>
+        <v>189</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>493</v>
+        <v>472</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>494</v>
+        <v>473</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -9049,13 +9044,13 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>488</v>
+        <v>466</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>85</v>
@@ -9076,27 +9071,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>85</v>
+        <v>474</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>495</v>
+        <v>475</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>496</v>
+        <v>476</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>85</v>
+        <v>477</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9107,7 +9102,7 @@
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>96</v>
@@ -9119,18 +9114,20 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>498</v>
+        <v>479</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>482</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>483</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
       </c>
@@ -9178,13 +9175,13 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>497</v>
+        <v>478</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>85</v>
@@ -9193,39 +9190,39 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>502</v>
+        <v>484</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>504</v>
+        <v>85</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>505</v>
+        <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>506</v>
+        <v>486</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>507</v>
+        <v>487</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>508</v>
+        <v>85</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>509</v>
+        <v>488</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>509</v>
+        <v>488</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9248,16 +9245,16 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>510</v>
+        <v>184</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>511</v>
+        <v>489</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>512</v>
+        <v>490</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9283,13 +9280,13 @@
         <v>85</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>85</v>
+        <v>493</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>85</v>
+        <v>494</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>85</v>
@@ -9307,7 +9304,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>509</v>
+        <v>488</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9334,27 +9331,27 @@
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>514</v>
+        <v>495</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>515</v>
+        <v>496</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>516</v>
+        <v>497</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>517</v>
+        <v>498</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9365,7 +9362,7 @@
         <v>83</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>85</v>
@@ -9377,19 +9374,19 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>519</v>
+        <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>520</v>
+        <v>500</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>521</v>
+        <v>501</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>522</v>
+        <v>502</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>523</v>
+        <v>503</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9414,13 +9411,13 @@
         <v>85</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>85</v>
+        <v>504</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>85</v>
+        <v>505</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>85</v>
@@ -9438,19 +9435,19 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>518</v>
+        <v>499</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>524</v>
+        <v>107</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>85</v>
@@ -9468,10 +9465,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>525</v>
+        <v>506</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>526</v>
+        <v>507</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9482,10 +9479,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>527</v>
+        <v>508</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9499,7 +9496,7 @@
         <v>95</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>85</v>
@@ -9508,15 +9505,17 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>162</v>
+        <v>509</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>163</v>
+        <v>510</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>511</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>512</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>85</v>
@@ -9565,7 +9564,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>165</v>
+        <v>508</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9577,53 +9576,53 @@
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>85</v>
+        <v>513</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>85</v>
+        <v>514</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>85</v>
+        <v>515</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>85</v>
+        <v>516</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>85</v>
+        <v>517</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>166</v>
+        <v>518</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>85</v>
+        <v>519</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>85</v>
@@ -9635,16 +9634,16 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>141</v>
+        <v>521</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>142</v>
+        <v>522</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>168</v>
+        <v>523</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>144</v>
+        <v>524</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9694,19 +9693,19 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>172</v>
+        <v>520</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -9721,19 +9720,19 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>85</v>
+        <v>525</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>85</v>
+        <v>526</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>166</v>
+        <v>527</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>85</v>
+        <v>528</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -9745,7 +9744,7 @@
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>530</v>
+        <v>85</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9758,13 +9757,13 @@
         <v>85</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>141</v>
+        <v>530</v>
       </c>
       <c r="L57" t="s" s="2">
         <v>531</v>
@@ -9773,10 +9772,10 @@
         <v>532</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>144</v>
+        <v>533</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>150</v>
+        <v>534</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9825,7 +9824,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9837,7 +9836,7 @@
         <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>146</v>
+        <v>535</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9855,10 +9854,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>85</v>
+        <v>536</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>138</v>
+        <v>537</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9869,10 +9868,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9895,13 +9894,13 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>535</v>
+        <v>162</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>536</v>
+        <v>163</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>537</v>
+        <v>164</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9952,7 +9951,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>534</v>
+        <v>165</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9961,10 +9960,10 @@
         <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>538</v>
+        <v>85</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>85</v>
@@ -9982,10 +9981,10 @@
         <v>85</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>539</v>
+        <v>85</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>540</v>
+        <v>166</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -9996,21 +9995,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>85</v>
@@ -10022,15 +10021,17 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>535</v>
+        <v>141</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>542</v>
+        <v>142</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="N59" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -10079,19 +10080,19 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>541</v>
+        <v>172</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>538</v>
+        <v>85</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>85</v>
@@ -10109,10 +10110,10 @@
         <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>539</v>
+        <v>85</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>544</v>
+        <v>166</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -10123,45 +10124,45 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>85</v>
+        <v>541</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>184</v>
+        <v>141</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>548</v>
+        <v>144</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>549</v>
+        <v>150</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -10186,13 +10187,13 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>550</v>
+        <v>85</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>551</v>
+        <v>85</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -10210,19 +10211,19 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>85</v>
@@ -10237,13 +10238,13 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>552</v>
+        <v>85</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>553</v>
+        <v>85</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>465</v>
+        <v>138</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10254,10 +10255,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10268,7 +10269,7 @@
         <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>85</v>
@@ -10280,20 +10281,16 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>184</v>
+        <v>546</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O61" t="s" s="2">
-        <v>558</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>85</v>
       </c>
@@ -10317,13 +10314,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>481</v>
+        <v>85</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>559</v>
+        <v>85</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>560</v>
+        <v>85</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10341,16 +10338,16 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>85</v>
+        <v>549</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -10368,13 +10365,13 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>552</v>
+        <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>465</v>
+        <v>551</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10385,10 +10382,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10411,18 +10408,16 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>562</v>
+        <v>546</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>564</v>
+        <v>554</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>565</v>
-      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10470,7 +10465,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10479,7 +10474,7 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>85</v>
+        <v>549</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10500,10 +10495,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>85</v>
+        <v>550</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>566</v>
+        <v>555</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10514,10 +10509,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10540,16 +10535,20 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>568</v>
+        <v>557</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" s="2"/>
+        <v>558</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>560</v>
+      </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
       </c>
@@ -10573,13 +10572,13 @@
         <v>85</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>85</v>
+        <v>561</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>85</v>
+        <v>562</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10597,7 +10596,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>567</v>
+        <v>556</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10624,13 +10623,13 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>85</v>
+        <v>563</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>539</v>
+        <v>564</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>570</v>
+        <v>476</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10641,10 +10640,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10664,21 +10663,23 @@
         <v>85</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>572</v>
+        <v>184</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>573</v>
+        <v>566</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>574</v>
+        <v>567</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="O64" s="2"/>
+        <v>568</v>
+      </c>
+      <c r="O64" t="s" s="2">
+        <v>569</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
       </c>
@@ -10702,29 +10703,31 @@
         <v>85</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>85</v>
+        <v>570</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>85</v>
+        <v>571</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB64" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AC64" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD64" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE64" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10751,13 +10754,13 @@
         <v>85</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>85</v>
+        <v>563</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>576</v>
+        <v>564</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>577</v>
+        <v>476</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10768,14 +10771,12 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C65" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>572</v>
+      </c>
+      <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10787,27 +10788,27 @@
         <v>95</v>
       </c>
       <c r="H65" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I65" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N65" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="O65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" t="s" s="2">
+        <v>576</v>
+      </c>
       <c r="P65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10855,13 +10856,13 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
@@ -10870,7 +10871,7 @@
         <v>107</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>581</v>
+        <v>85</v>
       </c>
       <c r="AL65" t="s" s="2">
         <v>85</v>
@@ -10885,7 +10886,7 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>576</v>
+        <v>85</v>
       </c>
       <c r="AQ65" t="s" s="2">
         <v>577</v>
@@ -10899,14 +10900,12 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C66" t="s" s="2">
-        <v>583</v>
-      </c>
+        <v>578</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>85</v>
       </c>
@@ -10918,26 +10917,24 @@
         <v>95</v>
       </c>
       <c r="H66" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I66" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>584</v>
+        <v>162</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>573</v>
+        <v>579</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>575</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
         <v>85</v>
@@ -10986,13 +10983,13 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>85</v>
@@ -11001,25 +10998,25 @@
         <v>107</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AQ66" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="AL66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="AQ66" t="s" s="2">
-        <v>577</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -11030,14 +11027,12 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>585</v>
+        <v>582</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C67" t="s" s="2">
-        <v>586</v>
-      </c>
+        <v>582</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>85</v>
       </c>
@@ -11046,10 +11041,10 @@
         <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>85</v>
@@ -11058,16 +11053,16 @@
         <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>587</v>
+        <v>583</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -11117,7 +11112,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11132,7 +11127,7 @@
         <v>107</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>581</v>
+        <v>85</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>85</v>
@@ -11147,10 +11142,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11161,14 +11156,12 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="C68" t="s" s="2">
         <v>589</v>
       </c>
+      <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
         <v>85</v>
       </c>
@@ -11177,10 +11170,10 @@
         <v>83</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>85</v>
@@ -11192,13 +11185,13 @@
         <v>590</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>573</v>
+        <v>591</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>574</v>
+        <v>592</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>575</v>
+        <v>593</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11248,7 +11241,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>571</v>
+        <v>589</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11263,7 +11256,7 @@
         <v>107</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>581</v>
+        <v>85</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>85</v>
@@ -11278,10 +11271,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>576</v>
+        <v>587</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>577</v>
+        <v>594</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11292,10 +11285,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11318,18 +11311,20 @@
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>592</v>
+        <v>530</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="O69" s="2"/>
+        <v>598</v>
+      </c>
+      <c r="O69" t="s" s="2">
+        <v>599</v>
+      </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
       </c>
@@ -11365,19 +11360,17 @@
         <v>85</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="AC69" s="2"/>
       <c r="AD69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11407,10 +11400,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>576</v>
+        <v>601</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>596</v>
+        <v>602</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11421,10 +11414,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>597</v>
+        <v>603</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11435,7 +11428,7 @@
         <v>83</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>85</v>
@@ -11444,23 +11437,19 @@
         <v>85</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>519</v>
+        <v>162</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>598</v>
+        <v>163</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>85</v>
       </c>
@@ -11496,29 +11485,31 @@
         <v>85</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="AC70" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>597</v>
+        <v>165</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>85</v>
@@ -11536,10 +11527,10 @@
         <v>85</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>603</v>
+        <v>85</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>604</v>
+        <v>166</v>
       </c>
       <c r="AR70" t="s" s="2">
         <v>85</v>
@@ -11550,21 +11541,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>85</v>
@@ -11576,15 +11567,17 @@
         <v>85</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N71" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>85</v>
@@ -11633,19 +11626,19 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>85</v>
@@ -11677,14 +11670,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>140</v>
+        <v>541</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11697,24 +11690,26 @@
         <v>85</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>141</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>142</v>
+        <v>542</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>168</v>
+        <v>543</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="O72" s="2"/>
+      <c r="O72" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
       </c>
@@ -11762,7 +11757,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>172</v>
+        <v>544</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11795,7 +11790,7 @@
         <v>85</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
@@ -11806,45 +11801,45 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>530</v>
+        <v>85</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I73" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J73" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>531</v>
+        <v>607</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>532</v>
+        <v>608</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>144</v>
+        <v>609</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11869,13 +11864,13 @@
         <v>85</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>85</v>
+        <v>610</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>85</v>
+        <v>282</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>85</v>
@@ -11893,19 +11888,19 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>533</v>
+        <v>606</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>85</v>
@@ -11920,16 +11915,16 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>85</v>
+        <v>611</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>85</v>
+        <v>285</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>138</v>
+        <v>286</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>85</v>
+        <v>287</v>
       </c>
       <c r="AS73" t="s" s="2">
         <v>85</v>
@@ -11937,10 +11932,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11948,7 +11943,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>95</v>
@@ -11963,19 +11958,19 @@
         <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>184</v>
+        <v>436</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>280</v>
+        <v>440</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -12000,34 +11995,34 @@
         <v>85</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>481</v>
+        <v>85</v>
       </c>
       <c r="Y74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="Z74" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>608</v>
-      </c>
       <c r="AG74" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH74" t="s" s="2">
         <v>95</v>
@@ -12051,27 +12046,27 @@
         <v>85</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>285</v>
+        <v>444</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>286</v>
+        <v>445</v>
       </c>
       <c r="AR74" t="s" s="2">
-        <v>287</v>
+        <v>85</v>
       </c>
       <c r="AS74" t="s" s="2">
-        <v>85</v>
+        <v>446</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12091,22 +12086,22 @@
         <v>85</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>435</v>
+        <v>184</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -12131,13 +12126,13 @@
         <v>85</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>85</v>
+        <v>621</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>85</v>
+        <v>462</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>85</v>
@@ -12155,7 +12150,7 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12164,7 +12159,7 @@
         <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>85</v>
+        <v>622</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
@@ -12182,38 +12177,38 @@
         <v>85</v>
       </c>
       <c r="AO75" t="s" s="2">
-        <v>618</v>
+        <v>85</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>443</v>
+        <v>138</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS75" t="s" s="2">
-        <v>445</v>
+        <v>85</v>
       </c>
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>85</v>
+        <v>467</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>85</v>
@@ -12228,16 +12223,16 @@
         <v>184</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>620</v>
+        <v>468</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>621</v>
+        <v>469</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>622</v>
+        <v>470</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>85</v>
@@ -12265,37 +12260,37 @@
         <v>189</v>
       </c>
       <c r="Y76" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF76" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="Z76" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AA76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE76" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF76" t="s" s="2">
-        <v>619</v>
-      </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>624</v>
+        <v>85</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>107</v>
@@ -12313,31 +12308,31 @@
         <v>85</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>85</v>
+        <v>474</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>138</v>
+        <v>475</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>85</v>
+        <v>477</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>456</v>
+        <v>85</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -12356,19 +12351,19 @@
         <v>85</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>184</v>
+        <v>86</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>457</v>
+        <v>625</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>458</v>
+        <v>626</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>459</v>
+        <v>533</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>460</v>
+        <v>534</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>85</v>
@@ -12393,13 +12388,13 @@
         <v>85</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>461</v>
+        <v>85</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>462</v>
+        <v>85</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>85</v>
@@ -12417,7 +12412,7 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12444,29 +12439,31 @@
         <v>85</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>463</v>
+        <v>85</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>464</v>
+        <v>536</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>465</v>
+        <v>537</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS77" t="s" s="2">
-        <v>466</v>
+        <v>85</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C78" s="2"/>
+        <v>595</v>
+      </c>
+      <c r="C78" t="s" s="2">
+        <v>628</v>
+      </c>
       <c r="D78" t="s" s="2">
         <v>85</v>
       </c>
@@ -12475,7 +12472,7 @@
         <v>83</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>85</v>
@@ -12484,22 +12481,22 @@
         <v>85</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>86</v>
+        <v>530</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>627</v>
+        <v>596</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>628</v>
+        <v>597</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>522</v>
+        <v>598</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>523</v>
+        <v>599</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>85</v>
@@ -12548,7 +12545,7 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>626</v>
+        <v>595</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -12578,10 +12575,10 @@
         <v>85</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>525</v>
+        <v>601</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>526</v>
+        <v>602</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>85</v>
@@ -12595,11 +12592,9 @@
         <v>629</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="C79" t="s" s="2">
-        <v>630</v>
-      </c>
+        <v>603</v>
+      </c>
+      <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
         <v>85</v>
       </c>
@@ -12617,23 +12612,19 @@
         <v>85</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>519</v>
+        <v>162</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>598</v>
+        <v>163</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>601</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>85</v>
       </c>
@@ -12681,19 +12672,19 @@
         <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>597</v>
+        <v>165</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>85</v>
@@ -12711,10 +12702,10 @@
         <v>85</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>603</v>
+        <v>85</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>604</v>
+        <v>166</v>
       </c>
       <c r="AR79" t="s" s="2">
         <v>85</v>
@@ -12725,21 +12716,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>85</v>
@@ -12751,15 +12742,17 @@
         <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N80" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>85</v>
@@ -12808,19 +12801,19 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>85</v>
@@ -12852,14 +12845,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>140</v>
+        <v>541</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12872,24 +12865,26 @@
         <v>85</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K81" t="s" s="2">
         <v>141</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>142</v>
+        <v>542</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>168</v>
+        <v>543</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="O81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>85</v>
       </c>
@@ -12937,7 +12932,7 @@
         <v>85</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>172</v>
+        <v>544</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
@@ -12970,7 +12965,7 @@
         <v>85</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>85</v>
@@ -12981,45 +12976,45 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>530</v>
+        <v>85</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>531</v>
+        <v>607</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>532</v>
+        <v>608</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>144</v>
+        <v>609</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>85</v>
@@ -13044,13 +13039,13 @@
         <v>85</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>85</v>
+        <v>610</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>85</v>
+        <v>282</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>85</v>
@@ -13068,22 +13063,22 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>533</v>
+        <v>606</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>85</v>
+        <v>633</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>85</v>
@@ -13095,16 +13090,16 @@
         <v>85</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>85</v>
+        <v>611</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>85</v>
+        <v>285</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>138</v>
+        <v>286</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>85</v>
+        <v>287</v>
       </c>
       <c r="AS82" t="s" s="2">
         <v>85</v>
@@ -13115,7 +13110,7 @@
         <v>634</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>608</v>
+        <v>635</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13123,35 +13118,31 @@
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G83" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J83" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>609</v>
+        <v>163</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>280</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>85</v>
       </c>
@@ -13175,13 +13166,13 @@
         <v>85</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>481</v>
+        <v>85</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>612</v>
+        <v>85</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>282</v>
+        <v>85</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>85</v>
@@ -13199,10 +13190,10 @@
         <v>85</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>608</v>
+        <v>165</v>
       </c>
       <c r="AG83" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH83" t="s" s="2">
         <v>95</v>
@@ -13211,10 +13202,10 @@
         <v>85</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>635</v>
+        <v>85</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>85</v>
@@ -13226,16 +13217,16 @@
         <v>85</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>613</v>
+        <v>85</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>285</v>
+        <v>85</v>
       </c>
       <c r="AQ83" t="s" s="2">
-        <v>286</v>
+        <v>166</v>
       </c>
       <c r="AR83" t="s" s="2">
-        <v>287</v>
+        <v>85</v>
       </c>
       <c r="AS83" t="s" s="2">
         <v>85</v>
@@ -13250,14 +13241,14 @@
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>85</v>
@@ -13269,15 +13260,17 @@
         <v>85</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>85</v>
@@ -13314,31 +13307,31 @@
         <v>85</v>
       </c>
       <c r="AB84" t="s" s="2">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="AC84" t="s" s="2">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AD84" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE84" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>85</v>
@@ -13377,7 +13370,7 @@
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -13393,21 +13386,23 @@
         <v>85</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>141</v>
+        <v>292</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>142</v>
+        <v>293</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>168</v>
+        <v>294</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>295</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>296</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>85</v>
       </c>
@@ -13443,19 +13438,19 @@
         <v>85</v>
       </c>
       <c r="AB85" t="s" s="2">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="AC85" t="s" s="2">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AD85" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE85" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>172</v>
+        <v>297</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
@@ -13467,7 +13462,7 @@
         <v>85</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>85</v>
@@ -13485,10 +13480,10 @@
         <v>85</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>85</v>
+        <v>299</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>166</v>
+        <v>300</v>
       </c>
       <c r="AR85" t="s" s="2">
         <v>85</v>
@@ -13513,7 +13508,7 @@
         <v>83</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>85</v>
@@ -13522,23 +13517,19 @@
         <v>85</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>292</v>
+        <v>162</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>293</v>
+        <v>163</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>296</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>85</v>
       </c>
@@ -13586,19 +13577,19 @@
         <v>85</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>297</v>
+        <v>165</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>85</v>
@@ -13616,10 +13607,10 @@
         <v>85</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>299</v>
+        <v>85</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>300</v>
+        <v>166</v>
       </c>
       <c r="AR86" t="s" s="2">
         <v>85</v>
@@ -13637,14 +13628,14 @@
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>85</v>
@@ -13656,15 +13647,17 @@
         <v>85</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>168</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>144</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>85</v>
@@ -13701,31 +13694,31 @@
         <v>85</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>85</v>
+        <v>146</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>85</v>
@@ -13764,37 +13757,39 @@
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>141</v>
+        <v>109</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>142</v>
+        <v>304</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>168</v>
+        <v>305</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="O88" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>85</v>
       </c>
@@ -13803,7 +13798,7 @@
         <v>85</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>85</v>
+        <v>646</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>85</v>
@@ -13830,34 +13825,34 @@
         <v>85</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>172</v>
+        <v>308</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>85</v>
+        <v>647</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>85</v>
@@ -13872,10 +13867,10 @@
         <v>85</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>85</v>
+        <v>311</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>166</v>
+        <v>312</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>85</v>
@@ -13886,10 +13881,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13903,7 +13898,7 @@
         <v>95</v>
       </c>
       <c r="H89" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I89" t="s" s="2">
         <v>85</v>
@@ -13912,20 +13907,18 @@
         <v>96</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>85</v>
       </c>
@@ -13934,7 +13927,7 @@
         <v>85</v>
       </c>
       <c r="S89" t="s" s="2">
-        <v>648</v>
+        <v>85</v>
       </c>
       <c r="T89" t="s" s="2">
         <v>85</v>
@@ -13973,7 +13966,7 @@
         <v>85</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -13988,7 +13981,7 @@
         <v>107</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>649</v>
+        <v>85</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>85</v>
@@ -14003,10 +13996,10 @@
         <v>85</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>85</v>
@@ -14034,7 +14027,7 @@
         <v>95</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>85</v>
@@ -14043,18 +14036,18 @@
         <v>96</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>162</v>
+        <v>115</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="O90" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" t="s" s="2">
+        <v>323</v>
+      </c>
       <c r="P90" t="s" s="2">
         <v>85</v>
       </c>
@@ -14102,7 +14095,7 @@
         <v>85</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
@@ -14117,7 +14110,7 @@
         <v>107</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>85</v>
+        <v>652</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>85</v>
@@ -14132,10 +14125,10 @@
         <v>85</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="AR90" t="s" s="2">
         <v>85</v>
@@ -14146,10 +14139,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14163,7 +14156,7 @@
         <v>95</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>85</v>
@@ -14172,17 +14165,17 @@
         <v>96</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>85</v>
@@ -14231,7 +14224,7 @@
         <v>85</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14246,7 +14239,7 @@
         <v>107</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>654</v>
+        <v>85</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>85</v>
@@ -14261,10 +14254,10 @@
         <v>85</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>85</v>
@@ -14301,17 +14294,19 @@
         <v>96</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>162</v>
+        <v>337</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="N92" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N92" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="O92" t="s" s="2">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>85</v>
@@ -14360,7 +14355,7 @@
         <v>85</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -14390,10 +14385,10 @@
         <v>85</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>85</v>
@@ -14430,19 +14425,19 @@
         <v>96</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>337</v>
+        <v>162</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>85</v>
@@ -14491,7 +14486,7 @@
         <v>85</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
@@ -14521,10 +14516,10 @@
         <v>85</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>85</v>
@@ -14538,7 +14533,7 @@
         <v>659</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>660</v>
+        <v>612</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14561,19 +14556,19 @@
         <v>96</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>162</v>
+        <v>436</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>346</v>
+        <v>613</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>347</v>
+        <v>614</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>348</v>
+        <v>615</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>349</v>
+        <v>440</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>85</v>
@@ -14610,19 +14605,17 @@
         <v>85</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC94" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>350</v>
+        <v>612</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14649,29 +14642,31 @@
         <v>85</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>85</v>
+        <v>616</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>351</v>
+        <v>444</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>352</v>
+        <v>445</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS94" t="s" s="2">
-        <v>85</v>
+        <v>446</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C95" s="2"/>
+        <v>612</v>
+      </c>
+      <c r="C95" t="s" s="2">
+        <v>455</v>
+      </c>
       <c r="D95" t="s" s="2">
         <v>85</v>
       </c>
@@ -14683,7 +14678,7 @@
         <v>95</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>85</v>
@@ -14692,19 +14687,19 @@
         <v>96</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>435</v>
+        <v>162</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="N95" t="s" s="2">
         <v>615</v>
       </c>
-      <c r="M95" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>617</v>
-      </c>
       <c r="O95" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>85</v>
@@ -14741,17 +14736,19 @@
         <v>85</v>
       </c>
       <c r="AB95" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AC95" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE95" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -14766,7 +14763,7 @@
         <v>107</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>85</v>
+        <v>661</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>85</v>
@@ -14778,19 +14775,19 @@
         <v>85</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS95" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="96" hidden="true">
@@ -14798,11 +14795,9 @@
         <v>662</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C96" t="s" s="2">
-        <v>663</v>
-      </c>
+        <v>617</v>
+      </c>
+      <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
         <v>85</v>
       </c>
@@ -14814,28 +14809,28 @@
         <v>95</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>439</v>
+        <v>461</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>85</v>
@@ -14860,13 +14855,13 @@
         <v>85</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>85</v>
+        <v>621</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>85</v>
+        <v>462</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>85</v>
@@ -14884,7 +14879,7 @@
         <v>85</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -14893,13 +14888,13 @@
         <v>95</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>85</v>
+        <v>622</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>664</v>
+        <v>85</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>85</v>
@@ -14911,41 +14906,41 @@
         <v>85</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>618</v>
+        <v>85</v>
       </c>
       <c r="AP96" t="s" s="2">
-        <v>443</v>
+        <v>138</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS96" t="s" s="2">
-        <v>445</v>
+        <v>85</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>85</v>
+        <v>467</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>85</v>
@@ -14957,16 +14952,16 @@
         <v>184</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>620</v>
+        <v>468</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>621</v>
+        <v>469</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>622</v>
+        <v>470</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>450</v>
+        <v>471</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>85</v>
@@ -14991,46 +14986,44 @@
         <v>85</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y97" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y97" s="2"/>
+      <c r="Z97" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AF97" t="s" s="2">
         <v>623</v>
       </c>
-      <c r="Z97" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>619</v>
-      </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH97" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>624</v>
+        <v>85</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>85</v>
+        <v>665</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>85</v>
@@ -15042,19 +15035,19 @@
         <v>85</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>85</v>
+        <v>474</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>138</v>
+        <v>475</v>
       </c>
       <c r="AQ97" t="s" s="2">
-        <v>454</v>
+        <v>476</v>
       </c>
       <c r="AR97" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS97" t="s" s="2">
-        <v>85</v>
+        <v>477</v>
       </c>
     </row>
     <row r="98" hidden="true">
@@ -15062,11 +15055,11 @@
         <v>666</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>456</v>
+        <v>85</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -15076,7 +15069,7 @@
         <v>84</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>85</v>
@@ -15085,19 +15078,19 @@
         <v>85</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>184</v>
+        <v>86</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>457</v>
+        <v>625</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>458</v>
+        <v>626</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>459</v>
+        <v>533</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>460</v>
+        <v>534</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>85</v>
@@ -15122,11 +15115,13 @@
         <v>85</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y98" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="Z98" t="s" s="2">
-        <v>667</v>
+        <v>85</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>85</v>
@@ -15144,7 +15139,7 @@
         <v>85</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -15159,7 +15154,7 @@
         <v>107</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>668</v>
+        <v>85</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>85</v>
@@ -15171,154 +15166,23 @@
         <v>85</v>
       </c>
       <c r="AO98" t="s" s="2">
-        <v>463</v>
+        <v>85</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>464</v>
+        <v>536</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>465</v>
+        <v>537</v>
       </c>
       <c r="AR98" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS98" t="s" s="2">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="AQ99" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="AR99" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS99" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS99">
+  <autoFilter ref="A1:AS98">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15328,7 +15192,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI98">
+  <conditionalFormatting sqref="A2:AI97">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4093" uniqueCount="667">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4093" uniqueCount="670">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -671,7 +671,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1476: source value from MICROBIOLOGY - IEN (63.05-.001)</t>
+    <t>1476: source value based on MICROBIOLOGY - IEN (63.05-.001)</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -946,7 +946,11 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t>1480: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) case Not NULL</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lombo-49-1480:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) {null}</t>
+  </si>
+  <si>
+    <t>1480: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) if Not NULL</t>
   </si>
   <si>
     <t>C*E.1-8, C*E.10-22</t>
@@ -980,10 +984,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lombo-49-1480-1:undefined: if Not NULL then http://loinc.org {null}</t>
-  </si>
-  <si>
-    <t>1480-1: fixed value = http://loinc.org case Not NULL</t>
+lombo-49-1480-1:If (undefined) is Not NULL then fixed value http://loinc.org {null}</t>
+  </si>
+  <si>
+    <t>1480-1: fixed value = http://loinc.org if Not NULL</t>
   </si>
   <si>
     <t>C*E.3</t>
@@ -1028,7 +1032,11 @@
     <t>Coding.code</t>
   </si>
   <si>
-    <t>1480-2: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) case Not NULL</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lombo-49-1480-2:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) {null}</t>
+  </si>
+  <si>
+    <t>1480-2: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) if Not NULL</t>
   </si>
   <si>
     <t>C*E.1</t>
@@ -1052,7 +1060,11 @@
     <t>Coding.display</t>
   </si>
   <si>
-    <t>1480-3: source value from MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) case Not NULL</t>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+lombo-49-1480-3:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) {null}</t>
+  </si>
+  <si>
+    <t>1480-3: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) if Not NULL</t>
   </si>
   <si>
     <t>C*E.2 - but note this is not well followed</t>
@@ -1132,7 +1144,7 @@
     <t>Observations have no value if you don't know who or what they're about.</t>
   </si>
   <si>
-    <t>844: reference from PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
+    <t>844: reference based on PATIENT - LABORATORY REFERENCE &gt; LAB DATA - LRDFN (2-63 &gt; 63-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.LRDFN,Micro.AntibioticSensitivityComment.LRDFN,Micro.BacteriologyReports.LRDFN,Micro.MicroAntibioticLevel.LRDFN,Micro.MicroAudit.LRDFN,Micro.Microbiology.LRDFN,Micro.MicroOrderedTest.LRDFN,Micro.MicroSterilityResults.LRDFN,Micro.MycobacteriologyReports.LRDFN,Micro.Mycology.LRDFN,Micro.MycologyReports.LRDFN,Micro.Parasitology.LRDFN,Micro.ParasitologyReports.LRDFN,Micro.ParasitologyStage.LRDFN,Micro.Virology.LRDFN,Micro.VirologyReports.LRDFN,Pathology.Autopsy.LRDFN,Pathology.CytoOrganTissueFunction.StaffIEN,SStaff.SMicroOrderedTest.LRDFN</t>
@@ -1264,7 +1276,7 @@
 </t>
   </si>
   <si>
-    <t>1450: source value from MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
+    <t>1450: source value based on MICROBIOLOGY - DATE/TIME SPECIMEN TAKEN (63.05-.01)</t>
   </si>
   <si>
     <t>Micro.AntibioticSensitivity.SpecimenTakenDateTime,Micro.AntibioticSensitivityComment.SpecimenTakenDateTime,Micro.BacteriologyReports.SpecimenTakenDateTime,Micro.MicroAntibioticLevel.SpecimenTakenDateTime,Micro.MicroAudit.SpecimenTakenDateTime,Micro.Microbiology.SpecimenTakenDateTime,Micro.MicroOrderedTest.SpecimenTakenDateTime,Micro.MicroSterilityResults.SpecimenTakenDateTime,Micro.MycobacteriologyReports.SpecimenTakenDateTime,Micro.Mycology.SpecimenTakenDateTime,Micro.MycologyReports.SpecimenTakenDateTime,Micro.Parasitology.SpecimenTakenDateTime,Micro.ParasitologyReports.SpecimenTakenDateTime,Micro.ParasitologyStage.SpecimenTakenDateTime,Micro.Virology.SpecimenTakenDateTime,Micro.VirologyReports.SpecimenTakenDateTime,SStaff.SMicroOrderedTest.SpecimenTakenDateTime</t>
@@ -1286,7 +1298,7 @@
     <t>For Observations that don’t require review and verification, it may be the same as the [`lastUpdated` ](http://hl7.org/fhir/R4/resource-definitions.html#Meta.lastUpdated) time of the resource itself.  For Observations that do require review and verification for certain updates, it might not be the same as the `lastUpdated` time of the resource itself due to a non-clinically significant update that doesn’t require the new version to be reviewed and verified again.</t>
   </si>
   <si>
-    <t>1484: source value from MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
+    <t>1484: source value based on MICROBIOLOGY - DATE REPORT COMPLETED (63.05-.03)</t>
   </si>
   <si>
     <t>Micro.Microbiology.ReportCompletedDateTime</t>
@@ -1346,7 +1358,7 @@
 </t>
   </si>
   <si>
-    <t>1464: reference from MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
+    <t>1464: reference based on MICROBIOLOGY - ACCESSIONING INSTITUTION (63.05-.112)</t>
   </si>
   <si>
     <t>Micro.Microbiology.AccessioningInstitutionIEN</t>
@@ -1365,7 +1377,7 @@
 </t>
   </si>
   <si>
-    <t>1679: reference from MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
+    <t>1679: reference based on MICROBIOLOGY - VERIFY PERSON (63.05-.04)</t>
   </si>
   <si>
     <t>Micro.Microbiology.VerifyingStaffIEN</t>
@@ -1529,7 +1541,7 @@
     <t>Need to be able to provide free text additional information.</t>
   </si>
   <si>
-    <t>1454: source value from MICROBIOLOGY - COMMENT ON SPECIMEN (63.05-.99)</t>
+    <t>1454: source value based on MICROBIOLOGY - COMMENT ON SPECIMEN (63.05-.99)</t>
   </si>
   <si>
     <t>Micro.Microbiology.SpecimenComment</t>
@@ -1618,7 +1630,7 @@
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
   </si>
   <si>
-    <t>1659: reference from MICROBIOLOGY - MICROBIOLOGY ACCESSION (63.05-.06)</t>
+    <t>1659: reference based on MICROBIOLOGY - MICROBIOLOGY ACCESSION (63.05-.06)</t>
   </si>
   <si>
     <t>Micro.Microbiology.MicrobiologyAccession</t>
@@ -2055,7 +2067,7 @@
     <t>Observation.component.code.coding.code</t>
   </si>
   <si>
-    <t>1522-1: fixed value without value?</t>
+    <t>1522-1: fixed value</t>
   </si>
   <si>
     <t>Observation.component:va-component.code.coding.display</t>
@@ -2082,7 +2094,7 @@
     <t>Observation.component:va-component.value[x]:valueString</t>
   </si>
   <si>
-    <t>1523: source value from MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (63.05-12 &gt; 63.3-5+to+160)</t>
+    <t>1523: source value based on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (63.05-12 &gt; 63.3-5+to+160)</t>
   </si>
   <si>
     <t>Observation.component:va-component.dataAbsentReason</t>
@@ -2452,7 +2464,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="250.93359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="251.96875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="99.32421875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="29.69921875" customWidth="true" bestFit="true"/>
@@ -6061,10 +6073,10 @@
         <v>85</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>107</v>
+        <v>298</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>85</v>
@@ -6079,10 +6091,10 @@
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -6093,10 +6105,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6220,10 +6232,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6349,10 +6361,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6378,16 +6390,16 @@
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>85</v>
@@ -6436,7 +6448,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6448,10 +6460,10 @@
         <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>85</v>
@@ -6466,10 +6478,10 @@
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -6480,10 +6492,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6509,13 +6521,13 @@
         <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6565,7 +6577,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6595,10 +6607,10 @@
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>85</v>
@@ -6609,10 +6621,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6638,14 +6650,14 @@
         <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6694,7 +6706,7 @@
         <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6706,10 +6718,10 @@
         <v>85</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>107</v>
+        <v>326</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>85</v>
@@ -6724,10 +6736,10 @@
         <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
@@ -6738,10 +6750,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6767,14 +6779,14 @@
         <v>162</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6823,7 +6835,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6835,10 +6847,10 @@
         <v>85</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>107</v>
+        <v>335</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>85</v>
@@ -6853,10 +6865,10 @@
         <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
@@ -6867,10 +6879,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6893,19 +6905,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6954,7 +6966,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6984,10 +6996,10 @@
         <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
@@ -6998,10 +7010,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7027,16 +7039,16 @@
         <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -7085,7 +7097,7 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -7115,10 +7127,10 @@
         <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
@@ -7129,10 +7141,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7155,19 +7167,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -7216,7 +7228,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7231,28 +7243,28 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AS37" t="s" s="2">
         <v>85</v>
@@ -7260,10 +7272,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7286,16 +7298,16 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7345,7 +7357,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7378,10 +7390,10 @@
         <v>285</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>85</v>
@@ -7389,14 +7401,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7415,19 +7427,19 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7476,7 +7488,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7500,19 +7512,19 @@
         <v>85</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>85</v>
@@ -7520,14 +7532,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7546,19 +7558,19 @@
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7595,7 +7607,7 @@
         <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7605,7 +7617,7 @@
         <v>171</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7614,10 +7626,10 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>85</v>
@@ -7629,19 +7641,19 @@
         <v>85</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>85</v>
@@ -7649,16 +7661,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7677,19 +7689,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7738,7 +7750,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7747,34 +7759,34 @@
         <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>85</v>
@@ -7782,10 +7794,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7808,16 +7820,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7867,7 +7879,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7882,13 +7894,13 @@
         <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>85</v>
@@ -7897,13 +7909,13 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>85</v>
@@ -7911,10 +7923,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7937,17 +7949,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -7984,7 +7996,7 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -7994,7 +8006,7 @@
         <v>171</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -8018,19 +8030,19 @@
         <v>85</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -8038,13 +8050,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
@@ -8066,17 +8078,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -8125,7 +8137,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -8140,28 +8152,28 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>85</v>
@@ -8169,13 +8181,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8197,17 +8209,17 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8256,7 +8268,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8271,28 +8283,28 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8300,10 +8312,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8326,19 +8338,19 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8375,7 +8387,7 @@
         <v>85</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -8385,7 +8397,7 @@
         <v>171</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8394,10 +8406,10 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8412,30 +8424,30 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>85</v>
@@ -8457,19 +8469,19 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8518,7 +8530,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8527,13 +8539,13 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>85</v>
@@ -8545,30 +8557,30 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>85</v>
@@ -8593,16 +8605,16 @@
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8651,7 +8663,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8660,13 +8672,13 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>85</v>
@@ -8678,30 +8690,30 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>85</v>
@@ -8726,16 +8738,16 @@
         <v>162</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8784,7 +8796,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8793,13 +8805,13 @@
         <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>85</v>
@@ -8811,27 +8823,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8857,16 +8869,16 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8895,7 +8907,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8913,7 +8925,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8922,13 +8934,13 @@
         <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>85</v>
@@ -8946,7 +8958,7 @@
         <v>138</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8957,14 +8969,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8986,16 +8998,16 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -9023,10 +9035,10 @@
         <v>189</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -9044,7 +9056,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9071,27 +9083,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9114,19 +9126,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -9175,7 +9187,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9190,10 +9202,10 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>85</v>
@@ -9205,10 +9217,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9219,10 +9231,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9248,13 +9260,13 @@
         <v>184</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9280,13 +9292,13 @@
         <v>85</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>85</v>
@@ -9304,7 +9316,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9331,27 +9343,27 @@
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9377,16 +9389,16 @@
         <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9411,13 +9423,13 @@
         <v>85</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>85</v>
@@ -9435,7 +9447,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9465,10 +9477,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9479,10 +9491,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9505,16 +9517,16 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9564,7 +9576,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9579,39 +9591,39 @@
         <v>107</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>519</v>
+        <v>522</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9634,16 +9646,16 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9693,7 +9705,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9720,27 +9732,27 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>528</v>
+        <v>531</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9763,19 +9775,19 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9824,7 +9836,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9836,7 +9848,7 @@
         <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9854,10 +9866,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9868,10 +9880,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9995,10 +10007,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10124,14 +10136,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -10153,10 +10165,10 @@
         <v>141</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>144</v>
@@ -10211,7 +10223,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10255,10 +10267,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10281,13 +10293,13 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10338,7 +10350,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10347,7 +10359,7 @@
         <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -10368,10 +10380,10 @@
         <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10382,10 +10394,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10408,13 +10420,13 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10465,7 +10477,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10474,7 +10486,7 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10495,10 +10507,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10509,10 +10521,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10538,16 +10550,16 @@
         <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10575,10 +10587,10 @@
         <v>119</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10596,7 +10608,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10623,13 +10635,13 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10640,10 +10652,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10669,16 +10681,16 @@
         <v>184</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
@@ -10703,13 +10715,13 @@
         <v>85</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>85</v>
@@ -10727,7 +10739,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10754,13 +10766,13 @@
         <v>85</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10771,10 +10783,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10797,17 +10809,17 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>85</v>
@@ -10856,7 +10868,7 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -10889,7 +10901,7 @@
         <v>85</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10900,10 +10912,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10929,10 +10941,10 @@
         <v>162</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10983,7 +10995,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -11013,10 +11025,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -11027,10 +11039,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11053,16 +11065,16 @@
         <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -11112,7 +11124,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11142,10 +11154,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11156,10 +11168,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11182,16 +11194,16 @@
         <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11241,7 +11253,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11271,10 +11283,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11285,10 +11297,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11311,19 +11323,19 @@
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11360,7 +11372,7 @@
         <v>85</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AC69" s="2"/>
       <c r="AD69" t="s" s="2">
@@ -11370,7 +11382,7 @@
         <v>171</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11400,10 +11412,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11414,10 +11426,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11541,10 +11553,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11670,14 +11682,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11699,10 +11711,10 @@
         <v>141</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>144</v>
@@ -11757,7 +11769,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11801,10 +11813,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11830,13 +11842,13 @@
         <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="O73" t="s" s="2">
         <v>280</v>
@@ -11864,10 +11876,10 @@
         <v>85</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="Z73" t="s" s="2">
         <v>282</v>
@@ -11888,7 +11900,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>95</v>
@@ -11915,7 +11927,7 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>285</v>
@@ -11932,10 +11944,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11958,19 +11970,19 @@
         <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -12019,7 +12031,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12046,27 +12058,27 @@
         <v>85</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS74" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12092,16 +12104,16 @@
         <v>184</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -12129,10 +12141,10 @@
         <v>189</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>85</v>
@@ -12150,7 +12162,7 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12159,7 +12171,7 @@
         <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
@@ -12183,7 +12195,7 @@
         <v>138</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
@@ -12194,14 +12206,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -12223,16 +12235,16 @@
         <v>184</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>85</v>
@@ -12260,10 +12272,10 @@
         <v>189</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>85</v>
@@ -12281,7 +12293,7 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12308,27 +12320,27 @@
         <v>85</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12354,16 +12366,16 @@
         <v>86</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>85</v>
@@ -12412,7 +12424,7 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12442,10 +12454,10 @@
         <v>85</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>85</v>
@@ -12456,13 +12468,13 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>85</v>
@@ -12484,19 +12496,19 @@
         <v>96</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>85</v>
@@ -12545,7 +12557,7 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -12575,10 +12587,10 @@
         <v>85</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>85</v>
@@ -12589,10 +12601,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12716,10 +12728,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12845,14 +12857,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12874,10 +12886,10 @@
         <v>141</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>144</v>
@@ -12932,7 +12944,7 @@
         <v>85</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
@@ -12976,10 +12988,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13005,13 +13017,13 @@
         <v>184</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="O82" t="s" s="2">
         <v>280</v>
@@ -13039,10 +13051,10 @@
         <v>85</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="Z82" t="s" s="2">
         <v>282</v>
@@ -13063,7 +13075,7 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>95</v>
@@ -13078,7 +13090,7 @@
         <v>107</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>85</v>
@@ -13090,7 +13102,7 @@
         <v>85</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>285</v>
@@ -13107,10 +13119,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13234,10 +13246,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13363,10 +13375,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13480,10 +13492,10 @@
         <v>85</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AR85" t="s" s="2">
         <v>85</v>
@@ -13494,10 +13506,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>641</v>
+        <v>644</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13621,10 +13633,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13750,10 +13762,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13779,16 +13791,16 @@
         <v>109</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>85</v>
@@ -13798,7 +13810,7 @@
         <v>85</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>85</v>
@@ -13837,7 +13849,7 @@
         <v>85</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -13852,7 +13864,7 @@
         <v>107</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>85</v>
@@ -13867,10 +13879,10 @@
         <v>85</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>85</v>
@@ -13881,10 +13893,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13910,13 +13922,13 @@
         <v>162</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13966,7 +13978,7 @@
         <v>85</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -13996,10 +14008,10 @@
         <v>85</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>85</v>
@@ -14010,10 +14022,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14039,14 +14051,14 @@
         <v>115</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>85</v>
@@ -14095,7 +14107,7 @@
         <v>85</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
@@ -14110,7 +14122,7 @@
         <v>107</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>85</v>
@@ -14125,10 +14137,10 @@
         <v>85</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AR90" t="s" s="2">
         <v>85</v>
@@ -14139,10 +14151,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14168,14 +14180,14 @@
         <v>162</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>85</v>
@@ -14224,7 +14236,7 @@
         <v>85</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14254,10 +14266,10 @@
         <v>85</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>85</v>
@@ -14268,10 +14280,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14294,19 +14306,19 @@
         <v>96</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>85</v>
@@ -14355,7 +14367,7 @@
         <v>85</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -14385,10 +14397,10 @@
         <v>85</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>85</v>
@@ -14399,10 +14411,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14428,16 +14440,16 @@
         <v>162</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>85</v>
@@ -14486,7 +14498,7 @@
         <v>85</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
@@ -14516,10 +14528,10 @@
         <v>85</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>85</v>
@@ -14530,10 +14542,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14556,19 +14568,19 @@
         <v>96</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>85</v>
@@ -14605,7 +14617,7 @@
         <v>85</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
@@ -14615,7 +14627,7 @@
         <v>171</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14642,30 +14654,30 @@
         <v>85</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS94" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>85</v>
@@ -14690,16 +14702,16 @@
         <v>162</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>85</v>
@@ -14748,7 +14760,7 @@
         <v>85</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -14763,7 +14775,7 @@
         <v>107</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>85</v>
@@ -14775,27 +14787,27 @@
         <v>85</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS95" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14821,16 +14833,16 @@
         <v>184</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>85</v>
@@ -14858,10 +14870,10 @@
         <v>189</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>85</v>
@@ -14879,7 +14891,7 @@
         <v>85</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -14888,7 +14900,7 @@
         <v>95</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>107</v>
@@ -14912,7 +14924,7 @@
         <v>138</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>85</v>
@@ -14923,14 +14935,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14952,16 +14964,16 @@
         <v>184</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>85</v>
@@ -14990,7 +15002,7 @@
       </c>
       <c r="Y97" s="2"/>
       <c r="Z97" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>85</v>
@@ -15008,7 +15020,7 @@
         <v>85</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -15023,7 +15035,7 @@
         <v>107</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>85</v>
@@ -15035,27 +15047,27 @@
         <v>85</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AQ97" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AR97" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS97" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15081,16 +15093,16 @@
         <v>86</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>85</v>
@@ -15139,7 +15151,7 @@
         <v>85</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -15169,10 +15181,10 @@
         <v>85</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="AR98" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4093" uniqueCount="670">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4095" uniqueCount="672">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -798,6 +798,9 @@
   </si>
   <si>
     <t>Need to track the status of individual results. Some results are finalized before the whole report is finalized.</t>
+  </si>
+  <si>
+    <t>see mapping [VF_LabObservationStatus](ConceptMap-VF-LabObservationStatus.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/LabObservationStatus</t>
@@ -2101,6 +2104,9 @@
   </si>
   <si>
     <t>Observation.component:va-component.interpretation</t>
+  </si>
+  <si>
+    <t>see mapping [VF_AntibioticSensitivityInterpretation](ConceptMap-VF-AntibioticSensitivityInterpretation.html)</t>
   </si>
   <si>
     <t>http://va.gov/fhir/ValueSet/AntibioticSensitivityInterpretation</t>
@@ -2453,7 +2459,7 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="101.265625" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="56.85546875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
@@ -5261,9 +5267,11 @@
       <c r="X22" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y22" s="2"/>
+      <c r="Y22" t="s" s="2">
+        <v>252</v>
+      </c>
       <c r="Z22" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>85</v>
@@ -5296,28 +5304,28 @@
         <v>107</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AQ22" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AR22" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AS22" t="s" s="2">
         <v>85</v>
@@ -5325,10 +5333,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5354,16 +5362,16 @@
         <v>184</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>85</v>
@@ -5373,7 +5381,7 @@
         <v>85</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>85</v>
@@ -5391,16 +5399,16 @@
         <v>119</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB23" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5410,7 +5418,7 @@
         <v>171</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>83</v>
@@ -5425,7 +5433,7 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>85</v>
@@ -5443,10 +5451,10 @@
         <v>85</v>
       </c>
       <c r="AQ23" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AR23" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -5454,13 +5462,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>85</v>
@@ -5485,16 +5493,16 @@
         <v>184</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>85</v>
@@ -5504,7 +5512,7 @@
         <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>85</v>
@@ -5522,10 +5530,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5543,7 +5551,7 @@
         <v>85</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>83</v>
@@ -5576,10 +5584,10 @@
         <v>85</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>85</v>
@@ -5587,14 +5595,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -5616,16 +5624,16 @@
         <v>184</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>85</v>
@@ -5653,10 +5661,10 @@
         <v>189</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>85</v>
@@ -5674,7 +5682,7 @@
         <v>85</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>95</v>
@@ -5698,30 +5706,30 @@
         <v>85</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ25" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AR25" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AS25" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5845,10 +5853,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5974,10 +5982,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -6000,19 +6008,19 @@
         <v>96</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>85</v>
@@ -6061,7 +6069,7 @@
         <v>85</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>83</v>
@@ -6073,10 +6081,10 @@
         <v>85</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>85</v>
@@ -6091,10 +6099,10 @@
         <v>85</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AQ28" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AR28" t="s" s="2">
         <v>85</v>
@@ -6105,10 +6113,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -6232,10 +6240,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6361,10 +6369,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6390,16 +6398,16 @@
         <v>109</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>85</v>
@@ -6448,7 +6456,7 @@
         <v>85</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>83</v>
@@ -6460,10 +6468,10 @@
         <v>85</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>85</v>
@@ -6478,10 +6486,10 @@
         <v>85</v>
       </c>
       <c r="AP31" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ31" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AR31" t="s" s="2">
         <v>85</v>
@@ -6492,10 +6500,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6521,13 +6529,13 @@
         <v>162</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6577,7 +6585,7 @@
         <v>85</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>83</v>
@@ -6607,10 +6615,10 @@
         <v>85</v>
       </c>
       <c r="AP32" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AQ32" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AR32" t="s" s="2">
         <v>85</v>
@@ -6621,10 +6629,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6650,14 +6658,14 @@
         <v>115</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>85</v>
@@ -6706,7 +6714,7 @@
         <v>85</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>83</v>
@@ -6718,10 +6726,10 @@
         <v>85</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AL33" t="s" s="2">
         <v>85</v>
@@ -6736,10 +6744,10 @@
         <v>85</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AQ33" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AR33" t="s" s="2">
         <v>85</v>
@@ -6750,10 +6758,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6779,14 +6787,14 @@
         <v>162</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>85</v>
@@ -6835,7 +6843,7 @@
         <v>85</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>83</v>
@@ -6847,10 +6855,10 @@
         <v>85</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>85</v>
@@ -6865,10 +6873,10 @@
         <v>85</v>
       </c>
       <c r="AP34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AQ34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AR34" t="s" s="2">
         <v>85</v>
@@ -6879,10 +6887,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6905,19 +6913,19 @@
         <v>96</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>85</v>
@@ -6966,7 +6974,7 @@
         <v>85</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>83</v>
@@ -6996,10 +7004,10 @@
         <v>85</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AQ35" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AR35" t="s" s="2">
         <v>85</v>
@@ -7010,10 +7018,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -7039,16 +7047,16 @@
         <v>162</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>85</v>
@@ -7097,7 +7105,7 @@
         <v>85</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>83</v>
@@ -7127,10 +7135,10 @@
         <v>85</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AQ36" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AR36" t="s" s="2">
         <v>85</v>
@@ -7141,10 +7149,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -7167,19 +7175,19 @@
         <v>96</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>85</v>
@@ -7228,7 +7236,7 @@
         <v>85</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>83</v>
@@ -7243,28 +7251,28 @@
         <v>107</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AQ37" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="AR37" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AS37" t="s" s="2">
         <v>85</v>
@@ -7272,10 +7280,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -7298,16 +7306,16 @@
         <v>96</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -7357,7 +7365,7 @@
         <v>85</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>83</v>
@@ -7387,13 +7395,13 @@
         <v>85</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AR38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="AS38" t="s" s="2">
         <v>85</v>
@@ -7401,14 +7409,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7427,19 +7435,19 @@
         <v>96</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>85</v>
@@ -7488,7 +7496,7 @@
         <v>85</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>83</v>
@@ -7512,19 +7520,19 @@
         <v>85</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AQ39" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AR39" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AS39" t="s" s="2">
         <v>85</v>
@@ -7532,14 +7540,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -7558,19 +7566,19 @@
         <v>96</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>85</v>
@@ -7607,7 +7615,7 @@
         <v>85</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AC40" s="2"/>
       <c r="AD40" t="s" s="2">
@@ -7617,7 +7625,7 @@
         <v>171</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>83</v>
@@ -7626,10 +7634,10 @@
         <v>95</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>85</v>
@@ -7641,19 +7649,19 @@
         <v>85</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ40" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AR40" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AS40" t="s" s="2">
         <v>85</v>
@@ -7661,16 +7669,16 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7689,19 +7697,19 @@
         <v>96</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>85</v>
@@ -7750,7 +7758,7 @@
         <v>85</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>83</v>
@@ -7759,34 +7767,34 @@
         <v>95</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AQ41" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AR41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AS41" t="s" s="2">
         <v>85</v>
@@ -7794,10 +7802,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7820,16 +7828,16 @@
         <v>96</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7879,7 +7887,7 @@
         <v>85</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>83</v>
@@ -7894,13 +7902,13 @@
         <v>107</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>85</v>
@@ -7909,13 +7917,13 @@
         <v>85</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AQ42" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AR42" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AS42" t="s" s="2">
         <v>85</v>
@@ -7923,10 +7931,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7949,17 +7957,17 @@
         <v>96</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>85</v>
@@ -7996,7 +8004,7 @@
         <v>85</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
@@ -8006,7 +8014,7 @@
         <v>171</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>83</v>
@@ -8030,19 +8038,19 @@
         <v>85</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AQ43" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AR43" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AS43" t="s" s="2">
         <v>85</v>
@@ -8050,13 +8058,13 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D44" t="s" s="2">
         <v>85</v>
@@ -8078,17 +8086,17 @@
         <v>96</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>85</v>
@@ -8137,7 +8145,7 @@
         <v>85</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>83</v>
@@ -8152,28 +8160,28 @@
         <v>107</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AQ44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AR44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AS44" t="s" s="2">
         <v>85</v>
@@ -8181,13 +8189,13 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="D45" t="s" s="2">
         <v>85</v>
@@ -8209,17 +8217,17 @@
         <v>96</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>85</v>
@@ -8268,7 +8276,7 @@
         <v>85</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>83</v>
@@ -8283,28 +8291,28 @@
         <v>107</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AQ45" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AR45" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AS45" t="s" s="2">
         <v>85</v>
@@ -8312,10 +8320,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -8338,19 +8346,19 @@
         <v>96</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>85</v>
@@ -8387,7 +8395,7 @@
         <v>85</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -8397,7 +8405,7 @@
         <v>171</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>83</v>
@@ -8406,10 +8414,10 @@
         <v>95</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>85</v>
@@ -8424,30 +8432,30 @@
         <v>85</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AP46" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ46" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AR46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS46" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>85</v>
@@ -8469,19 +8477,19 @@
         <v>96</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8530,7 +8538,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8539,13 +8547,13 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>85</v>
@@ -8557,30 +8565,30 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>85</v>
@@ -8605,16 +8613,16 @@
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8663,7 +8671,7 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
@@ -8672,13 +8680,13 @@
         <v>95</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>85</v>
@@ -8690,30 +8698,30 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>85</v>
@@ -8738,16 +8746,16 @@
         <v>162</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8796,7 +8804,7 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
@@ -8805,13 +8813,13 @@
         <v>95</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>85</v>
@@ -8823,27 +8831,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8869,16 +8877,16 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>85</v>
@@ -8907,7 +8915,7 @@
       </c>
       <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8925,7 +8933,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8934,13 +8942,13 @@
         <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>85</v>
@@ -8958,7 +8966,7 @@
         <v>138</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
@@ -8969,14 +8977,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -8998,16 +9006,16 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -9035,10 +9043,10 @@
         <v>189</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -9056,7 +9064,7 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
@@ -9083,27 +9091,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9126,19 +9134,19 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>85</v>
@@ -9187,7 +9195,7 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
@@ -9202,10 +9210,10 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>85</v>
@@ -9217,10 +9225,10 @@
         <v>85</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
@@ -9231,10 +9239,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9260,13 +9268,13 @@
         <v>184</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9292,13 +9300,13 @@
         <v>85</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>85</v>
@@ -9316,7 +9324,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9343,27 +9351,27 @@
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9389,16 +9397,16 @@
         <v>184</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9423,13 +9431,13 @@
         <v>85</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>85</v>
@@ -9447,7 +9455,7 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
@@ -9477,10 +9485,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9491,10 +9499,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9517,16 +9525,16 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -9576,7 +9584,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9591,39 +9599,39 @@
         <v>107</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9646,16 +9654,16 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9705,7 +9713,7 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
@@ -9732,27 +9740,27 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9775,19 +9783,19 @@
         <v>85</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9836,7 +9844,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9848,7 +9856,7 @@
         <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9866,10 +9874,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9880,10 +9888,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -10007,10 +10015,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -10136,14 +10144,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -10165,10 +10173,10 @@
         <v>141</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>144</v>
@@ -10223,7 +10231,7 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
@@ -10267,10 +10275,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10293,13 +10301,13 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -10350,7 +10358,7 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
@@ -10359,7 +10367,7 @@
         <v>95</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -10380,10 +10388,10 @@
         <v>85</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10394,10 +10402,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10420,13 +10428,13 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -10477,7 +10485,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10486,7 +10494,7 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10507,10 +10515,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10521,10 +10529,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10550,16 +10558,16 @@
         <v>184</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>85</v>
@@ -10587,10 +10595,10 @@
         <v>119</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10608,7 +10616,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10635,13 +10643,13 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10652,10 +10660,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10681,16 +10689,16 @@
         <v>184</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>85</v>
@@ -10715,13 +10723,13 @@
         <v>85</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>85</v>
@@ -10739,7 +10747,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10766,13 +10774,13 @@
         <v>85</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10783,10 +10791,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10809,17 +10817,17 @@
         <v>85</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>85</v>
@@ -10868,7 +10876,7 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
@@ -10901,7 +10909,7 @@
         <v>85</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10912,10 +10920,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10941,10 +10949,10 @@
         <v>162</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10995,7 +11003,7 @@
         <v>85</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
@@ -11025,10 +11033,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -11039,10 +11047,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11065,16 +11073,16 @@
         <v>96</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -11124,7 +11132,7 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
@@ -11154,10 +11162,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11168,10 +11176,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -11194,16 +11202,16 @@
         <v>96</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11253,7 +11261,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11283,10 +11291,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11297,10 +11305,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -11323,19 +11331,19 @@
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11372,7 +11380,7 @@
         <v>85</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AC69" s="2"/>
       <c r="AD69" t="s" s="2">
@@ -11382,7 +11390,7 @@
         <v>171</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11412,10 +11420,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11426,10 +11434,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11553,10 +11561,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -11682,14 +11690,14 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
@@ -11711,10 +11719,10 @@
         <v>141</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>144</v>
@@ -11769,7 +11777,7 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
@@ -11813,10 +11821,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11842,16 +11850,16 @@
         <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11876,13 +11884,13 @@
         <v>85</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>85</v>
@@ -11900,7 +11908,7 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>95</v>
@@ -11927,16 +11935,16 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AS73" t="s" s="2">
         <v>85</v>
@@ -11944,10 +11952,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11970,19 +11978,19 @@
         <v>96</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -12031,7 +12039,7 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
@@ -12058,27 +12066,27 @@
         <v>85</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS74" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -12104,16 +12112,16 @@
         <v>184</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -12141,10 +12149,10 @@
         <v>189</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>85</v>
@@ -12162,7 +12170,7 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
@@ -12171,7 +12179,7 @@
         <v>95</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
@@ -12195,7 +12203,7 @@
         <v>138</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
@@ -12206,14 +12214,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -12235,16 +12243,16 @@
         <v>184</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>85</v>
@@ -12272,10 +12280,10 @@
         <v>189</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>85</v>
@@ -12293,7 +12301,7 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
@@ -12320,27 +12328,27 @@
         <v>85</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -12366,16 +12374,16 @@
         <v>86</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>85</v>
@@ -12424,7 +12432,7 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12454,10 +12462,10 @@
         <v>85</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>85</v>
@@ -12468,13 +12476,13 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="D78" t="s" s="2">
         <v>85</v>
@@ -12496,19 +12504,19 @@
         <v>96</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>85</v>
@@ -12557,7 +12565,7 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -12587,10 +12595,10 @@
         <v>85</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>85</v>
@@ -12601,10 +12609,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12728,10 +12736,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12857,14 +12865,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12886,10 +12894,10 @@
         <v>141</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>144</v>
@@ -12944,7 +12952,7 @@
         <v>85</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
@@ -12988,10 +12996,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13017,16 +13025,16 @@
         <v>184</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>85</v>
@@ -13051,13 +13059,13 @@
         <v>85</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>85</v>
@@ -13075,7 +13083,7 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>95</v>
@@ -13090,7 +13098,7 @@
         <v>107</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>85</v>
@@ -13102,16 +13110,16 @@
         <v>85</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AS82" t="s" s="2">
         <v>85</v>
@@ -13119,10 +13127,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13246,10 +13254,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13375,10 +13383,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13401,19 +13409,19 @@
         <v>96</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>85</v>
@@ -13462,7 +13470,7 @@
         <v>85</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
@@ -13492,10 +13500,10 @@
         <v>85</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AR85" t="s" s="2">
         <v>85</v>
@@ -13506,10 +13514,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13633,10 +13641,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -13762,10 +13770,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13791,16 +13799,16 @@
         <v>109</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="O88" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>85</v>
@@ -13810,7 +13818,7 @@
         <v>85</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>85</v>
@@ -13849,7 +13857,7 @@
         <v>85</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -13864,7 +13872,7 @@
         <v>107</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>85</v>
@@ -13879,10 +13887,10 @@
         <v>85</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>85</v>
@@ -13893,10 +13901,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13922,13 +13930,13 @@
         <v>162</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -13978,7 +13986,7 @@
         <v>85</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -14008,10 +14016,10 @@
         <v>85</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>85</v>
@@ -14022,10 +14030,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14051,14 +14059,14 @@
         <v>115</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>85</v>
@@ -14107,7 +14115,7 @@
         <v>85</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
@@ -14122,7 +14130,7 @@
         <v>107</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>85</v>
@@ -14137,10 +14145,10 @@
         <v>85</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AR90" t="s" s="2">
         <v>85</v>
@@ -14151,10 +14159,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14180,14 +14188,14 @@
         <v>162</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>85</v>
@@ -14236,7 +14244,7 @@
         <v>85</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14266,10 +14274,10 @@
         <v>85</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>85</v>
@@ -14280,10 +14288,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -14306,19 +14314,19 @@
         <v>96</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>85</v>
@@ -14367,7 +14375,7 @@
         <v>85</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -14397,10 +14405,10 @@
         <v>85</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>85</v>
@@ -14411,10 +14419,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14440,16 +14448,16 @@
         <v>162</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>85</v>
@@ -14498,7 +14506,7 @@
         <v>85</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
@@ -14528,10 +14536,10 @@
         <v>85</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>85</v>
@@ -14542,10 +14550,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -14568,19 +14576,19 @@
         <v>96</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>85</v>
@@ -14617,7 +14625,7 @@
         <v>85</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AC94" s="2"/>
       <c r="AD94" t="s" s="2">
@@ -14627,7 +14635,7 @@
         <v>171</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
@@ -14654,30 +14662,30 @@
         <v>85</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS94" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>85</v>
@@ -14702,16 +14710,16 @@
         <v>162</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>85</v>
@@ -14760,7 +14768,7 @@
         <v>85</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
@@ -14775,7 +14783,7 @@
         <v>107</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>85</v>
@@ -14787,27 +14795,27 @@
         <v>85</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS95" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -14833,16 +14841,16 @@
         <v>184</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>85</v>
@@ -14870,10 +14878,10 @@
         <v>189</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>85</v>
@@ -14891,7 +14899,7 @@
         <v>85</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>83</v>
@@ -14900,7 +14908,7 @@
         <v>95</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>107</v>
@@ -14924,7 +14932,7 @@
         <v>138</v>
       </c>
       <c r="AQ96" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AR96" t="s" s="2">
         <v>85</v>
@@ -14935,14 +14943,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -14964,16 +14972,16 @@
         <v>184</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>85</v>
@@ -15000,9 +15008,11 @@
       <c r="X97" t="s" s="2">
         <v>178</v>
       </c>
-      <c r="Y97" s="2"/>
+      <c r="Y97" t="s" s="2">
+        <v>668</v>
+      </c>
       <c r="Z97" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>85</v>
@@ -15020,7 +15030,7 @@
         <v>85</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>83</v>
@@ -15035,7 +15045,7 @@
         <v>107</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AL97" t="s" s="2">
         <v>85</v>
@@ -15047,27 +15057,27 @@
         <v>85</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AQ97" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AR97" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS97" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -15093,16 +15103,16 @@
         <v>86</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>85</v>
@@ -15151,7 +15161,7 @@
         <v>85</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>83</v>
@@ -15181,10 +15191,10 @@
         <v>85</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AQ98" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AR98" t="s" s="2">
         <v>85</v>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -950,7 +950,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lombo-49-1480:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) {null}</t>
+lombo-49-1480:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) {true}</t>
   </si>
   <si>
     <t>1480: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-) if Not NULL</t>
@@ -987,7 +987,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lombo-49-1480-1:If (undefined) is Not NULL then fixed value http://loinc.org {null}</t>
+lombo-49-1480-1:If Not NULL then fixed value http://loinc.org {true}</t>
   </si>
   <si>
     <t>1480-1: fixed value = http://loinc.org if Not NULL</t>
@@ -1036,7 +1036,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lombo-49-1480-2:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) {null}</t>
+lombo-49-1480-2:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) {true}</t>
   </si>
   <si>
     <t>1480-2: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - CODE (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-.01) if Not NULL</t>
@@ -1064,7 +1064,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-lombo-49-1480-3:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) {null}</t>
+lombo-49-1480-3:If Not NULL then source value from (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) {true}</t>
   </si>
   <si>
     <t>1480-3: source value based on MICROBIOLOGY - ORDERED TEST &gt; ORDERED TEST - LAB TEST ORDERED &gt; LABORATORY TEST - SITE/SPECIMEN &gt; SITE/SPECIMEN - LOINC CODE &gt; LAB LOINC - COMPONENT (63.05-.35 &gt; 63.5-13 &gt; 60-100 &gt; 60.01-95.3 &gt; 95.3-1) if Not NULL</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AS$95</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4095" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3967" uniqueCount="663">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -843,6 +843,28 @@
   </si>
   <si>
     <t>Used for filtering what observations are retrieved and displayed.</t>
+  </si>
+  <si>
+    <t>Codes for high level observation categories.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pattern:$this}
+</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Observation.category:Laboratory</t>
+  </si>
+  <si>
+    <t>Laboratory</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -853,29 +875,7 @@
 &lt;/valueCodeableConcept&gt;</t>
   </si>
   <si>
-    <t>Codes for high level observation categories.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pattern:$this}
-</t>
-  </si>
-  <si>
     <t>843: fixed value = http://terminology.hl7.org/CodeSystem/observation-category#laboratory</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>Observation.category:Laboratory</t>
-  </si>
-  <si>
-    <t>Laboratory</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1428,37 +1428,6 @@
     <t>363714003 |Interprets|</t>
   </si>
   <si>
-    <t>Observation.value[x]:valueQuantity</t>
-  </si>
-  <si>
-    <t>valueQuantity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity
-</t>
-  </si>
-  <si>
-    <t>2062: target not supported</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>2063: target not supported</t>
-  </si>
-  <si>
-    <t>Observation.value[x]:valueString</t>
-  </si>
-  <si>
-    <t>valueString</t>
-  </si>
-  <si>
-    <t>2064: target not supported</t>
-  </si>
-  <si>
     <t>Observation.dataAbsentReason</t>
   </si>
   <si>
@@ -1620,7 +1589,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologySpecimen)
+    <t xml:space="preserve">Reference(http://va.gov/fhir/StructureDefinition/LabObservationMicrobiologyBacteriologySpecimen)
 </t>
   </si>
   <si>
@@ -2095,6 +2064,9 @@
   </si>
   <si>
     <t>Observation.component:va-component.value[x]:valueString</t>
+  </si>
+  <si>
+    <t>valueString</t>
   </si>
   <si>
     <t>1523: source value based on MICROBIOLOGY - ORGANISM &gt; ORGANISM - ORGANISM (63.05-12 &gt; 63.3-5+to+160)</t>
@@ -2432,12 +2404,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AS98"/>
+  <dimension ref="A1:AS95"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="61.265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="47.40625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="22.25390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="17.96484375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -5381,7 +5353,7 @@
         <v>85</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>267</v>
+        <v>85</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>85</v>
@@ -5399,16 +5371,16 @@
         <v>119</v>
       </c>
       <c r="Y23" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="Z23" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="Z23" t="s" s="2">
+      <c r="AA23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AB23" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="AC23" s="2"/>
       <c r="AD23" t="s" s="2">
@@ -5433,28 +5405,28 @@
         <v>107</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AM23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AN23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AO23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AP23" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AQ23" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="AR23" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AQ23" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="AR23" t="s" s="2">
-        <v>273</v>
       </c>
       <c r="AS23" t="s" s="2">
         <v>85</v>
@@ -5462,13 +5434,13 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="B24" t="s" s="2">
         <v>262</v>
       </c>
       <c r="C24" t="s" s="2">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="D24" t="s" s="2">
         <v>85</v>
@@ -5512,7 +5484,7 @@
         <v>85</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>85</v>
@@ -5530,10 +5502,10 @@
         <v>119</v>
       </c>
       <c r="Y24" t="s" s="2">
+        <v>267</v>
+      </c>
+      <c r="Z24" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="Z24" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>85</v>
@@ -5566,7 +5538,7 @@
         <v>107</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>85</v>
+        <v>275</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>85</v>
@@ -5584,10 +5556,10 @@
         <v>85</v>
       </c>
       <c r="AQ24" t="s" s="2">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AR24" t="s" s="2">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="AS24" t="s" s="2">
         <v>85</v>
@@ -8395,14 +8367,16 @@
         <v>85</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AC46" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD46" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>439</v>
@@ -8452,11 +8426,9 @@
         <v>451</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C47" t="s" s="2">
-        <v>452</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
         <v>85</v>
       </c>
@@ -8474,22 +8446,22 @@
         <v>85</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="L47" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>442</v>
-      </c>
       <c r="N47" t="s" s="2">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>85</v>
@@ -8514,13 +8486,11 @@
         <v>85</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="Y47" s="2"/>
       <c r="Z47" t="s" s="2">
-        <v>85</v>
+        <v>456</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>85</v>
@@ -8538,7 +8508,7 @@
         <v>85</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>83</v>
@@ -8547,13 +8517,13 @@
         <v>95</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>446</v>
+        <v>107</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>85</v>
@@ -8565,64 +8535,62 @@
         <v>85</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>447</v>
+        <v>85</v>
       </c>
       <c r="AP47" t="s" s="2">
-        <v>448</v>
+        <v>138</v>
       </c>
       <c r="AQ47" t="s" s="2">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="AR47" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS47" t="s" s="2">
-        <v>450</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C48" t="s" s="2">
-        <v>456</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>85</v>
+        <v>461</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H48" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K48" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>441</v>
+        <v>462</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>442</v>
+        <v>463</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>443</v>
+        <v>464</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>85</v>
@@ -8647,13 +8615,13 @@
         <v>85</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>85</v>
+        <v>466</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>85</v>
+        <v>467</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>85</v>
@@ -8671,22 +8639,22 @@
         <v>85</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>439</v>
+        <v>460</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>445</v>
+        <v>85</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>446</v>
+        <v>107</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>457</v>
+        <v>85</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>85</v>
@@ -8698,31 +8666,29 @@
         <v>85</v>
       </c>
       <c r="AO48" t="s" s="2">
-        <v>447</v>
+        <v>468</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="AQ48" t="s" s="2">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="AR48" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS48" t="s" s="2">
-        <v>450</v>
+        <v>471</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>458</v>
+        <v>472</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>472</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>85</v>
       </c>
@@ -8731,7 +8697,7 @@
         <v>83</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>96</v>
@@ -8740,22 +8706,22 @@
         <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>162</v>
+        <v>473</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>441</v>
+        <v>474</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>442</v>
+        <v>475</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>443</v>
+        <v>476</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>444</v>
+        <v>477</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>85</v>
@@ -8804,25 +8770,25 @@
         <v>85</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>439</v>
+        <v>472</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>445</v>
+        <v>85</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>446</v>
+        <v>107</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>460</v>
+        <v>478</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>85</v>
+        <v>479</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>85</v>
@@ -8831,27 +8797,27 @@
         <v>85</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>447</v>
+        <v>85</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>448</v>
+        <v>480</v>
       </c>
       <c r="AQ49" t="s" s="2">
-        <v>449</v>
+        <v>481</v>
       </c>
       <c r="AR49" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS49" t="s" s="2">
-        <v>450</v>
+        <v>85</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8865,7 +8831,7 @@
         <v>95</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>85</v>
@@ -8877,17 +8843,15 @@
         <v>184</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>462</v>
+        <v>483</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>463</v>
+        <v>484</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>465</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>85</v>
       </c>
@@ -8911,11 +8875,13 @@
         <v>85</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>486</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>487</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>466</v>
+        <v>488</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>85</v>
@@ -8933,7 +8899,7 @@
         <v>85</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>461</v>
+        <v>482</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>83</v>
@@ -8942,13 +8908,13 @@
         <v>95</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>467</v>
+        <v>85</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>107</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>468</v>
+        <v>85</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>85</v>
@@ -8960,38 +8926,38 @@
         <v>85</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>85</v>
+        <v>489</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>138</v>
+        <v>490</v>
       </c>
       <c r="AQ50" t="s" s="2">
-        <v>469</v>
+        <v>491</v>
       </c>
       <c r="AR50" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS50" t="s" s="2">
-        <v>85</v>
+        <v>492</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>471</v>
+        <v>85</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>85</v>
@@ -9006,16 +8972,16 @@
         <v>184</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>472</v>
+        <v>494</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>473</v>
+        <v>495</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>474</v>
+        <v>496</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>475</v>
+        <v>497</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>85</v>
@@ -9040,13 +9006,13 @@
         <v>85</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>189</v>
+        <v>486</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>476</v>
+        <v>498</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>477</v>
+        <v>499</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>85</v>
@@ -9064,13 +9030,13 @@
         <v>85</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>470</v>
+        <v>493</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>85</v>
@@ -9091,27 +9057,27 @@
         <v>85</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>478</v>
+        <v>85</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>479</v>
+        <v>500</v>
       </c>
       <c r="AQ51" t="s" s="2">
-        <v>480</v>
+        <v>501</v>
       </c>
       <c r="AR51" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS51" t="s" s="2">
-        <v>481</v>
+        <v>85</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -9122,7 +9088,7 @@
         <v>83</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>96</v>
@@ -9134,20 +9100,18 @@
         <v>85</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>483</v>
+        <v>503</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>484</v>
+        <v>504</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>485</v>
+        <v>505</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>506</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>85</v>
       </c>
@@ -9195,13 +9159,13 @@
         <v>85</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>482</v>
+        <v>502</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>85</v>
@@ -9210,39 +9174,39 @@
         <v>107</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>488</v>
+        <v>507</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>489</v>
+        <v>508</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>85</v>
+        <v>509</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>85</v>
+        <v>510</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>490</v>
+        <v>511</v>
       </c>
       <c r="AQ52" t="s" s="2">
-        <v>491</v>
+        <v>512</v>
       </c>
       <c r="AR52" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS52" t="s" s="2">
-        <v>85</v>
+        <v>513</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -9265,16 +9229,16 @@
         <v>85</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>184</v>
+        <v>515</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>493</v>
+        <v>516</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>494</v>
+        <v>517</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>495</v>
+        <v>518</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -9300,13 +9264,13 @@
         <v>85</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>496</v>
+        <v>85</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>497</v>
+        <v>85</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>498</v>
+        <v>85</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>85</v>
@@ -9324,7 +9288,7 @@
         <v>85</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>492</v>
+        <v>514</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>83</v>
@@ -9351,27 +9315,27 @@
         <v>85</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>499</v>
+        <v>519</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="AQ53" t="s" s="2">
-        <v>501</v>
+        <v>521</v>
       </c>
       <c r="AR53" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS53" t="s" s="2">
-        <v>502</v>
+        <v>522</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -9382,7 +9346,7 @@
         <v>83</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>85</v>
@@ -9394,19 +9358,19 @@
         <v>85</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>184</v>
+        <v>524</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>504</v>
+        <v>525</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>505</v>
+        <v>526</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>506</v>
+        <v>527</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>507</v>
+        <v>528</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>85</v>
@@ -9431,13 +9395,13 @@
         <v>85</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>496</v>
+        <v>85</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>508</v>
+        <v>85</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>509</v>
+        <v>85</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>85</v>
@@ -9455,19 +9419,19 @@
         <v>85</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>503</v>
+        <v>523</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>107</v>
+        <v>529</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>85</v>
@@ -9485,10 +9449,10 @@
         <v>85</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>510</v>
+        <v>530</v>
       </c>
       <c r="AQ54" t="s" s="2">
-        <v>511</v>
+        <v>531</v>
       </c>
       <c r="AR54" t="s" s="2">
         <v>85</v>
@@ -9499,10 +9463,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>512</v>
+        <v>532</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -9516,7 +9480,7 @@
         <v>95</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>85</v>
@@ -9525,17 +9489,15 @@
         <v>85</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>513</v>
+        <v>162</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>514</v>
+        <v>163</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>516</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>85</v>
@@ -9584,7 +9546,7 @@
         <v>85</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>512</v>
+        <v>165</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>83</v>
@@ -9596,53 +9558,53 @@
         <v>85</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>517</v>
+        <v>85</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>518</v>
+        <v>85</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>519</v>
+        <v>85</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>520</v>
+        <v>85</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>521</v>
+        <v>85</v>
       </c>
       <c r="AQ55" t="s" s="2">
-        <v>522</v>
+        <v>166</v>
       </c>
       <c r="AR55" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS55" t="s" s="2">
-        <v>523</v>
+        <v>85</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>85</v>
@@ -9654,16 +9616,16 @@
         <v>85</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>525</v>
+        <v>141</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>526</v>
+        <v>142</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>527</v>
+        <v>168</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>528</v>
+        <v>144</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9713,19 +9675,19 @@
         <v>85</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>524</v>
+        <v>172</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>85</v>
@@ -9740,31 +9702,31 @@
         <v>85</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>529</v>
+        <v>85</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>530</v>
+        <v>85</v>
       </c>
       <c r="AQ56" t="s" s="2">
-        <v>531</v>
+        <v>166</v>
       </c>
       <c r="AR56" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS56" t="s" s="2">
-        <v>532</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>85</v>
+        <v>535</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9777,25 +9739,25 @@
         <v>85</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>534</v>
+        <v>141</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>537</v>
+        <v>144</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>538</v>
+        <v>150</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>85</v>
@@ -9844,7 +9806,7 @@
         <v>85</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>533</v>
+        <v>538</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>83</v>
@@ -9856,7 +9818,7 @@
         <v>85</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>539</v>
+        <v>146</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>85</v>
@@ -9874,10 +9836,10 @@
         <v>85</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>540</v>
+        <v>85</v>
       </c>
       <c r="AQ57" t="s" s="2">
-        <v>541</v>
+        <v>138</v>
       </c>
       <c r="AR57" t="s" s="2">
         <v>85</v>
@@ -9888,10 +9850,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9914,13 +9876,13 @@
         <v>85</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>162</v>
+        <v>540</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>163</v>
+        <v>541</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>164</v>
+        <v>542</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9971,7 +9933,7 @@
         <v>85</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>165</v>
+        <v>539</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>83</v>
@@ -9980,10 +9942,10 @@
         <v>95</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>85</v>
+        <v>543</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>85</v>
@@ -10001,10 +9963,10 @@
         <v>85</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>85</v>
+        <v>544</v>
       </c>
       <c r="AQ58" t="s" s="2">
-        <v>166</v>
+        <v>545</v>
       </c>
       <c r="AR58" t="s" s="2">
         <v>85</v>
@@ -10015,21 +9977,21 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>85</v>
@@ -10041,17 +10003,15 @@
         <v>85</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>141</v>
+        <v>540</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>142</v>
+        <v>547</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>85</v>
@@ -10100,19 +10060,19 @@
         <v>85</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>172</v>
+        <v>546</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>85</v>
+        <v>543</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>85</v>
@@ -10130,10 +10090,10 @@
         <v>85</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>85</v>
+        <v>544</v>
       </c>
       <c r="AQ59" t="s" s="2">
-        <v>166</v>
+        <v>549</v>
       </c>
       <c r="AR59" t="s" s="2">
         <v>85</v>
@@ -10144,45 +10104,45 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>545</v>
+        <v>85</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>144</v>
+        <v>553</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>150</v>
+        <v>554</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>85</v>
@@ -10207,13 +10167,13 @@
         <v>85</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>85</v>
+        <v>555</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>85</v>
+        <v>556</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>85</v>
@@ -10231,19 +10191,19 @@
         <v>85</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>85</v>
@@ -10258,13 +10218,13 @@
         <v>85</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>85</v>
+        <v>557</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>85</v>
+        <v>558</v>
       </c>
       <c r="AQ60" t="s" s="2">
-        <v>138</v>
+        <v>470</v>
       </c>
       <c r="AR60" t="s" s="2">
         <v>85</v>
@@ -10275,10 +10235,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -10289,7 +10249,7 @@
         <v>83</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>85</v>
@@ -10301,16 +10261,20 @@
         <v>85</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>550</v>
+        <v>184</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>561</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>563</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>85</v>
       </c>
@@ -10334,13 +10298,13 @@
         <v>85</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>85</v>
+        <v>564</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>85</v>
+        <v>565</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>85</v>
@@ -10358,16 +10322,16 @@
         <v>85</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>549</v>
+        <v>559</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>553</v>
+        <v>85</v>
       </c>
       <c r="AJ61" t="s" s="2">
         <v>107</v>
@@ -10385,13 +10349,13 @@
         <v>85</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>85</v>
+        <v>557</v>
       </c>
       <c r="AP61" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="AQ61" t="s" s="2">
-        <v>555</v>
+        <v>470</v>
       </c>
       <c r="AR61" t="s" s="2">
         <v>85</v>
@@ -10402,10 +10366,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -10428,16 +10392,18 @@
         <v>85</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>550</v>
+        <v>567</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="N62" s="2"/>
-      <c r="O62" s="2"/>
+      <c r="O62" t="s" s="2">
+        <v>570</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>85</v>
       </c>
@@ -10485,7 +10451,7 @@
         <v>85</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>556</v>
+        <v>566</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>83</v>
@@ -10494,7 +10460,7 @@
         <v>95</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>553</v>
+        <v>85</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>107</v>
@@ -10515,10 +10481,10 @@
         <v>85</v>
       </c>
       <c r="AP62" t="s" s="2">
-        <v>554</v>
+        <v>85</v>
       </c>
       <c r="AQ62" t="s" s="2">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="AR62" t="s" s="2">
         <v>85</v>
@@ -10529,10 +10495,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -10555,20 +10521,16 @@
         <v>85</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>564</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>85</v>
       </c>
@@ -10592,13 +10554,13 @@
         <v>85</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>119</v>
+        <v>85</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>565</v>
+        <v>85</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>566</v>
+        <v>85</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>85</v>
@@ -10616,7 +10578,7 @@
         <v>85</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>83</v>
@@ -10643,13 +10605,13 @@
         <v>85</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>567</v>
+        <v>85</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>568</v>
+        <v>544</v>
       </c>
       <c r="AQ63" t="s" s="2">
-        <v>480</v>
+        <v>575</v>
       </c>
       <c r="AR63" t="s" s="2">
         <v>85</v>
@@ -10660,10 +10622,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10683,23 +10645,21 @@
         <v>85</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>184</v>
+        <v>577</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>570</v>
+        <v>578</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>571</v>
+        <v>579</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="O64" t="s" s="2">
-        <v>573</v>
-      </c>
+        <v>580</v>
+      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>85</v>
       </c>
@@ -10723,13 +10683,13 @@
         <v>85</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>496</v>
+        <v>85</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>574</v>
+        <v>85</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>575</v>
+        <v>85</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>85</v>
@@ -10747,7 +10707,7 @@
         <v>85</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>569</v>
+        <v>576</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>83</v>
@@ -10774,13 +10734,13 @@
         <v>85</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>567</v>
+        <v>85</v>
       </c>
       <c r="AP64" t="s" s="2">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="AQ64" t="s" s="2">
-        <v>480</v>
+        <v>582</v>
       </c>
       <c r="AR64" t="s" s="2">
         <v>85</v>
@@ -10791,10 +10751,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10805,7 +10765,7 @@
         <v>83</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>85</v>
@@ -10814,21 +10774,21 @@
         <v>85</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="N65" s="2"/>
-      <c r="O65" t="s" s="2">
-        <v>580</v>
-      </c>
+        <v>586</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>85</v>
       </c>
@@ -10876,13 +10836,13 @@
         <v>85</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>85</v>
@@ -10906,10 +10866,10 @@
         <v>85</v>
       </c>
       <c r="AP65" t="s" s="2">
-        <v>85</v>
+        <v>581</v>
       </c>
       <c r="AQ65" t="s" s="2">
-        <v>581</v>
+        <v>588</v>
       </c>
       <c r="AR65" t="s" s="2">
         <v>85</v>
@@ -10920,10 +10880,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10934,7 +10894,7 @@
         <v>83</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>85</v>
@@ -10943,19 +10903,23 @@
         <v>85</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>162</v>
+        <v>524</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>583</v>
+        <v>590</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>591</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>593</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>85</v>
       </c>
@@ -10991,25 +10955,23 @@
         <v>85</v>
       </c>
       <c r="AB66" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="AC66" s="2"/>
       <c r="AD66" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE66" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>582</v>
+        <v>589</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>85</v>
@@ -11033,10 +10995,10 @@
         <v>85</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>554</v>
+        <v>595</v>
       </c>
       <c r="AQ66" t="s" s="2">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="AR66" t="s" s="2">
         <v>85</v>
@@ -11047,10 +11009,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -11061,7 +11023,7 @@
         <v>83</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>85</v>
@@ -11070,20 +11032,18 @@
         <v>85</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>587</v>
+        <v>162</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>588</v>
+        <v>163</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>590</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N67" s="2"/>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>85</v>
@@ -11132,19 +11092,19 @@
         <v>85</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>586</v>
+        <v>165</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>85</v>
@@ -11162,10 +11122,10 @@
         <v>85</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>591</v>
+        <v>85</v>
       </c>
       <c r="AQ67" t="s" s="2">
-        <v>592</v>
+        <v>166</v>
       </c>
       <c r="AR67" t="s" s="2">
         <v>85</v>
@@ -11176,14 +11136,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>593</v>
+        <v>598</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -11199,19 +11159,19 @@
         <v>85</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>594</v>
+        <v>141</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>595</v>
+        <v>142</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>596</v>
+        <v>168</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>597</v>
+        <v>144</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -11261,7 +11221,7 @@
         <v>85</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>593</v>
+        <v>172</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>83</v>
@@ -11273,7 +11233,7 @@
         <v>85</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>85</v>
@@ -11291,10 +11251,10 @@
         <v>85</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>591</v>
+        <v>85</v>
       </c>
       <c r="AQ68" t="s" s="2">
-        <v>598</v>
+        <v>166</v>
       </c>
       <c r="AR68" t="s" s="2">
         <v>85</v>
@@ -11312,7 +11272,7 @@
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>85</v>
+        <v>535</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -11325,25 +11285,25 @@
         <v>85</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>534</v>
+        <v>141</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>600</v>
+        <v>536</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>601</v>
+        <v>537</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>602</v>
+        <v>144</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>603</v>
+        <v>150</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>85</v>
@@ -11380,17 +11340,19 @@
         <v>85</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="AC69" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD69" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>599</v>
+        <v>538</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>83</v>
@@ -11402,7 +11364,7 @@
         <v>85</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>85</v>
@@ -11420,10 +11382,10 @@
         <v>85</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>605</v>
+        <v>85</v>
       </c>
       <c r="AQ69" t="s" s="2">
-        <v>606</v>
+        <v>138</v>
       </c>
       <c r="AR69" t="s" s="2">
         <v>85</v>
@@ -11434,10 +11396,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -11445,7 +11407,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>95</v>
@@ -11457,19 +11419,23 @@
         <v>85</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>163</v>
+        <v>601</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N70" s="2"/>
-      <c r="O70" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>85</v>
       </c>
@@ -11493,13 +11459,13 @@
         <v>85</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>85</v>
+        <v>604</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>85</v>
+        <v>283</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>85</v>
@@ -11517,10 +11483,10 @@
         <v>85</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>165</v>
+        <v>600</v>
       </c>
       <c r="AG70" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH70" t="s" s="2">
         <v>95</v>
@@ -11529,7 +11495,7 @@
         <v>85</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>85</v>
@@ -11544,16 +11510,16 @@
         <v>85</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>85</v>
+        <v>605</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>85</v>
+        <v>286</v>
       </c>
       <c r="AQ70" t="s" s="2">
-        <v>166</v>
+        <v>287</v>
       </c>
       <c r="AR70" t="s" s="2">
-        <v>85</v>
+        <v>288</v>
       </c>
       <c r="AS70" t="s" s="2">
         <v>85</v>
@@ -11561,21 +11527,21 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>85</v>
@@ -11584,21 +11550,23 @@
         <v>85</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>141</v>
+        <v>440</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>142</v>
+        <v>607</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>168</v>
+        <v>608</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O71" s="2"/>
+        <v>609</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>444</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>85</v>
       </c>
@@ -11646,19 +11614,19 @@
         <v>85</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>172</v>
+        <v>606</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>85</v>
@@ -11673,62 +11641,62 @@
         <v>85</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>85</v>
+        <v>610</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>85</v>
+        <v>448</v>
       </c>
       <c r="AQ71" t="s" s="2">
-        <v>166</v>
+        <v>449</v>
       </c>
       <c r="AR71" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS71" t="s" s="2">
-        <v>85</v>
+        <v>450</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>545</v>
+        <v>85</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I72" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>546</v>
+        <v>612</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>547</v>
+        <v>613</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>144</v>
+        <v>614</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>150</v>
+        <v>455</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>85</v>
@@ -11753,13 +11721,13 @@
         <v>85</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>85</v>
+        <v>615</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>85</v>
+        <v>456</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>85</v>
@@ -11777,19 +11745,19 @@
         <v>85</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>548</v>
+        <v>611</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>85</v>
+        <v>616</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>85</v>
@@ -11807,10 +11775,10 @@
         <v>85</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>85</v>
+        <v>138</v>
       </c>
       <c r="AQ72" t="s" s="2">
-        <v>138</v>
+        <v>459</v>
       </c>
       <c r="AR72" t="s" s="2">
         <v>85</v>
@@ -11821,21 +11789,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>85</v>
+        <v>461</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>85</v>
@@ -11844,22 +11812,22 @@
         <v>85</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K73" t="s" s="2">
         <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>611</v>
+        <v>462</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>612</v>
+        <v>463</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>613</v>
+        <v>464</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>281</v>
+        <v>465</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>85</v>
@@ -11884,13 +11852,13 @@
         <v>85</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>496</v>
+        <v>189</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>614</v>
+        <v>466</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>283</v>
+        <v>467</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>85</v>
@@ -11908,13 +11876,13 @@
         <v>85</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>610</v>
+        <v>617</v>
       </c>
       <c r="AG73" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>85</v>
@@ -11935,27 +11903,27 @@
         <v>85</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>615</v>
+        <v>468</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>286</v>
+        <v>469</v>
       </c>
       <c r="AQ73" t="s" s="2">
-        <v>287</v>
+        <v>470</v>
       </c>
       <c r="AR73" t="s" s="2">
-        <v>288</v>
+        <v>85</v>
       </c>
       <c r="AS73" t="s" s="2">
-        <v>85</v>
+        <v>471</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11966,7 +11934,7 @@
         <v>83</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>85</v>
@@ -11975,22 +11943,22 @@
         <v>85</v>
       </c>
       <c r="J74" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>440</v>
+        <v>86</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>619</v>
+        <v>527</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>444</v>
+        <v>528</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>85</v>
@@ -12039,13 +12007,13 @@
         <v>85</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>85</v>
@@ -12066,19 +12034,19 @@
         <v>85</v>
       </c>
       <c r="AO74" t="s" s="2">
-        <v>620</v>
+        <v>85</v>
       </c>
       <c r="AP74" t="s" s="2">
-        <v>448</v>
+        <v>530</v>
       </c>
       <c r="AQ74" t="s" s="2">
-        <v>449</v>
+        <v>531</v>
       </c>
       <c r="AR74" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS74" t="s" s="2">
-        <v>450</v>
+        <v>85</v>
       </c>
     </row>
     <row r="75" hidden="true">
@@ -12086,9 +12054,11 @@
         <v>621</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C75" s="2"/>
+        <v>589</v>
+      </c>
+      <c r="C75" t="s" s="2">
+        <v>622</v>
+      </c>
       <c r="D75" t="s" s="2">
         <v>85</v>
       </c>
@@ -12106,22 +12076,22 @@
         <v>85</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>184</v>
+        <v>524</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>622</v>
+        <v>590</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>623</v>
+        <v>591</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>624</v>
+        <v>592</v>
       </c>
       <c r="O75" t="s" s="2">
-        <v>465</v>
+        <v>593</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>85</v>
@@ -12146,13 +12116,13 @@
         <v>85</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>625</v>
+        <v>85</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>466</v>
+        <v>85</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>85</v>
@@ -12170,16 +12140,16 @@
         <v>85</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>621</v>
+        <v>589</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>626</v>
+        <v>85</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>107</v>
@@ -12200,10 +12170,10 @@
         <v>85</v>
       </c>
       <c r="AP75" t="s" s="2">
-        <v>138</v>
+        <v>595</v>
       </c>
       <c r="AQ75" t="s" s="2">
-        <v>469</v>
+        <v>596</v>
       </c>
       <c r="AR75" t="s" s="2">
         <v>85</v>
@@ -12214,21 +12184,21 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>627</v>
+        <v>597</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>471</v>
+        <v>85</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>85</v>
@@ -12240,20 +12210,16 @@
         <v>85</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>184</v>
+        <v>162</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>472</v>
+        <v>163</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>475</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>85</v>
       </c>
@@ -12277,13 +12243,13 @@
         <v>85</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>189</v>
+        <v>85</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>476</v>
+        <v>85</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>477</v>
+        <v>85</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>85</v>
@@ -12301,19 +12267,19 @@
         <v>85</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>627</v>
+        <v>165</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>85</v>
@@ -12328,31 +12294,31 @@
         <v>85</v>
       </c>
       <c r="AO76" t="s" s="2">
-        <v>478</v>
+        <v>85</v>
       </c>
       <c r="AP76" t="s" s="2">
-        <v>479</v>
+        <v>85</v>
       </c>
       <c r="AQ76" t="s" s="2">
-        <v>480</v>
+        <v>166</v>
       </c>
       <c r="AR76" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS76" t="s" s="2">
-        <v>481</v>
+        <v>85</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>628</v>
+        <v>598</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -12371,20 +12337,18 @@
         <v>85</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>629</v>
+        <v>142</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>630</v>
+        <v>168</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>144</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>85</v>
       </c>
@@ -12432,7 +12396,7 @@
         <v>85</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>628</v>
+        <v>172</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>83</v>
@@ -12444,7 +12408,7 @@
         <v>85</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>85</v>
@@ -12462,10 +12426,10 @@
         <v>85</v>
       </c>
       <c r="AP77" t="s" s="2">
-        <v>540</v>
+        <v>85</v>
       </c>
       <c r="AQ77" t="s" s="2">
-        <v>541</v>
+        <v>166</v>
       </c>
       <c r="AR77" t="s" s="2">
         <v>85</v>
@@ -12476,47 +12440,45 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="C78" t="s" s="2">
-        <v>632</v>
-      </c>
+      <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>85</v>
+        <v>535</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>85</v>
       </c>
       <c r="I78" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="J78" t="s" s="2">
         <v>96</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>534</v>
+        <v>141</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>600</v>
+        <v>536</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>601</v>
+        <v>537</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>602</v>
+        <v>144</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>603</v>
+        <v>150</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>85</v>
@@ -12565,7 +12527,7 @@
         <v>85</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>599</v>
+        <v>538</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>83</v>
@@ -12577,7 +12539,7 @@
         <v>85</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>107</v>
+        <v>146</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>85</v>
@@ -12595,10 +12557,10 @@
         <v>85</v>
       </c>
       <c r="AP78" t="s" s="2">
-        <v>605</v>
+        <v>85</v>
       </c>
       <c r="AQ78" t="s" s="2">
-        <v>606</v>
+        <v>138</v>
       </c>
       <c r="AR78" t="s" s="2">
         <v>85</v>
@@ -12609,10 +12571,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -12620,31 +12582,35 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="G79" t="s" s="2">
         <v>95</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>163</v>
+        <v>601</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+        <v>602</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="O79" t="s" s="2">
+        <v>281</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>85</v>
       </c>
@@ -12668,13 +12634,13 @@
         <v>85</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>85</v>
+        <v>486</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>85</v>
+        <v>604</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>85</v>
+        <v>283</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>85</v>
@@ -12692,10 +12658,10 @@
         <v>85</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>165</v>
+        <v>600</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="AH79" t="s" s="2">
         <v>95</v>
@@ -12704,10 +12670,10 @@
         <v>85</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>85</v>
+        <v>627</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>85</v>
@@ -12719,16 +12685,16 @@
         <v>85</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>85</v>
+        <v>605</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>85</v>
+        <v>286</v>
       </c>
       <c r="AQ79" t="s" s="2">
-        <v>166</v>
+        <v>287</v>
       </c>
       <c r="AR79" t="s" s="2">
-        <v>85</v>
+        <v>288</v>
       </c>
       <c r="AS79" t="s" s="2">
         <v>85</v>
@@ -12736,21 +12702,21 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>608</v>
+        <v>629</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>85</v>
@@ -12762,17 +12728,15 @@
         <v>85</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>141</v>
+        <v>162</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N80" t="s" s="2">
-        <v>144</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N80" s="2"/>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>85</v>
@@ -12821,19 +12785,19 @@
         <v>85</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>146</v>
+        <v>85</v>
       </c>
       <c r="AK80" t="s" s="2">
         <v>85</v>
@@ -12865,14 +12829,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>635</v>
+        <v>630</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>609</v>
+        <v>631</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>545</v>
+        <v>140</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -12885,26 +12849,24 @@
         <v>85</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K81" t="s" s="2">
         <v>141</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>546</v>
+        <v>142</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>547</v>
+        <v>168</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="O81" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>85</v>
       </c>
@@ -12940,19 +12902,19 @@
         <v>85</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>85</v>
+        <v>169</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>85</v>
+        <v>170</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>548</v>
+        <v>172</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>83</v>
@@ -12985,7 +12947,7 @@
         <v>85</v>
       </c>
       <c r="AQ81" t="s" s="2">
-        <v>138</v>
+        <v>166</v>
       </c>
       <c r="AR81" t="s" s="2">
         <v>85</v>
@@ -12996,10 +12958,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>610</v>
+        <v>633</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -13007,13 +12969,13 @@
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>85</v>
@@ -13022,19 +12984,19 @@
         <v>96</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>184</v>
+        <v>293</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>611</v>
+        <v>294</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>612</v>
+        <v>295</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>613</v>
+        <v>296</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>85</v>
@@ -13059,13 +13021,13 @@
         <v>85</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>496</v>
+        <v>85</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>614</v>
+        <v>85</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>283</v>
+        <v>85</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>85</v>
@@ -13083,13 +13045,13 @@
         <v>85</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>610</v>
+        <v>298</v>
       </c>
       <c r="AG82" t="s" s="2">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>85</v>
@@ -13098,7 +13060,7 @@
         <v>107</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>637</v>
+        <v>85</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>85</v>
@@ -13110,16 +13072,16 @@
         <v>85</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>615</v>
+        <v>85</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="AQ82" t="s" s="2">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="AR82" t="s" s="2">
-        <v>288</v>
+        <v>85</v>
       </c>
       <c r="AS82" t="s" s="2">
         <v>85</v>
@@ -13127,10 +13089,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -13254,10 +13216,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -13383,10 +13345,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>643</v>
+        <v>639</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -13397,10 +13359,10 @@
         <v>83</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>85</v>
@@ -13409,19 +13371,19 @@
         <v>96</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>293</v>
+        <v>109</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>296</v>
+        <v>308</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>85</v>
@@ -13431,7 +13393,7 @@
         <v>85</v>
       </c>
       <c r="S85" t="s" s="2">
-        <v>85</v>
+        <v>640</v>
       </c>
       <c r="T85" t="s" s="2">
         <v>85</v>
@@ -13470,13 +13432,13 @@
         <v>85</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>85</v>
@@ -13485,7 +13447,7 @@
         <v>107</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>85</v>
+        <v>641</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>85</v>
@@ -13500,10 +13462,10 @@
         <v>85</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="AQ85" t="s" s="2">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="AR85" t="s" s="2">
         <v>85</v>
@@ -13514,10 +13476,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -13537,18 +13499,20 @@
         <v>85</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K86" t="s" s="2">
         <v>162</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>163</v>
+        <v>316</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N86" s="2"/>
+        <v>317</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>85</v>
@@ -13597,7 +13561,7 @@
         <v>85</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>165</v>
+        <v>319</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>83</v>
@@ -13609,7 +13573,7 @@
         <v>85</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>85</v>
@@ -13627,10 +13591,10 @@
         <v>85</v>
       </c>
       <c r="AP86" t="s" s="2">
-        <v>85</v>
+        <v>320</v>
       </c>
       <c r="AQ86" t="s" s="2">
-        <v>166</v>
+        <v>321</v>
       </c>
       <c r="AR86" t="s" s="2">
         <v>85</v>
@@ -13641,44 +13605,44 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>140</v>
+        <v>85</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="H87" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I87" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>142</v>
+        <v>323</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="O87" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>85</v>
       </c>
@@ -13714,34 +13678,34 @@
         <v>85</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>169</v>
+        <v>85</v>
       </c>
       <c r="AC87" t="s" s="2">
-        <v>170</v>
+        <v>85</v>
       </c>
       <c r="AD87" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE87" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>172</v>
+        <v>326</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>146</v>
+        <v>107</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>85</v>
+        <v>646</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>85</v>
@@ -13756,10 +13720,10 @@
         <v>85</v>
       </c>
       <c r="AP87" t="s" s="2">
-        <v>85</v>
+        <v>329</v>
       </c>
       <c r="AQ87" t="s" s="2">
-        <v>166</v>
+        <v>330</v>
       </c>
       <c r="AR87" t="s" s="2">
         <v>85</v>
@@ -13770,10 +13734,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="B88" t="s" s="2">
         <v>648</v>
-      </c>
-      <c r="B88" t="s" s="2">
-        <v>649</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13787,7 +13751,7 @@
         <v>95</v>
       </c>
       <c r="H88" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I88" t="s" s="2">
         <v>85</v>
@@ -13796,19 +13760,17 @@
         <v>96</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>109</v>
+        <v>162</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>306</v>
+        <v>332</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>309</v>
+        <v>334</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>85</v>
@@ -13818,7 +13780,7 @@
         <v>85</v>
       </c>
       <c r="S88" t="s" s="2">
-        <v>650</v>
+        <v>85</v>
       </c>
       <c r="T88" t="s" s="2">
         <v>85</v>
@@ -13857,7 +13819,7 @@
         <v>85</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>83</v>
@@ -13872,7 +13834,7 @@
         <v>107</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>651</v>
+        <v>85</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>85</v>
@@ -13887,10 +13849,10 @@
         <v>85</v>
       </c>
       <c r="AP88" t="s" s="2">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="AQ88" t="s" s="2">
-        <v>314</v>
+        <v>339</v>
       </c>
       <c r="AR88" t="s" s="2">
         <v>85</v>
@@ -13901,10 +13863,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13927,18 +13889,20 @@
         <v>96</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>162</v>
+        <v>341</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>316</v>
+        <v>342</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>317</v>
+        <v>343</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="O89" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>345</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>85</v>
       </c>
@@ -13986,7 +13950,7 @@
         <v>85</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>83</v>
@@ -14016,10 +13980,10 @@
         <v>85</v>
       </c>
       <c r="AP89" t="s" s="2">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="AQ89" t="s" s="2">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="AR89" t="s" s="2">
         <v>85</v>
@@ -14030,10 +13994,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -14047,7 +14011,7 @@
         <v>95</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>85</v>
@@ -14056,17 +14020,19 @@
         <v>96</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>115</v>
+        <v>162</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>323</v>
+        <v>350</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>351</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>352</v>
+      </c>
       <c r="O90" t="s" s="2">
-        <v>325</v>
+        <v>353</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>85</v>
@@ -14115,7 +14081,7 @@
         <v>85</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>83</v>
@@ -14130,7 +14096,7 @@
         <v>107</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>656</v>
+        <v>85</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>85</v>
@@ -14145,10 +14111,10 @@
         <v>85</v>
       </c>
       <c r="AP90" t="s" s="2">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="AQ90" t="s" s="2">
-        <v>330</v>
+        <v>356</v>
       </c>
       <c r="AR90" t="s" s="2">
         <v>85</v>
@@ -14159,10 +14125,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>658</v>
+        <v>606</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -14185,17 +14151,19 @@
         <v>96</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>162</v>
+        <v>440</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>332</v>
+        <v>607</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>608</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>609</v>
+      </c>
       <c r="O91" t="s" s="2">
-        <v>334</v>
+        <v>444</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>85</v>
@@ -14232,19 +14200,17 @@
         <v>85</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC91" t="s" s="2">
-        <v>85</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="AC91" s="2"/>
       <c r="AD91" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>85</v>
+        <v>171</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>335</v>
+        <v>606</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>83</v>
@@ -14271,29 +14237,31 @@
         <v>85</v>
       </c>
       <c r="AO91" t="s" s="2">
-        <v>85</v>
+        <v>610</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>338</v>
+        <v>448</v>
       </c>
       <c r="AQ91" t="s" s="2">
-        <v>339</v>
+        <v>449</v>
       </c>
       <c r="AR91" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS91" t="s" s="2">
-        <v>85</v>
+        <v>450</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="C92" s="2"/>
+        <v>606</v>
+      </c>
+      <c r="C92" t="s" s="2">
+        <v>655</v>
+      </c>
       <c r="D92" t="s" s="2">
         <v>85</v>
       </c>
@@ -14305,7 +14273,7 @@
         <v>95</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>85</v>
@@ -14314,19 +14282,19 @@
         <v>96</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>341</v>
+        <v>162</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>342</v>
+        <v>607</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>343</v>
+        <v>608</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>344</v>
+        <v>609</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>345</v>
+        <v>444</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>85</v>
@@ -14375,7 +14343,7 @@
         <v>85</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>346</v>
+        <v>606</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>83</v>
@@ -14390,7 +14358,7 @@
         <v>107</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>85</v>
+        <v>656</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>85</v>
@@ -14402,27 +14370,27 @@
         <v>85</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>85</v>
+        <v>610</v>
       </c>
       <c r="AP92" t="s" s="2">
-        <v>347</v>
+        <v>448</v>
       </c>
       <c r="AQ92" t="s" s="2">
-        <v>348</v>
+        <v>449</v>
       </c>
       <c r="AR92" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS92" t="s" s="2">
-        <v>85</v>
+        <v>450</v>
       </c>
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>661</v>
+        <v>657</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>662</v>
+        <v>611</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -14442,22 +14410,22 @@
         <v>85</v>
       </c>
       <c r="J93" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>162</v>
+        <v>184</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>350</v>
+        <v>612</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>351</v>
+        <v>613</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>352</v>
+        <v>614</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>353</v>
+        <v>455</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>85</v>
@@ -14482,13 +14450,13 @@
         <v>85</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>85</v>
+        <v>189</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>85</v>
+        <v>615</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>85</v>
+        <v>456</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>85</v>
@@ -14506,7 +14474,7 @@
         <v>85</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>354</v>
+        <v>611</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>83</v>
@@ -14515,7 +14483,7 @@
         <v>95</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>85</v>
+        <v>616</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>107</v>
@@ -14536,10 +14504,10 @@
         <v>85</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>355</v>
+        <v>138</v>
       </c>
       <c r="AQ93" t="s" s="2">
-        <v>356</v>
+        <v>459</v>
       </c>
       <c r="AR93" t="s" s="2">
         <v>85</v>
@@ -14550,45 +14518,45 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>663</v>
+        <v>658</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>85</v>
+        <v>461</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="G94" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H94" t="s" s="2">
-        <v>85</v>
+        <v>96</v>
       </c>
       <c r="I94" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>440</v>
+        <v>184</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>617</v>
+        <v>462</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>618</v>
+        <v>463</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>619</v>
+        <v>464</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>444</v>
+        <v>465</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>85</v>
@@ -14613,35 +14581,37 @@
         <v>85</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>85</v>
+        <v>178</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>85</v>
+        <v>659</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>85</v>
+        <v>660</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AB94" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AC94" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="AD94" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AE94" t="s" s="2">
-        <v>171</v>
+        <v>85</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>85</v>
@@ -14650,7 +14620,7 @@
         <v>107</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>85</v>
+        <v>661</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>85</v>
@@ -14662,31 +14632,29 @@
         <v>85</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>620</v>
+        <v>468</v>
       </c>
       <c r="AP94" t="s" s="2">
-        <v>448</v>
+        <v>469</v>
       </c>
       <c r="AQ94" t="s" s="2">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="AR94" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS94" t="s" s="2">
-        <v>450</v>
+        <v>471</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="C95" t="s" s="2">
-        <v>459</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>85</v>
       </c>
@@ -14695,31 +14663,31 @@
         <v>83</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>619</v>
+        <v>527</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>444</v>
+        <v>528</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>85</v>
@@ -14768,13 +14736,13 @@
         <v>85</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>85</v>
@@ -14783,7 +14751,7 @@
         <v>107</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>665</v>
+        <v>85</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>85</v>
@@ -14795,416 +14763,23 @@
         <v>85</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>620</v>
+        <v>85</v>
       </c>
       <c r="AP95" t="s" s="2">
-        <v>448</v>
+        <v>530</v>
       </c>
       <c r="AQ95" t="s" s="2">
-        <v>449</v>
+        <v>531</v>
       </c>
       <c r="AR95" t="s" s="2">
         <v>85</v>
       </c>
       <c r="AS95" t="s" s="2">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="96" hidden="true">
-      <c r="A96" t="s" s="2">
-        <v>666</v>
-      </c>
-      <c r="B96" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="C96" s="2"/>
-      <c r="D96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E96" s="2"/>
-      <c r="F96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G96" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="H96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K96" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L96" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="O96" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="P96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q96" s="2"/>
-      <c r="R96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X96" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="Y96" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="Z96" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AA96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF96" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="AG96" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH96" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AI96" t="s" s="2">
-        <v>626</v>
-      </c>
-      <c r="AJ96" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AQ96" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AR96" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS96" t="s" s="2">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="97" hidden="true">
-      <c r="A97" t="s" s="2">
-        <v>667</v>
-      </c>
-      <c r="B97" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="C97" s="2"/>
-      <c r="D97" t="s" s="2">
-        <v>471</v>
-      </c>
-      <c r="E97" s="2"/>
-      <c r="F97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H97" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="I97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K97" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L97" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="M97" t="s" s="2">
-        <v>473</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>474</v>
-      </c>
-      <c r="O97" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="P97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q97" s="2"/>
-      <c r="R97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X97" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="Y97" t="s" s="2">
-        <v>668</v>
-      </c>
-      <c r="Z97" t="s" s="2">
-        <v>669</v>
-      </c>
-      <c r="AA97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF97" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="AG97" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH97" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ97" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK97" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>478</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>479</v>
-      </c>
-      <c r="AQ97" t="s" s="2">
-        <v>480</v>
-      </c>
-      <c r="AR97" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS97" t="s" s="2">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>671</v>
-      </c>
-      <c r="B98" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="C98" s="2"/>
-      <c r="D98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="E98" s="2"/>
-      <c r="F98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="G98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="H98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="I98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="J98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="K98" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L98" t="s" s="2">
-        <v>629</v>
-      </c>
-      <c r="M98" t="s" s="2">
-        <v>630</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="P98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Q98" s="2"/>
-      <c r="R98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="S98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="T98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="U98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="V98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="W98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="X98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="Z98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AA98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AB98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AC98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AD98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AE98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AF98" t="s" s="2">
-        <v>628</v>
-      </c>
-      <c r="AG98" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AH98" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AJ98" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AK98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AL98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AP98" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="AQ98" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="AR98" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="AS98" t="s" s="2">
         <v>85</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AS98">
+  <autoFilter ref="A1:AS95">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15214,7 +14789,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI97">
+  <conditionalFormatting sqref="A2:AI94">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyBacteriologyObservation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
